--- a/sample-data/sample-run/selections/Chain Ladder Selections - LDFs.xlsx
+++ b/sample-data/sample-run/selections/Chain Ladder Selections - LDFs.xlsx
@@ -5881,49 +5881,49 @@
         <v>1.7024</v>
       </c>
       <c r="C72" s="21" t="n">
-        <v>1.2309</v>
+        <v>1.2575</v>
       </c>
       <c r="D72" s="21" t="n">
-        <v>1.1874</v>
+        <v>1.2002</v>
       </c>
       <c r="E72" s="21" t="n">
-        <v>1.057</v>
+        <v>1.0567</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>1.1071</v>
+        <v>1.1027</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>1.0836</v>
+        <v>1.087</v>
       </c>
       <c r="H72" s="21" t="n">
-        <v>1.0076</v>
+        <v>1.0065</v>
       </c>
       <c r="I72" s="21" t="n">
-        <v>1.0207</v>
+        <v>1.0146</v>
       </c>
       <c r="J72" s="21" t="n">
-        <v>1.0354</v>
+        <v>1.0485</v>
       </c>
       <c r="K72" s="21" t="n">
-        <v>1.0059</v>
+        <v>1.0082</v>
       </c>
       <c r="L72" s="21" t="n">
-        <v>1.0379</v>
+        <v>1.035</v>
       </c>
       <c r="M72" s="21" t="n">
-        <v>1.0033</v>
+        <v>1.0022</v>
       </c>
       <c r="N72" s="21" t="n">
         <v>1.0004</v>
       </c>
       <c r="O72" s="21" t="n">
-        <v>1.01</v>
+        <v>1.0211</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>1.0047</v>
+        <v>1.0036</v>
       </c>
       <c r="Q72" s="21" t="n">
-        <v>1.0086</v>
+        <v>1.0076</v>
       </c>
       <c r="R72" s="21" t="n">
         <v>1.002</v>
@@ -5932,13 +5932,13 @@
         <v>1</v>
       </c>
       <c r="T72" s="21" t="n">
-        <v>1.0085</v>
+        <v>1.0089</v>
       </c>
       <c r="U72" s="21" t="n">
-        <v>1.0043</v>
+        <v>1.0069</v>
       </c>
       <c r="V72" s="21" t="n">
-        <v>1.0166</v>
+        <v>1.0174</v>
       </c>
       <c r="W72" s="21" t="n">
         <v>1</v>
@@ -5955,117 +5955,117 @@
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.7024. Five-year volume-weighted (1.7024) selected. Significant variance (CV_5yr 0.3284) warrants high/low exclusion. 3-year (1.4891) vs 5-year (1.7024) shows 14% divergence—suggests regime change or emerging severity trend. Slope_5yr negative (-0.2685), but 3yr positive (0.1182), indicating recent reversal. Bayesian approach: blend 60% toward 3-year (1.4891) and 40% toward 5-year result = 0.6×1.4891 + 0.4×1.7024 ≈ 1.5762; round to 1.5840 conservatively for early maturity upside risk on incurred. Diagnostics: paid_to_incurred ranges 0.35–0.50 (normal early case posting), no catastrophic spike in incurred_severity.</t>
+          <t>Incurred Loss: 1.7024. CV_5yr 0.3284 (exceeds 0.20 threshold) triggers outlier caution. Apply exclusion of single high/low per framework. Weighted 5-year (1.7024) and simple 5-year (1.784) show 3.2% gap; weighted preferred to dampen outlier influence. All-year (1.6135) 5.5% below, suggesting old periods skew lower. Slope_5yr negative (-0.2685) signals potential regime shift. Incurred more volatile than paid at early maturity; Bayesian anchoring toward weighted 5-year appropriate. Asymmetric conservatism: 3-year (1.4891) substantially below 5-year, so moderate upward approach from lower bounds. Select weighted 5-year as primary anchor with outlier dampening.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.2309. Five-year volume-weighted (1.2309) selected. High variance (CV_5yr 0.2103) indicates single high/low exclusion applied; exclude_high_low_5yr 1.2120 slightly lower suggests outlier removal has modest downward pull. 3yr (1.054) significantly below 5yr (1.2309)—14% divergence. Trending detected: 3yr lower, suggesting development may be slowing post-report. Bayesian: weight 60% recent (1.054) + 40% 5yr (1.2309) ≈ 1.1176; but 2003 (1.5785 per diagnostics) shows reserve strengthening at this age in older years. Select 1.2309 with caution; incurred reserve adequacy flat per diagnostics, no case reserve shift. This maturity is post-reporting; use convergence safeguard.</t>
+          <t>Incurred Loss: 1.2575. CV_5yr 0.2103 (at upper tolerance, &lt;0.20 marginal) applies standard averaging with caution. Weighted 5-year (1.2575) vs simple 5-year (1.2309) ~2.1% gap; weighted preferred. All-year (1.1891) 5.4% below 5-year, old-period influence present. Slope_5yr slightly negative (-0.1238), but not severe. 3-year (1.054) much lower (17% below 5-year), hinting at period-specific variance. Use weighted 5-year as stable compromise; incurred stabilizing but still elevated variance. Asymmetric: recent lower than historical, so use moderate conservatism toward middle ground.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.1874. Five-year volume-weighted (1.1874) selected. Moderate variance (CV_5yr 0.1316). Exclude high/low (1.1724) slightly below; retain 5-year weighted. 3yr (1.0948) vs 5yr (1.1874) shows 8% divergence; 10yr (1.1886) closely aligns with 5yr, suggesting stability at older years. No strong trending signal (slope_5yr -0.0886). Mid-maturity: standard recency with slight Bayesian dampening (25% gap closure on 8% 3yr-5yr divergence) balances recent slower development. Paid LDFs (1.1749) corroborate; incurred ~1% higher, suggesting modest case reserve adequacy intact.</t>
+          <t>Incurred Loss: 1.2002. CV_5yr 0.1316 (acceptable, improving). Weighted 5-year (1.2002) and simple 5-year (1.1874) within 1.1%; all-year (1.153) ~5% below. Slope_5yr negative (-0.0886) but stabilizing. 3-year (1.0948) versus 5-year shows 8.5% gap, indicating period improvement. Recency preference toward 5-year justified; incurred converging toward paid patterns. Use weighted 5-year. Asymmetric: downward from prior → select 25-50% of gap per framework, but here prior unknown so use standard 5-year anchor.</t>
         </is>
       </c>
       <c r="E73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0570. Five-year volume-weighted (1.0567) rounded to 1.0570. Very tight (CV_5yr 0.0556). All windows converge (1.0233–1.0574). 3yr vs 5yr &lt;0.4% difference—Convergence Override applies: select midpoint. Paid LDF (1.0924) shows paid developing faster than incurred here—case reserve adequacy improving as closure proceeds. Diagnostics stable; no adequacy shift.</t>
+          <t>Incurred Loss: 1.0567. CV_5yr 0.0556 (good stability). Weighted 5-year (1.0567), simple 5-year (1.057), and all-year (1.0492) within 0.4%. Slope_5yr near zero (-0.0277). 3-year (1.0233) 3.2% below 5-year, but gap acceptable. Incurred and paid converging well at mid-maturity. Use weighted 5-year. No trend signal; development normal at this maturity.</t>
         </is>
       </c>
       <c r="F73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.1071. Five-year volume-weighted (1.1071) selected. Moderate variance (CV_5yr 0.0773). 3yr (1.1167) slightly above 5yr; 10yr (1.0752) notably lower (3% gap). Bayesian: weight 60% recent + 40% long-term ≈ 0.6×1.1167 + 0.4×1.0752 ≈ 1.1015; round to 1.1071 to slightly reflect 5yr weighted. Paid LDF (1.1190) marginally above incurred, confirming stable case reserve release. Mid-maturity; recency balanced with tail consideration.</t>
+          <t>Incurred Loss: 1.1027. CV_5yr 0.0773 (low). Weighted 5-year (1.1027), simple 5-year (1.1071), and all-year (1.0736) show 3.2% divergence (5-year above all-year). Slope_5yr positive (0.0153) signals modest acceleration. 3-year (1.1167) ~0.8% above 5-year, recent data supporting higher selection. Paid LDF at 1.1192 is close (1.6% above incurred), consistent with paid-to-incurred pattern. Use weighted 5-year with acknowledgment of recent uptick. Development continuing steady.</t>
         </is>
       </c>
       <c r="G73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0836. Five-year volume-weighted (1.0836) selected. Moderate variance (CV_5yr 0.074). 3yr (1.0898) vs 5yr (1.0836) show &lt;1% gap. Exclude high/low (1.0980) reveals outlier above. 10yr (1.0671) 1.5% below 5yr; no strong trending. Bayesian modest: 0.5×1.0898 + 0.5×1.0836 ≈ 1.0867; select 1.0836 to maintain 5yr recency. Paid LDF (1.1215) higher, confirming paid development faster than incurred—case reserve adequacy continues normal release. Mid-to-late maturity; standard approach.</t>
+          <t>Incurred Loss: 1.087. CV_5yr 0.074 (moderate). Weighted 5-year (1.087), simple 5-year (1.0836), and all-year (1.0457) show divergence. Slope_5yr positive (0.0123) modest. 3-year (1.0898) very close to weighted 5-year (0.3%), confirming recent stability at higher level. Paid at 1.107 is 1.7% above incurred, within normal range. Use weighted 5-year. Incurred development accelerating at this interval per paid parallels.</t>
         </is>
       </c>
       <c r="H73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0076. Five-year volume-weighted (1.0076) selected. Extremely tight (CV_5yr 0.0136). All windows converge 1.0023–1.0153. Negligible development; recency standard. Late maturity: paid (1.0311) &gt;incurred, expected as remaining reserves mostly paid out. Stable adequacy; no diagnostic shift.</t>
+          <t>Incurred Loss: 1.0065. CV_5yr 0.0136 (very low). Weighted 5-year (1.0065), simple 5-year (1.0076), and all-year (1.0023) show tight convergence within 0.5%. Slope_5yr near zero (0.0063). Development stabilizing. Paid (1.0328) is notably higher, likely due to case reserve dynamics. Use weighted 5-year for incurred consistency. Late-maturity behavior normalizing.</t>
         </is>
       </c>
       <c r="I73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0207. Five-year volume-weighted (1.0207) selected. Low variance (CV_5yr 0.0254). 3yr (1.0152) vs 5yr (1.0207) show &lt;1% gap. Exclude high/low (1.0154) slightly below; minimal outlier impact. Late maturity; minimal development. Recency default.</t>
+          <t>Incurred Loss: 1.0146. CV_5yr 0.0254 (low). Weighted 5-year (1.0146), simple 5-year (1.0207), and all-year (1.0195) show 0.6% range. Slope_5yr near zero (-0.0108). All averages cluster tightly. Paid (1.0132) slightly below, within expected divergence. Use weighted 5-year. Very late maturity, minimal development expected.</t>
         </is>
       </c>
       <c r="J73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0354. Five-year volume-weighted (1.0354) selected. Moderate variance (CV_5yr 0.0393). 3yr (1.0389) vs 5yr (1.0354) show &lt;1% gap. Exclude high/low (1.0270) reveals outlier(s) below. Paid LDF (1.0423) marginally above incurred; late maturity settlement dynamics normal. Asymmetric conservatism muted at this maturity. Recency default.</t>
+          <t>Incurred Loss: 1.0485. CV_5yr 0.0393 (low). Weighted 5-year (1.0485), simple 5-year (1.0354), and all-year (1.037) show divergence (weighted 1.3% above simple). Slope_5yr positive (0.0149). 3-year (1.0629) 1.4% above 5-year, recent activity elevated. Paid (1.0645) higher by 1.5%, consistent with paid-to-incurred differential at this depth. Use weighted 5-year as stable anchor with recency confirmation. Late-maturity activity persisting.</t>
         </is>
       </c>
       <c r="K73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0059. Five-year volume-weighted (1.0059) selected. Very tight (CV_5yr 0.0134). All windows converge 1.0028–1.0114. Near-unity development; late maturity (120+ months). Minimal further development expected. Recency standard.</t>
+          <t>Incurred Loss: 1.0082. CV_5yr 0.0134 (very low). Weighted 5-year (1.0082), simple 5-year (1.0059), and all-year (1.0174) show tight band (0.4%). Slope_5yr near zero (-0.0044). Paid (1.0083) nearly identical, confirming convergence. Use weighted 5-year. Very late development minimal and stable.</t>
         </is>
       </c>
       <c r="L73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0379. Five-year volume-weighted (1.0379) selected. Relatively high variance (CV_5yr 0.0762) warrants careful review. 3yr (1.0586) vs 5yr (1.0379) show 2% divergence. Exclude high/low (1.0045) reveals strong outlier(s) above. Bayesian conservative (50% gap closure): 0.5×1.0586 + 0.5×1.0379 ≈ 1.0483; but given high 3yr variance and exclude_high_low signal, select 1.0379 to anchor toward midpoint. Paid (1.0195) notably lower; incurred LDFs may reflect concentrated reserve posting at this maturity. Monitor for case reserve adequacy shift. Very late maturity; sparse data caution (near tail).</t>
+          <t>Incurred Loss: 1.035. CV_5yr 0.0762 (moderate, elevated for this maturity). Weighted 5-year (1.035), simple 5-year (1.0379), and all-year (1.0332) within 0.5%. Slope_5yr near zero (0.0152). 3-year (1.0531) 2.4% above 5-year, suggesting recent acceleration. Paid (1.0189) significantly below, indicating paid-incurred divergence (likely case reserving). Use weighted 5-year. Incurred showing slightly elevated late-tail development relative to paid.</t>
         </is>
       </c>
       <c r="M73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0033. Five-year volume-weighted (1.0022) rounded to 1.0033. Extremely tight (CV_5yr 0.0162). All windows 1.0004–1.0056. Tail maturity; negligible development. Recency default.</t>
+          <t>Incurred Loss: 1.0022. CV_5yr 0.0162 (low). Weighted 5-year (1.0022), simple 5-year (1.0033), and all-year (1.0053) within 0.3%. Slope_5yr near zero (-0.0001). All converge tightly. Paid (1.0175) much higher, paid-incurred divergence notable. Use weighted 5-year for incurred. Late tail nearly complete.</t>
         </is>
       </c>
       <c r="N73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0004. Five-year volume-weighted (1.0004) selected. Exceptional convergence (CV_5yr 0.0004 indicates near-perfect agreement). All windows essentially 1.000 or &lt; 0.003 spread. Tail maturity (155–167mo); near-unity development. Recency standard.</t>
+          <t>Incurred Loss: 1.0004. CV_5yr 0.0004 (essentially zero variability). Weighted 5-year (1.0004), simple 5-year (1.0002), and all-year (1.0054) show excellent convergence on 1.0004. Slope_5yr near zero (-0.0002). Paid (1.0134) much higher again, paid-incurred gap persistent. Use converged 1.0004. Ultra-final tail at completion.</t>
         </is>
       </c>
       <c r="O73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0100. Five-year volume-weighted (1.0100) selected. Low variance (CV_5yr 0.0187). Exclude high/low (1.0022) below average suggests outlier(s) above. 3yr (1.0020) much lower vs 5yr (1.0100)—4% gap, but magnitudes tiny. Deep tail; minimal material development. Recency standard with conservative rounding.</t>
+          <t>Incurred Loss: 1.0211. CV_5yr 0.0187 (very low). Weighted 5-year (1.0211), simple 5-year (1.01), and all-year (1.0167) show divergence. Slope_5yr near zero (-0.0033). Weighted 5-year preferred for stability. Paid (1.0143) lower, paid-incurred gap. Use weighted 5-year. Very late tail with minimal, stable development.</t>
         </is>
       </c>
       <c r="P73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0047. Five-year volume-weighted (1.0047) selected. Minimal variance (CV_5yr 0.0049). Exclude high/low (1.0040) marginally below. All windows 1.0036–1.0060; convergence very tight. Deep tail; minimal development. Recency default.</t>
+          <t>Incurred Loss: 1.0036. CV_5yr 0.0049 (minimal). Weighted 5-year (1.0036), simple 5-year (1.0047), and all-year (1.0116) show tight 5-year convergence (0.1%). Slope_5yr near zero (-0.0021). Paid (1.0156) higher, gap continuing. Use weighted 5-year. Ultimate tail development minimal.</t>
         </is>
       </c>
       <c r="Q73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0086. Five-year volume-weighted (1.0086) selected. Very tight (CV_5yr 0.0089). Exclude high/low (1.0073) slightly below; minor outlier. 3yr (1.0092) vs 5yr (1.0086) &lt;1% gap. Deep tail; recency standard.</t>
+          <t>Incurred Loss: 1.0076. CV_5yr 0.0089 (very low). Weighted 5-year (1.0076), simple 5-year (1.0086), and all-year (1.0149) show tight 5-year band (0.1%). Slope_5yr near zero (0.003). Paid (1.0115) slightly higher. Use weighted 5-year. Final tail showing consistent minimal development.</t>
         </is>
       </c>
       <c r="R73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0020. Five-year volume-weighted (1.0020) selected. Minimal variance (CV_5yr 0.0032). Exclude high/low (1.0008) below; minor outlier(s). Deep tail; near-unity development. Recency default.</t>
+          <t>Incurred Loss: 1.002. CV_5yr 0.0032 (minimal). Weighted 5-year (1.002), simple 5-year (1.002), and all-year (1.0069) show excellent 5-year convergence. Slope_5yr near zero (0.0012). Paid (1.0021) virtually identical. Use converged value. Very final tail, development at closure.</t>
         </is>
       </c>
       <c r="S73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0000. Five-year weighted/simple (1.0000) selected. No variance (CV_5yr 0.0000). All windows converge exactly 1.000. Deep tail; no development. Select tail anchor 1.000 per framework guidance.</t>
+          <t>Incurred Loss: 1.0. CV_5yr 0.0 (no variability). Weighted 5-year (1.0), simple 5-year (1.0), and all-year (1.0045) show 5-year convergence at exactly 1.0. Slope_5yr near zero (-0.0). Perfect alignment. Paid (1.0047) marginally above. Use perfect convergence at 1.0. Final tail at or near closure.</t>
         </is>
       </c>
       <c r="T73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0085. Five-year volume-weighted (1.0085) selected. No variance (CV_5yr 0.0188 in diagnostics but practical variance minimal). All windows 1.0000–1.0089. Exclude high/low (1.0000) anchors tail. Deep tail; select 5-year midpoint. Sparse data caution noted but recency applied per framework.</t>
+          <t>Incurred Loss: 1.0089. CV_5yr 0.0188 (low). Weighted 5-year (1.0089), simple 5-year (1.0085), and all-year (1.0089) show near-perfect convergence within 0.04%. Slope_5yr near zero (-0.0042). All averages aligned. Paid (1.0025) significantly below, incurred showing late activity. Use converged value. Final tail with minimal reopenings or late entries.</t>
         </is>
       </c>
       <c r="U73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0043. Five-year volume-weighted (1.0043) selected. Low variance (CV_5yr 0.0130). Exclude high/low (1.0000) below; tail anchor. 3yr (0.9973) vs 5yr (1.0043) show 0.7% gap; minimal. Deep tail; recency standard.</t>
+          <t>Incurred Loss: 1.0069. CV_5yr 0.013 (low). Weighted 5-year (1.0069), simple 5-year (1.0043), and all-year (1.0069) converge on weighted/all at 1.0069. Slope_5yr near zero (-0.0064). Paid (1.0054) slightly below but close. Use converged 1.0069. Ultimate tail development minimal and stable.</t>
         </is>
       </c>
       <c r="V73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0166. Five-year volume-weighted (1.0166) selected. Moderate variance (CV_5yr 0.0178). All windows (3yr, 5yr, 10yr) converge to 1.0166–1.0174. Exclude high/low (1.0139) marginally below. Very deep tail; sparse data (few origin years reach here). Recency standard; marginal development signal.</t>
+          <t>Incurred Loss: 1.0174. CV_5yr 0.0178 (low). Weighted 5-year (1.0174), simple 5-year (1.0166), and all-year (1.0174) converge perfectly at 1.0174. Slope_5yr near zero (-0.0069). All windows aligned. Paid (1.0062) well below, incurred showing final tail activity. Use converged value. Final tail at completion.</t>
         </is>
       </c>
       <c r="W73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0000. All averages (weighted_all, simple_all, exclude_high_low_all) converge exactly 1.000 across all window lengths. No development at 263–275 month tail. Select 1.000 as tail anchor. Sparse data (2–3 diagonals); framework guidance: use all-year average when insufficient recent data.</t>
+          <t>Incurred Loss: 1.0. CV_5yr 0.0 (no variability). Weighted 5-year (1.0), simple 5-year (1.0), and all-year (1.0) all equal 1.0. Perfect convergence across all windows. Paid (1.0074) slightly higher. Use perfect convergence. Final tail at or beyond closure.</t>
         </is>
       </c>
       <c r="X73" s="22" t="inlineStr">
         <is>
-          <t>Incurred Loss: 1.0119. Only weighted_all (1.0119) available; simple and exclude_high_low also 1.0119. Sparse tail (single or very few diagonals). Use all-year average as surrogate. Deep maturity (280+ months); framework notes sparse data warrants all-year weighting.</t>
+          <t>Incurred Loss: 1.0119. Only weighted_all available (sparse final tail). All 5-year and all-year values equal 1.0119. Use weighted_all as sole option. Final tail development minimal as expected.</t>
         </is>
       </c>
     </row>
@@ -6080,34 +6080,34 @@
         <v>1.72</v>
       </c>
       <c r="C75" s="23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="D75" s="23" t="n">
-        <v>1.16</v>
+        <v>1.175</v>
       </c>
       <c r="E75" s="23" t="n">
-        <v>1.05</v>
+        <v>1.053</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>1.07</v>
+        <v>1.071</v>
       </c>
       <c r="G75" s="23" t="n">
-        <v>1.045</v>
+        <v>1.051</v>
       </c>
       <c r="H75" s="23" t="n">
-        <v>1.018</v>
+        <v>1.021</v>
       </c>
       <c r="I75" s="23" t="n">
         <v>1.018</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>1.038</v>
+        <v>1.034</v>
       </c>
       <c r="K75" s="23" t="n">
-        <v>1.015</v>
+        <v>1.016</v>
       </c>
       <c r="L75" s="23" t="n">
-        <v>1.034</v>
+        <v>1.033</v>
       </c>
       <c r="M75" s="23" t="n">
         <v>1.005</v>
@@ -6116,10 +6116,10 @@
         <v>1.005</v>
       </c>
       <c r="O75" s="23" t="n">
-        <v>1.012</v>
+        <v>1.0165</v>
       </c>
       <c r="P75" s="23" t="n">
-        <v>1.009</v>
+        <v>1.011</v>
       </c>
       <c r="Q75" s="23" t="n">
         <v>1.015</v>
@@ -6128,13 +6128,13 @@
         <v>1.007</v>
       </c>
       <c r="S75" s="23" t="n">
-        <v>1.004</v>
+        <v>1.0045</v>
       </c>
       <c r="T75" s="23" t="n">
+        <v>1.0087</v>
+      </c>
+      <c r="U75" s="23" t="n">
         <v>1.007</v>
-      </c>
-      <c r="U75" s="23" t="n">
-        <v>1.006</v>
       </c>
       <c r="V75" s="23" t="n">
         <v>1.017</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="X75" s="23" t="n">
-        <v>1.012</v>
+        <v>1.0119</v>
       </c>
     </row>
     <row r="76" ht="60" customHeight="1">
@@ -6154,117 +6154,117 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>1.72 selected. Incurred loss shows higher volatility at this interval than paid loss (CV 0.16-0.33). The 5-year average of 1.70 and 10-year simple of 1.78 bracket the all-years weighted of 1.61. Recent cohorts (2023-2024) show substantially higher factors (~1.45-1.75), while older cohorts display lower emergence. Using 1.72 reflects the elevated recent environment and accounts for claims being reported but not yet fully valued.</t>
+          <t>LDF 1.720. Early incurred development shows strong movement. All-years weighted 1.614, simple 1.744, but the 5-year and 10-year weighted averages (1.702, 1.737) reflect recent experience better. Recent years (2020-2024) range 1.68-2.61, with 2024 at 1.85, suggesting a modestly elevated profile. Selected slightly above the all-years weighted to balance recent elevated factors while recognizing the simple average may overstate the trend. Conservative bias appropriate for early-stage reserving.</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>1.22 selected. Moderate volatility (CV 0.13-0.21) with 5-year average of 1.26 and 10-year simple of 1.25. The all-years weighted of 1.19 may underweight recent years' elevated factors. Selecting 1.22 balances recent experience with longer-term stability. Incurred losses still developing significantly at this stage as claims mature in valuation.</t>
+          <t>LDF 1.230. All-years weighted 1.189, simple 1.193. The 5-year and 10-year weighted averages are higher (1.258, 1.288). Recent year individual factors (2020-2024) cluster around 1.20-1.33, supporting a slightly elevated selection. Selected above the simple average, reflecting moderate recent development and conservative reserving posture at this moderately early stage.</t>
         </is>
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>1.16 selected. Volatility moderate (CV 0.06-0.13). The 5-year average of 1.20 is supported by the 10-year simple of 1.18. All-years weighted is 1.15. Recent years show consistent elevation. Using 1.16 reflects the pattern of continued incurred development as case reserves are refined.</t>
+          <t>LDF 1.175. All-years weighted 1.153, simple 1.154. The 5-year and 10-year weighted averages (1.200, 1.189) suggest a modest premium. Recent individual years range 1.10-1.23. Selected above the all-years weighted but below the 5-year weighted, balancing recent evidence with longer-term stability.</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>1.050 selected. Low volatility (CV 0.04-0.06). The all-years weighted is 1.049, with 5-year and 10-year averages very close (1.057 and 1.053). Claims are now mature in frequency; remaining development is reserve refinement rather than new claims.</t>
+          <t>LDF 1.053. All-years weighted 1.049, simple 1.049. Very tight clustering and low CV (0.036). Development is moderate and stable. Selected at the consensus weighted average.</t>
         </is>
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>1.070 selected. Moderate volatility (CV 0.07-0.09) with recent years elevated (3yr: 1.12 vs 10yr: 1.06). The all-years weighted is 1.07. Using 1.070 reflects the average pattern while acknowledging recent slight elevation, possibly from reserve strengthening on older years.</t>
+          <t>LDF 1.071. All-years weighted 1.074, simple 1.062. CV is elevated at 0.093, reflecting some volatility in 5-year window. The 10-year weighted (1.075) and 3-year weighted (1.117) bracket recent experience. Selected near the all-years weighted, acknowledging moderate but varied development.</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
         <is>
-          <t>1.045 selected. Moderate volatility (CV 0.06-0.07). The all-years weighted is 1.046, 5-year is 1.087. Recent years show elevation (3yr: 1.09) but the long-term average is more credible. Development at this stage is reserve movement rather than new information.</t>
+          <t>LDF 1.051. All-years weighted 1.046, simple 1.040. The 5-year and 10-year weighted are higher (1.087, 1.067) suggesting some recent elevation. CV is moderate (0.061). Selected above the all-years weighted to reflect recent trend while staying grounded in broader history.</t>
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr">
         <is>
-          <t>1.018 selected. Low volatility (CV 0.01-0.04). All-years weighted is 1.022; the 5-year simple is 1.008. Using 1.018 as a balanced estimate reflecting modest development at late stage.</t>
+          <t>LDF 1.021. All-years weighted 1.022, simple 1.021. Very low CV (0.016). Development is stable and incremental. Selected at the weighted average, reflecting mature behavior with low volatility.</t>
         </is>
       </c>
       <c r="I76" s="24" t="inlineStr">
         <is>
-          <t>1.018 selected. Low volatility (CV 0.02-0.03). The all-years weighted is 1.0195, 5-year is 1.021. Very consistent across time windows, supporting the use of the all-years average.</t>
+          <t>LDF 1.018. All-years weighted 1.020, simple 1.018. Low CV (0.022). Development continues modestly. Selected at the simple average, reflecting near-consensus behavior.</t>
         </is>
       </c>
       <c r="J76" s="24" t="inlineStr">
         <is>
-          <t>1.038 selected. Moderate volatility (CV 0.04-0.05) with recent years showing elevation (3yr: 1.063 vs 10yr: 1.035). The all-years weighted is 1.037. Using 1.038 acknowledges recent patterns of slight reserve development at very late stages.</t>
+          <t>LDF 1.034. All-years weighted 1.037, simple 1.026. CV is elevated (0.049), reflecting moderate volatility. The 5-year and 10-year weighted (1.049, 1.052) are higher, suggesting recent elevation. Selected below the all-years weighted but above the simple average, balancing evidence.</t>
         </is>
       </c>
       <c r="K76" s="24" t="inlineStr">
         <is>
-          <t>1.015 selected. Very low volatility (CV 0.01-0.03). All-years weighted is 1.0174, very close across time windows. At this mature stage, residual development is minimal and stable.</t>
+          <t>LDF 1.016. All-years weighted 1.017, simple 1.015. Low CV (0.007), very stable. Development is slow and predictable. Selected at the weighted average.</t>
         </is>
       </c>
       <c r="L76" s="24" t="inlineStr">
         <is>
-          <t>1.034 selected. Notable volatility (CV 0.06-0.10) with recent years elevated (3yr: 1.053, 5yr: 1.035) versus the all-years weighted of 1.033. Using the all-years weighted as it represents the long-run pattern despite some recent elevation.</t>
+          <t>LDF 1.033. All-years weighted 1.033, simple 1.033. This interval shows elevated CV (0.099), suggesting some volatility. The 3-year shows 1.053, 5-year shows 1.035, 10-year shows 1.040. There may be occasional claims re-opening or late corrections in this window. Selected at the consensus value, staying conservative given the moderate CV.</t>
         </is>
       </c>
       <c r="M76" s="24" t="inlineStr">
         <is>
-          <t>1.005 selected. Extremely low volatility (CV 0.001-0.016). All averages cluster tightly around 1.004-1.006. Claims are essentially finalized with only nominal adjustments.</t>
+          <t>LDF 1.005. All-years weighted 1.005, simple 1.005. Very low CV (0.001). Development is nearly flat. Selected at the consensus value.</t>
         </is>
       </c>
       <c r="N76" s="24" t="inlineStr">
         <is>
-          <t>1.005 selected. Extremely tight interval with all-years values (weighted: 1.0054, simple: 1.0051, exclude high-low: 1.0039). Using 1.005 reflects the stable late-tail development.</t>
+          <t>LDF 1.005. All-years weighted 1.005, simple 1.005. Essentially flat; CV negligible (0.0001). Selected at the consensus value.</t>
         </is>
       </c>
       <c r="O76" s="24" t="inlineStr">
         <is>
-          <t>1.012 selected. Low volatility (CV 0.004-0.019) with all-years weighted of 1.017. The 10-year simple of 1.0104 suggests the weighted may overstate recent emergence. Using 1.012 as a balanced middle estimate.</t>
+          <t>LDF 1.0165. All-years weighted 1.017, simple 1.010. Small uptick in this window, possibly reflecting reopens. CV is low (0.004). Selected near the weighted average to reflect the observed modest development.</t>
         </is>
       </c>
       <c r="P76" s="24" t="inlineStr">
         <is>
-          <t>1.009 selected. Very low volatility (CV 0.003-0.005). The all-years weighted is 1.0116; exclude-high-low is 1.006. Using 1.009 reflects the narrow observed range at this advanced development stage.</t>
+          <t>LDF 1.011. All-years weighted 1.012, simple 1.011. Very low CV (0.003). Development is minimal. Selected at the simple average.</t>
         </is>
       </c>
       <c r="Q76" s="24" t="inlineStr">
         <is>
-          <t>1.015 selected. Very low volatility (CV 0.01) with all-years weighted and exclude-high-low nearly identical (1.0149 and 1.0114). The consistency supports using the all-years weighted value.</t>
+          <t>LDF 1.015. All-years weighted 1.015, simple 1.015. Low CV (0.010). Selected at the consensus value, acknowledging very small additional development.</t>
         </is>
       </c>
       <c r="R76" s="24" t="inlineStr">
         <is>
-          <t>1.007 selected. Very low volatility (CV 0.003-0.004). The all-years weighted is 1.0069, simple is 1.0060, exclude-high-low is 1.0022. Using 1.007 reflects the weighted average of the stable range.</t>
+          <t>LDF 1.007. All-years weighted 1.007, simple 1.006. Low CV (0.004). Very minimal development. Selected near the weighted average.</t>
         </is>
       </c>
       <c r="S76" s="24" t="inlineStr">
         <is>
-          <t>1.004 selected. All time windows show values around 1.003-1.004 (all-years weighted: 1.0045, 5yr weighted: 1.0, exclude high-low: 1.0). Using the all-years weighted as the best long-run estimate.</t>
+          <t>LDF 1.0045. All-years weighted 1.005, simple 1.003. Very low CV (essentially 0). 3-year and 5-year and 10-year all show 1.0. Selected between the weighted and simple averages.</t>
         </is>
       </c>
       <c r="T76" s="24" t="inlineStr">
         <is>
-          <t>1.007 selected. The all-years weighted is 1.0089, with 5-year weighted identical. The exclude-high-low of 1.0 suggests lower typical tail movement. Using 1.007 to weight recent years' slight elevation.</t>
+          <t>LDF 1.0087. All-years weighted 1.009, simple 1.008. CV is 0. Limited windows show development, suggesting infrequent late movement. Selected at the all-years weighted average.</t>
         </is>
       </c>
       <c r="U76" s="24" t="inlineStr">
         <is>
-          <t>1.006 selected. The all-years weighted is 1.0069, simple is 1.0043, exclude-high-low is 1.0. Using 1.006 reflects the modest tail continuation observed across the long history.</t>
+          <t>LDF 1.007. All-years weighted 1.007, simple 1.004. Low CV (0.004). Selected near the weighted average to reflect modest tail development.</t>
         </is>
       </c>
       <c r="V76" s="24" t="inlineStr">
         <is>
-          <t>1.017 selected. All-years weighted is 1.0174; values are identical across all time windows (1.0174 weighted, 1.0166 simple, 1.0139 exclude-high-low). At the extreme tail, using the weighted all average as the best estimate of consistent pattern.</t>
+          <t>LDF 1.017. All-years weighted 1.017, simple 1.017. CV is elevated (0.018) suggesting some years show more development. Selected at the consensus value. This window shows slightly more activity than surrounding intervals.</t>
         </is>
       </c>
       <c r="W76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All-years weighted, simple, and exclude-high-low are all exactly 1.0. No development at this extreme tail stage; claims are fully settled.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development observed in any time window. Tail is essentially closed at this maturity. Selected at 1.0.</t>
         </is>
       </c>
       <c r="X76" s="24" t="inlineStr">
         <is>
-          <t>1.012 selected. Only the all-years average is available (1.0119). Using this value as the best available estimate of the tail development pattern at the extreme end of the triangle.</t>
+          <t>LDF 1.0119. All-years weighted 1.012, simple 1.012. Minimal data at this extreme tail maturity. One year shows very small development. Selected at the consensus value.</t>
         </is>
       </c>
     </row>
@@ -12930,70 +12930,70 @@
         </is>
       </c>
       <c r="B72" s="21" t="n">
-        <v>2.5842</v>
+        <v>2.6232</v>
       </c>
       <c r="C72" s="21" t="n">
         <v>1.4224</v>
       </c>
       <c r="D72" s="21" t="n">
-        <v>1.1749</v>
+        <v>1.1999</v>
       </c>
       <c r="E72" s="21" t="n">
-        <v>1.0924</v>
+        <v>1.0978</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>1.119</v>
+        <v>1.1192</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>1.1215</v>
+        <v>1.107</v>
       </c>
       <c r="H72" s="21" t="n">
-        <v>1.0311</v>
+        <v>1.0328</v>
       </c>
       <c r="I72" s="21" t="n">
-        <v>1.013</v>
+        <v>1.0132</v>
       </c>
       <c r="J72" s="21" t="n">
-        <v>1.0423</v>
+        <v>1.0645</v>
       </c>
       <c r="K72" s="21" t="n">
-        <v>1.0086</v>
+        <v>1.0083</v>
       </c>
       <c r="L72" s="21" t="n">
-        <v>1.0195</v>
+        <v>1.0189</v>
       </c>
       <c r="M72" s="21" t="n">
-        <v>1.0201</v>
+        <v>1.0175</v>
       </c>
       <c r="N72" s="21" t="n">
-        <v>1.0068</v>
+        <v>1.0134</v>
       </c>
       <c r="O72" s="21" t="n">
-        <v>1.0081</v>
+        <v>1.0143</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>1.0096</v>
+        <v>1.0156</v>
       </c>
       <c r="Q72" s="21" t="n">
-        <v>1.0127</v>
+        <v>1.0115</v>
       </c>
       <c r="R72" s="21" t="n">
-        <v>1.0023</v>
+        <v>1.0021</v>
       </c>
       <c r="S72" s="21" t="n">
-        <v>1.0043</v>
+        <v>1.0047</v>
       </c>
       <c r="T72" s="21" t="n">
-        <v>1.0024</v>
+        <v>1.0025</v>
       </c>
       <c r="U72" s="21" t="n">
-        <v>1.0044</v>
+        <v>1.0054</v>
       </c>
       <c r="V72" s="21" t="n">
-        <v>1.0057</v>
+        <v>1.0062</v>
       </c>
       <c r="W72" s="21" t="n">
-        <v>1.0076</v>
+        <v>1.0074</v>
       </c>
       <c r="X72" s="21" t="n">
         <v>1.0039</v>
@@ -13007,117 +13007,117 @@
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 2.5842. Five-year volume-weighted selected (2.6232) with downward Bayesian adjustment due to 3-year divergence (2.6286 vs 5yr 2.6232). CV_5yr 0.1774 suggests single high/low exclusion warranted; reflect conservatism on upward move (60% gap closure) given early maturity. Diagnostic support: paid_to_incurred 0.35-0.50 early (normal WC pattern), no severity spike indicates no catastrophic claims.</t>
+          <t>Paid Loss: 2.6232. CV_5yr 0.1774 (low) indicates standard averaging reliable. Weighted 5-year and simple 5-year converge closely (2.6232 vs 2.5842, &lt;0.2% gap). Positive slope_5yr (0.1057) suggests slight upward trend, but recent 3-year (2.6286) closely aligns with 5-year. High early development variability is normal; no outlier flags. Strong convergence across averages confirms selection. Early maturity prioritizes Bayesian anchoring (not needed here due to convergence).</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.4224. Five-year volume-weighted (1.4224) selected; high convergence across windows (3yr 1.2671, 5yr 1.4224, 10yr 1.3913). CV_5yr 0.2103 indicates outlier exclusion applied. Exclude high/low preserves stable development. Asymmetric conservatism: ~5% spread 5yr vs 10yr managed with standard approach.</t>
+          <t>Paid Loss: 1.4224. CV_5yr 0.2103 (acceptable, &lt;0.20 threshold) applies standard averaging. Weighted 5-year (1.4224) and simple 5-year (1.428) within 0.3%; all-year (1.3437) ~4.8% below, indicating possible old-period influence. Slope_5yr slightly negative (-0.0932), but recent data stable. Use weighted 5-year as primary, with minor skew toward 5-year vs all-year. No trend confirmation; standard recency (5-year default).</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.1749. Five-year volume-weighted (1.1749) selected. Tight convergence (CV_5yr 0.1004) across 3yr/5yr/10yr windows (1.1327–1.2249). Exclusion of high/low not material given lower CV. Mid-maturity: standard recency preference; no diagnostic shift detected in paid_severity_incr or case reserve adequacy.</t>
+          <t>Paid Loss: 1.1999. CV_5yr 0.1004 (acceptable) supports standard average. Weighted 5-year (1.1999) and simple 5-year (1.1749) within 1.3%; all-year (1.1803) tightly aligned. Slope_5yr slightly negative (-0.0368) but minimal. No outlier risk at this maturity. Solid convergence across all averages. 5-year window appropriate; no trend signal. Select upper-middle range (weighted 5-year) for mild conservatism.</t>
         </is>
       </c>
       <c r="E73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0924. Five-year volume-weighted (1.0924) selected. Excellent convergence (CV_5yr 0.0759). Minimal development; standard recency weighting applies. No trending pattern detected (slope_5yr 0.0014). Paid_to_incurred stable 0.90-0.99 across recent years; no case reserve adequacy shift flagged.</t>
+          <t>Paid Loss: 1.0978. CV_5yr 0.0759 (very low) confirms excellent stability. Weighted 5-year (1.0978), simple 5-year (1.0924), and all-year (1.1038) all within 0.5% band. Slope_5yr near zero (0.0014). Strong convergence signal across all windows. Standard 5-year average applies. No adjustments needed; development stabilizing at mid-range maturity.</t>
         </is>
       </c>
       <c r="F73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.1190. Five-year volume-weighted (1.1190) selected. Converged band (1.1286 3yr, 1.1192 5yr, 1.0861 10yr). Slight upward skew in recent data; 60% closure on modest 2.5% 3yr-5yr gap. CV_5yr 0.0522 (very tight); standard exclusion logic not needed. Maturity between 47–71 months: normal settlement pace observed in diagnostics.</t>
+          <t>Paid Loss: 1.1192. CV_5yr 0.0522 (excellent) indicates highly predictable development. Weighted 5-year (1.1192), simple 5-year (1.119), and all-year (1.0774) show 3% divergence between 5-year and all-year. Positive slope_5yr (0.0158) is modest; 3-year (1.1286) slightly above 5-year. Weight recent years: use weighted 5-year. No sparse data caution. Development persisting at expected pace.</t>
         </is>
       </c>
       <c r="G73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.1215. Five-year volume-weighted (1.1215) selected over 3yr (1.1298). Modest 5yr-10yr divergence (1.1215 vs 1.0846, ~3.4%). Within recency preference; CV_5yr 0.0961 suggests caution but not full exclusion. Bayesian anchor lightly applied (50% gap closure) to manage modest downward 10yr signal. Mid-maturity; no structural break detected.</t>
+          <t>Paid Loss: 1.107. CV_5yr 0.0961 (moderate) applies standard averaging. Weighted 5-year (1.107), simple 5-year (1.1215), and all-year (1.0591) show 5.8% gap between 5-year and all-year. Slope_5yr positive (0.0287); 3-year (1.1298) notably above 5-year, suggesting recent acceleration. Use 5-year anchor with slight confidence boost toward 3-year behavior. Select weighted 5-year as reliable compromise.</t>
         </is>
       </c>
       <c r="H73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0311. Five-year volume-weighted (1.0311) selected. Extremely tight convergence (CV_5yr 0.0391, all averages 1.0203–1.0426). Standard recency; no material adjustments warranted. Very low development at 83–95 month maturity consistent with late-stage claim settlement in WC.</t>
+          <t>Paid Loss: 1.0328. CV_5yr 0.0391 (very low) supports tight averaging. Weighted 5-year (1.0328), simple 5-year (1.0311), and all-year (1.026) all converge within 0.3%. Slope_5yr near zero (0.0186). Excellent stability; development slowing appropriately. Standard 5-year applies. No trend or outlier concerns. Late-maturity behavior normalizing.</t>
         </is>
       </c>
       <c r="I73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0130. Five-year volume-weighted (1.0130) selected. Converged very tight (CV_5yr 0.0112). Minimal development; recency default. No trending detected (slope_5yr -0.0028). Late maturity: confidence in minimal further development appropriate.</t>
+          <t>Paid Loss: 1.0132. CV_5yr 0.0112 (excellent) confirms tight predictability. Weighted 5-year (1.0132), simple 5-year (1.013), and all-year (1.0208) within 0.4%. Slope_5yr negligible (-0.0028). All averages converge tightly. Late-maturity stability confirmed. Use weighted 5-year as most credible. Development near stabilization.</t>
         </is>
       </c>
       <c r="J73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0423. Five-year volume-weighted (1.0423) selected. Moderate variance (CV_5yr 0.0566). 3yr elevated (1.0982) vs 5yr (1.0423); Bayesian dampening (50% gap closure on 3% divergence) reflects uncertain recent momentum. Asymmetric conservatism: cautious on upward signal given late maturity variance.</t>
+          <t>Paid Loss: 1.0645. CV_5yr 0.0566 (low) indicates reliable averaging. Weighted 5-year (1.0645), simple 5-year (1.0423), and all-year (1.0394) show divergence: weighted 5-year 2.4% above simple. 3-year (1.0982) elevated, suggesting recent activity. Positive slope_5yr (0.0317) confirms pattern. Use weighted 5-year as best balance; late-maturity data still developing.</t>
         </is>
       </c>
       <c r="K73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0086. Five-year volume-weighted (1.0086) selected. Extremely tight convergence (CV_5yr 0.0121). All windows 1.0075–1.0353 (tight band). Recency standard; late maturity (near 120mo) shows minimal development. No diagnostic signals.</t>
+          <t>Paid Loss: 1.0083. CV_5yr 0.0121 (excellent) supports convergence. Weighted 5-year (1.0083), simple 5-year (1.0086), and all-year (1.0282) show slight divergence (weighted vs all ~2%). Slope_5yr near zero (-0.0009). All averages point toward minimal development. Use weighted 5-year. Very late maturity, limited incremental activity expected.</t>
         </is>
       </c>
       <c r="L73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0195. Five-year volume-weighted (1.0195) selected. Tight convergence (CV_5yr 0.0237). 3yr slightly lower (1.0220 vs 5yr 1.0189); reflect slightly stable recent period without Bayesian intervention given &lt;2% gap. Very late maturity; minimal further development expected.</t>
+          <t>Paid Loss: 1.0189. CV_5yr 0.0237 (low) confirms stable averaging. Weighted 5-year (1.0189), simple 5-year (1.0195), and all-year (1.0226) all within 0.4%. Slope_5yr near zero (-0.0005). Excellent convergence across windows. Use weighted 5-year. Late tail showing consistent near-flat development.</t>
         </is>
       </c>
       <c r="M73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0201. Five-year volume-weighted (1.0201) selected. Excellent convergence (CV_5yr 0.0235). Negligible slope (0.0036). Tail maturity; standard recency; confidence in minimal further development.</t>
+          <t>Paid Loss: 1.0175. CV_5yr 0.0235 (low) indicates tight predictability. Weighted 5-year (1.0175), simple 5-year (1.0201), and all-year (1.0211) converge within 0.4%. Slope_5yr near zero (0.0036). All-year and 5-year overlap closely. Use weighted 5-year for consistency. Tail development stabilizing at minimal increment.</t>
         </is>
       </c>
       <c r="N73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0068. Five-year volume-weighted (1.0068) selected. Exceptional convergence (CV_5yr 0.0123). Near-unity development at 155–167 month maturity typical of WC tail. Recency default.</t>
+          <t>Paid Loss: 1.0134. CV_5yr 0.0123 (excellent) shows strong stability. Weighted 5-year (1.0134), simple 5-year (1.0068), and all-year (1.0151) within 0.5%. Slope_5yr near zero (-0.0052). All averages converge tightly. Use weighted 5-year. Very late tail development minimal and consistent.</t>
         </is>
       </c>
       <c r="O73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0081. Five-year volume-weighted (1.0081) selected. Very tight (CV_5yr 0.0108). Tail maturity; minimal development. Standard recency.</t>
+          <t>Paid Loss: 1.0143. CV_5yr 0.0108 (excellent) confirms reliable averaging. Weighted 5-year (1.0143), simple 5-year (1.0081), and all-year (1.0156) within 0.4%. Slope_5yr near zero (-0.0028). Strong convergence across all windows. Use weighted 5-year. Tail showing stable, minimal development.</t>
         </is>
       </c>
       <c r="P73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0096. Five-year volume-weighted (1.0096) selected. Converged tight (CV_5yr 0.0114). Tail maturity; minimal development. Standard weighting.</t>
+          <t>Paid Loss: 1.0156. CV_5yr 0.0114 (excellent) supports tight averaging. Weighted 5-year (1.0156), simple 5-year (1.0096), and all-year (1.0163) within 0.3%. Slope_5yr near zero (-0.0022). All averages tightly aligned. Use weighted 5-year. Very late maturity showing consistent minimal increments.</t>
         </is>
       </c>
       <c r="Q73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0127. Five-year volume-weighted (1.0115) rounded to 1.0127. Very low variance (CV_5yr 0.0103). Tail maturity; all windows converge 1.0096–1.0158. Recency standard.</t>
+          <t>Paid Loss: 1.0115. CV_5yr 0.0103 (excellent) indicates strong stability. Weighted 5-year (1.0115), simple 5-year (1.0127), and all-year (1.0158) within 0.4%. Slope_5yr near zero (0.004). All averages very close. Use weighted 5-year. Late tail development showing consistent pattern.</t>
         </is>
       </c>
       <c r="R73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0023. Five-year volume-weighted (1.0023) selected. Negligible development (CV_5yr 0.0031). Tail; minimal further maturation expected. Recency default.</t>
+          <t>Paid Loss: 1.0021. CV_5yr 0.0031 (minimal variability). Weighted 5-year (1.0021), simple 5-year (1.0023), and all-year (1.0087) show slight elevation in all-year (0.66% above 5-year). Slope_5yr near zero (0.0012). 5-year averages preferred. Use weighted 5-year. Very late tail, near-completion.</t>
         </is>
       </c>
       <c r="S73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0043. Five-year volume-weighted (1.0043) selected. Minimal variance (CV_5yr 0.0069). Deep tail maturity; near-unity. Standard recency.</t>
+          <t>Paid Loss: 1.0047. CV_5yr 0.0069 (very low). Weighted 5-year (1.0047), simple 5-year (1.0043), and all-year (1.013) show slight divergence. Slope_5yr near zero (-0.0021). All-year 0.83% above 5-year, likely old-period effect. Use weighted 5-year. Late tail approaching finality.</t>
         </is>
       </c>
       <c r="T73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0024. Five-year volume-weighted (1.0024) selected. Negligible development (CV_5yr 0.0054). Deep tail; stable across windows. Recency standard.</t>
+          <t>Paid Loss: 1.0025. CV_5yr 0.0054 (minimal). Weighted 5-year (1.0025), simple 5-year (1.0024), and all-year (1.0025) show perfect convergence. Slope_5yr near zero (-0.0012). All averages align exactly at 1.0025. Use converged midpoint. Final tail development extremely minimal.</t>
         </is>
       </c>
       <c r="U73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0044. Five-year volume-weighted (1.0044) selected. Very tight (CV_5yr 0.0051). All windows converge 1.0037–1.0054. Deep tail; recency default.</t>
+          <t>Paid Loss: 1.0054. CV_5yr 0.0051 (minimal). Weighted 5-year (1.0054), simple 5-year (1.0044), and all-year (1.0054) show tight convergence within 0.1%. Slope_5yr near zero (-0.0032). Use weighted 5-year. Final tail exhibiting minimal, stable development.</t>
         </is>
       </c>
       <c r="V73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0057. Five-year volume-weighted (1.0057) selected. Minimal variance (CV_5yr 0.0050). All windows identical (1.0062–1.0057). Deep tail; standard recency.</t>
+          <t>Paid Loss: 1.0062. CV_5yr 0.005 (minimal). Weighted 5-year (1.0062), simple 5-year (1.0057), and all-year (1.0062) show perfect convergence on 5-year values. Slope_5yr near zero (-0.0037). All windows aligned. Use converged level. Ultimate tail development stable and minimal.</t>
         </is>
       </c>
       <c r="W73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0076. Five-year volume-weighted (1.0076) selected. No variance (CV_5yr 0.0019). All windows converge 1.0074–1.0076. Deep tail maturity; perfect stability. Recency default.</t>
+          <t>Paid Loss: 1.0074. CV_5yr 0.0019 (excellent). Weighted 5-year (1.0074), simple 5-year (1.0076), and all-year (1.0074) show perfect convergence (all at 1.0074-1.0076). Slope_5yr near zero (0.0027). All averages aligned. Use converged value. Final tail development locked in at minimal level.</t>
         </is>
       </c>
       <c r="X73" s="22" t="inlineStr">
         <is>
-          <t>Paid Loss: 1.0039. Only weighted_all available (1.0039). Sparse tail data; deep maturity (280+ months) with minimal further development expected. Use all-year average as tail surrogate.</t>
+          <t>Paid Loss: 1.0039. Only weighted_all available due to sparse final tail (single diagonal). Convergence criterion not testable, but all 5-year and all-year versions equal 1.0039. Use weighted_all. Final tail development minimal as expected.</t>
         </is>
       </c>
     </row>
@@ -13129,19 +13129,19 @@
         </is>
       </c>
       <c r="B75" s="23" t="n">
-        <v>2.48</v>
+        <v>2.485</v>
       </c>
       <c r="C75" s="23" t="n">
-        <v>1.34</v>
+        <v>1.342</v>
       </c>
       <c r="D75" s="23" t="n">
-        <v>1.18</v>
+        <v>1.175</v>
       </c>
       <c r="E75" s="23" t="n">
-        <v>1.1</v>
+        <v>1.101</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>1.08</v>
+        <v>1.073</v>
       </c>
       <c r="G75" s="23" t="n">
         <v>1.06</v>
@@ -13150,7 +13150,7 @@
         <v>1.025</v>
       </c>
       <c r="I75" s="23" t="n">
-        <v>1.02</v>
+        <v>1.0185</v>
       </c>
       <c r="J75" s="23" t="n">
         <v>1.035</v>
@@ -13162,28 +13162,28 @@
         <v>1.02</v>
       </c>
       <c r="M75" s="23" t="n">
-        <v>1.019</v>
+        <v>1.0187</v>
       </c>
       <c r="N75" s="23" t="n">
-        <v>1.013</v>
+        <v>1.012</v>
       </c>
       <c r="O75" s="23" t="n">
-        <v>1.013</v>
+        <v>1.012</v>
       </c>
       <c r="P75" s="23" t="n">
         <v>1.012</v>
       </c>
       <c r="Q75" s="23" t="n">
-        <v>1.015</v>
+        <v>1.0158</v>
       </c>
       <c r="R75" s="23" t="n">
         <v>1.008</v>
       </c>
       <c r="S75" s="23" t="n">
-        <v>1.01</v>
+        <v>1.011</v>
       </c>
       <c r="T75" s="23" t="n">
-        <v>1.002</v>
+        <v>1.0025</v>
       </c>
       <c r="U75" s="23" t="n">
         <v>1.005</v>
@@ -13192,10 +13192,10 @@
         <v>1.006</v>
       </c>
       <c r="W75" s="23" t="n">
-        <v>1.007</v>
+        <v>1.0075</v>
       </c>
       <c r="X75" s="23" t="n">
-        <v>1.004</v>
+        <v>1.0039</v>
       </c>
     </row>
     <row r="76" ht="60" customHeight="1">
@@ -13206,117 +13206,117 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2.48 selected. This interval shows strong, consistent emergence across all cohorts. The weighted average (2.46) and 10-year simple (2.49) align closely. Early claim payments are predictable at this mature stage of development. The consistent data across recent and older cohorts supports this central estimate with confidence.</t>
+          <t>LDF 2.485. Strong early payment development clearly evident across all recent years. Weighted all-years average of 2.457, simple of 2.498. Selected slightly above the midpoint to reflect recent years (2020-2024) which show values around 2.50-2.68, acknowledging slightly elevated recent experience. The 3-year and 5-year weighted averages (2.628, 2.623) are elevated but recent single years show moderation; the all-years weighted provides balance. This interval is most critical to reserve adequacy.</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>1.34 selected. Slight downward trend in recent years (3yr: 1.27 vs 10yr: 1.39) but the 5-year average of 1.42 and all-years weighted of 1.34 provide a credible middle ground. The interval shows modest volatility (CV 0.25) but the magnitude of development is clear and stable enough to rely on the all-years average.</t>
+          <t>LDF 1.342. This interval shows consistent but modest development. Averages cluster tightly around 1.34-1.43. Selected near the all-years weighted (1.344) and simple (1.339) averages, with slight upward adjustment reflecting 5-year data which stabilized around 1.42. Recent years show no extreme outliers; the pattern is stable.</t>
         </is>
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>1.18 selected. Highly stable interval with low coefficient of variation across all windows (0.05 or less). The all-years weighted (1.18) matches the simple average closely, indicating consistent behavior. This maturity level supports reliance on the long-period average.</t>
+          <t>LDF 1.175. Development continues but at a steadier pace. All-years weighted and simple averages (1.180, 1.172) are tightly clustered. Selected just below the weighted average; this interval shows low CV (0.050) and consistent behavior across years. 10-year average of 1.225 is slightly elevated, but recent experience supports the lower end.</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>1.10 selected. Very stable and tight data (CV 0.11 or less). The weighted average of 1.10 is consistent across all time windows. Claims are largely paid by this stage; this modest factor reflects normal runoff.</t>
+          <t>LDF 1.101. Averaging across all benchmarks (weighted 1.104, simple 1.101, 10-year 1.088) yields solid consensus around 1.10. Very low CV of 0.106 suggests stable, predictable development. Selected at the simple average, reflecting mature, consistent factor.</t>
         </is>
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>1.08 selected. Stable interval with CV around 0.06-0.07. The all-years weighted is 1.08; 3-year and 5-year averages are slightly higher (1.11-1.12) but the longer history supports the all-years value. Slight upward bias in recent years may reflect demographic or claims settlement patterns.</t>
+          <t>LDF 1.073. All-years weighted average 1.077, simple 1.067. The 3-year weighted jumps to 1.129, but recent individual years (2022-2024) cluster tightly in the 1.06-1.09 range. Selected near the simple all-years average to reflect current trajectory. Development continues but at a slow rate.</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
         <is>
-          <t>1.06 selected. Low volatility (CV 0.08-0.10) and the weighted all-years average of 1.06 is supported by the exclude-high-low average. Recent years show slightly elevated factors but the long-term average is more credible given the data stability.</t>
+          <t>LDF 1.060. All-years weighted 1.059, simple 1.056. Very low variance across timeframes. The pattern is stable and predictable. Tail development is approaching maturity; this interval continues the gradual pace. Selected near the weighted average.</t>
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr">
         <is>
-          <t>1.025 selected. Very tight interval with minimal variation across time windows. All averages cluster around 1.02-1.03. At this mature stage, incremental development is small and predictable.</t>
+          <t>LDF 1.025. All-years weighted 1.026, simple 1.023. Extremely tight CV (0.040) reflects mature, consistent behavior. Beyond age 83, development is incremental. Selected at the weighted average, reflecting the mature state of claims at this age.</t>
         </is>
       </c>
       <c r="I76" s="24" t="inlineStr">
         <is>
-          <t>1.020 selected. Stable interval with averages very close to each other. The all-years weighted of 1.02 reflects the normal slow runoff at late development stages.</t>
+          <t>LDF 1.019 (rounded to 1.0185). All-years weighted 1.021, simple 1.018. Tail development is very minimal; CV is 0.004, nearly zero. Claims are substantially paid by age 95. Selected just above the simple average to acknowledge lingering late payments.</t>
         </is>
       </c>
       <c r="J76" s="24" t="inlineStr">
         <is>
-          <t>1.035 selected. Moderate variability (CV 0.04-0.07) with recent years slightly elevated (1.10 3yr) suggesting potentially longer tail development or payment timing shifts. Using 1.035 bridges the elevated recent and lower historical estimates, leaning slightly conservative.</t>
+          <t>LDF 1.035. Slight uptick from the prior interval. All-years weighted 1.039, simple 1.028. The 10-year average of 1.055 is elevated but driven by historical years; recent experience supports 1.03-1.04. Selected near the midpoint reflecting modest tail development.</t>
         </is>
       </c>
       <c r="K76" s="24" t="inlineStr">
         <is>
-          <t>1.022 selected. Very stable (CV 0.01-0.03). The all-years weighted of 1.03 is consistent across time windows, though recent 3-year shows 1.01. The longer horizon supports 1.022 as a balanced estimate reflecting modest late-tail development.</t>
+          <t>LDF 1.022. All-years weighted 1.028, simple 1.022. Very low CV (0.015). Development continues incrementally. Selected at the simple average, balancing tight consensus across time windows.</t>
         </is>
       </c>
       <c r="L76" s="24" t="inlineStr">
         <is>
-          <t>1.020 selected. Low volatility (CV 0.02-0.03). All long-period averages cluster around 1.019-1.023. Development is minimal but consistent at this mature stage.</t>
+          <t>LDF 1.020. All-years weighted 1.023, simple 1.019. Tight clustering. Very low CV (0.029). Tail development is very gradual. Selected just below the weighted average, reflecting the mature state and minimal additional development expected.</t>
         </is>
       </c>
       <c r="M76" s="24" t="inlineStr">
         <is>
-          <t>1.019 selected. Very tight all-years weighted of 1.021, with minimal deviation across time windows (CV 0.02-0.02). Claims are essentially finalized; this small factor reflects nominal late adjustments.</t>
+          <t>LDF 1.0187. All-years weighted 1.021, simple 1.019. CV 0.023, very stable. Development is minimal at this maturity level. Selected near the simple average.</t>
         </is>
       </c>
       <c r="N76" s="24" t="inlineStr">
         <is>
-          <t>1.013 selected. Extremely stable (CV 0.0017). The all-years weighted is 1.015; the 10-year simple is 1.011. Using 1.013 reflects the narrow range and minimal development at this advanced maturity.</t>
+          <t>LDF 1.012. All-years weighted 1.015, simple 1.011. Nearly flat development at this stage. Very low CV (0.002). Selected slightly above the simple average to account for lingering tail activity.</t>
         </is>
       </c>
       <c r="O76" s="24" t="inlineStr">
         <is>
-          <t>1.013 selected. Very low volatility consistent across all windows (CV 0.003-0.012). The all-years weighted is 1.016 but the exclude-high-low is 1.010, suggesting tight central behavior around 1.01-1.02. Selecting 1.013 as middle ground.</t>
+          <t>LDF 1.012. All-years weighted 1.016, simple 1.011. Consistent with prior interval. Extremely low CV (0.003). Development is nominal. Selected at the weighted average.</t>
         </is>
       </c>
       <c r="P76" s="24" t="inlineStr">
         <is>
-          <t>1.012 selected. Stable interval with all-years weighted of 1.016 and exclude-high-low of 1.011. Recent 3yr is elevated (1.019) but the longer average supports a slightly lower value. Very late tail with minimal predictive information.</t>
+          <t>LDF 1.012. All-years weighted 1.016, simple 1.012. Very flat tail. Development is negligible. Selected at the simple average, reflecting near-maturity.</t>
         </is>
       </c>
       <c r="Q76" s="24" t="inlineStr">
         <is>
-          <t>1.015 selected. All averages are nearly identical (1.0158 weighted, 1.0157 exclude high-low). Very low coefficient of variation indicates stable, repeatable late-tail development.</t>
+          <t>LDF 1.0158. All-years weighted 1.016, simple 1.016. Slightly elevated from prior; perhaps some small class of reopens or late activity. CV very low (0.010). Selected at the weighted average.</t>
         </is>
       </c>
       <c r="R76" s="24" t="inlineStr">
         <is>
-          <t>1.008 selected. All-years weighted is 1.0087; extremely tight data (CV 0.003-0.011). At this stage claims are fully settled; this reflects nominal final adjustments.</t>
+          <t>LDF 1.008. All-years weighted 1.009, simple 1.008. Development is minimal. Very low CV (0.003). Tail is essentially closed. Selected at the simple average.</t>
         </is>
       </c>
       <c r="S76" s="24" t="inlineStr">
         <is>
-          <t>1.010 selected. The all-years weighted of 1.013 is slightly elevated versus the exclude-high-low of 1.0054, but given the very late development stage and limited data, using 1.010 balances conservatism with the observed long-tail behavior.</t>
+          <t>LDF 1.011. All-years weighted 1.013, simple 1.010. Small uptick, possibly reflecting infrequent late settlements. CV very low (0.003). Selected between the two averages.</t>
         </is>
       </c>
       <c r="T76" s="24" t="inlineStr">
         <is>
-          <t>1.002 selected. The all-years weighted is 1.0025; exclude-high-low is 1.0. Using 1.002 reflects nominal continuation of the extreme tail with minimal expected development.</t>
+          <t>LDF 1.0025. All-years weighted 1.003, simple 1.002. Minimal tail development. 3-year and 5-year show 1.0 (no development in those windows). Selected at the all-years weighted, reflecting very mature tail.</t>
         </is>
       </c>
       <c r="U76" s="24" t="inlineStr">
         <is>
-          <t>1.005 selected. All-years weighted is 1.0054, close to the simple all of 1.0044. These late-tail intervals show minimal consistent development; using the weighted average as the best estimate of persistent pattern.</t>
+          <t>LDF 1.005. All-years weighted 1.005, simple 1.004. Extremely mature tail. Very low CV (0.006). Selected at the weighted average, acknowledging minimal late-reopening activity.</t>
         </is>
       </c>
       <c r="V76" s="24" t="inlineStr">
         <is>
-          <t>1.006 selected. Identical across all time windows (weighted, simple, exclude high-low all equal 1.0062). This consistency supports the average directly.</t>
+          <t>LDF 1.006. All-years weighted 1.006, simple 1.006. Consistent value across all windows (CV 0.005). Tail is highly mature but not 100% closed. Selected at the consensus value.</t>
         </is>
       </c>
       <c r="W76" s="24" t="inlineStr">
         <is>
-          <t>1.007 selected. All-years weighted is 1.0074, simple is 1.0076, exclude-high-low is 1.0076. Perfect consistency across methods indicates stable late-tail emergence pattern.</t>
+          <t>LDF 1.0075. All-years weighted 1.007, simple 1.008. Tiny amount of late development. Very low CV (0.002). Selected between the two averages.</t>
         </is>
       </c>
       <c r="X76" s="24" t="inlineStr">
         <is>
-          <t>1.004 selected. Only all-years average available (1.0039). At the extreme tail with limited cohort-to-cohort movement, using the provided all-years average as the best available estimate of the tail development pattern.</t>
+          <t>LDF 1.0039. All-years weighted 1.004, simple 1.004. Only one year of data at this extreme tail maturity. Minimal development expected. Selected at the consensus.</t>
         </is>
       </c>
     </row>
@@ -18702,13 +18702,13 @@
         <v>1</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>0.9993</v>
+        <v>0.9992</v>
       </c>
       <c r="G72" s="21" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="21" t="n">
-        <v>0.9992</v>
+        <v>0.9993</v>
       </c>
       <c r="I72" s="21" t="n">
         <v>1</v>
@@ -18767,117 +18767,117 @@
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.1180. Five-year simple (1.1204) selected, rounded to 1.1180 reflecting volume-weighted (1.1180) and exclude_high_low_5yr (1.1330) balance. Early maturity; CV_3yr 0.013 (very tight) but CV_5yr 0.0316 suggests minor variance. 3yr (1.1330) vs 5yr (1.1180) show 1.3% divergence within recency tolerance. Slight downward Bayesian dampening (25% gap closure) reflects recent stable reported count growth without catastrophic spike. Diagnostics: reported_claims stable across all years (~250–700 claims/AY), no anomalies. No frequency shock detected.</t>
+          <t>Reported Count: 1.118. CV_5yr 0.0316 (low, excellent for count data). Weighted 5-year (1.118), simple 5-year (1.1204), and all-year (1.0617) show divergence: weighted/simple at 1.118-1.120 vs all-year 5.3% below. Slope_5yr near zero (0.0027) shows stability. 3-year (1.133) 1.2% above 5-year, recent counts elevated. Reported count stability high; use weighted 5-year as primary anchor with confidence. Early maturity count reporting strong. Frequency-related development normal; no severity shock signals (paid/incurred LDFs independently high, separate drivers).</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). No development in reported count from age 23–35 months across all time windows. Negligible variance; framework guidance: select convergence midpoint (1.0000). Reporting essentially completes by age 23 months in this WC portfolio.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages (weighted 5-year, simple 5-year, all-year) equal 1.0 exactly. Perfect convergence signal (§8). Slope_5yr near zero (-0.0). Count development completely flat at this maturity; virtually no incremental reported claims. Use converged 1.0. Counts solidifying after early reporting spike.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0008. Five-year volume-weighted (1.0008) selected. Negligible variance (CV_5yr 0.0019). All windows (simple, weighted, exclude_high_low) converge 1.0004–1.0009. Minimal reported count development at 35–47 months. Recency default; near-unity expected.</t>
+          <t>Reported Count: 1.0008. CV_5yr 0.0019 (minimal). All averages (weighted 5-year 1.0008, simple 5-year 1.0008, all-year 1.0004) converge extremely tightly within 0.04%. Slope_5yr near zero (-0.0008). Perfect alignment signal. Count development negligible at this interval. Use converged 1.0008. Counts essentially finalized by this depth.</t>
         </is>
       </c>
       <c r="E73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. Five-year weighted (1.0000) selected. Negligible variance (CV_5yr 0.0029). All windows converge 0.9998–1.0000. No development in reported counts post-reporting. Framework guidance: select 1.000 anchor.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0029 (minimal). Weighted 5-year (1.0), simple 5-year (1.0), and all-year (0.9998) show convergence at 1.0 for recent windows. Slope_5yr near zero (0.0004). All main averages align at 1.0. Count development flat. Use 1.0. Counts fully crystallized by mid-tail.</t>
         </is>
       </c>
       <c r="F73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 0.9993. Five-year simple (0.9993) selected, reflecting weighted (0.9992), simple (0.9993), and exclude_high_low_5yr (1.0000) consensus. Extremely tight (CV_5yr 0.0017). Slight downward drift (slope_5yr -0.0007) suggests very marginal count decline or stability. Late-stage reported count; near-unity expected. Recency default; minimal material impact.</t>
+          <t>Reported Count: 0.9992. CV_5yr 0.0017 (minimal). Weighted 5-year (0.9992), simple 5-year (0.9993), and all-year (1.0019) converge on 5-year at ~0.9992. Slope_5yr near zero (-0.0007). All-year 0.27% above 5-year. Count development showing minimal closure activity (LDF &lt;1.0 indicates claim closure without new reports). Use weighted 5-year. Count finalization in progress, slight decline normal.</t>
         </is>
       </c>
       <c r="G73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge precisely (CV_5yr 0.0000). Perfect stability across all windows. No development in reported counts at 71–83 month maturity. Select tail anchor 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages (weighted 5-year, simple 5-year, all-year) equal 1.0 exactly. Perfect convergence. Slope_5yr near zero (0.0). Count development flat at this maturity. Use 1.0. Counts stable and final.</t>
         </is>
       </c>
       <c r="H73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 0.9992. Five-year simple (0.9992) selected. Minimal variance (CV_5yr 0.0019). All windows 0.9986–1.0000. Slight downward slope (slope_5yr -0.0008) consistent with late-stage reporting closure. Framework: marginal development. Recency default.</t>
+          <t>Reported Count: 0.9993. CV_5yr 0.0019 (minimal). Weighted 5-year (0.9993), simple 5-year (0.9992), and all-year (0.9998) converge tightly on 5-year at ~0.9993. Slope_5yr near zero (-0.0008). Convergence signal (§8). Count development showing slight closure dynamic (&lt;1.0). Use weighted 5-year. Counts declining slightly through settlement.</t>
         </is>
       </c>
       <c r="I73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). No variance across windows. Late maturity; no reported count development. Select tail anchor 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence across all windows. Slope_5yr 0.0. Count development flat. Use 1.0. Counts static at this maturity.</t>
         </is>
       </c>
       <c r="J73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 0.9977. Five-year weighted (0.9977) selected. Low variance (CV_5yr 0.0052). All windows 0.9961–1.0000. Slight downward development (slope_5yr -0.0023) consistent with minor late-stage closures. Framework: late maturity; asymmetric conservatism downward muted. Recency default.</t>
+          <t>Reported Count: 0.9977. CV_5yr 0.0052 (low). Weighted 5-year (0.9977), simple 5-year (0.9977), and all-year (0.9994) show convergence on 5-year at 0.9977. Slope_5yr near zero (-0.0023). All-year 0.17% above 5-year. Count development showing mild closure/retirement activity. Use weighted 5-year. Late counts declining through normal closure process.</t>
         </is>
       </c>
       <c r="K73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). Perfect stability. Late tail; no development. Framework: select 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages (weighted 5-year, simple 5-year, all-year) equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Count development flat. Use 1.0. Counts finalized and static.</t>
         </is>
       </c>
       <c r="L73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). Perfect stability across all windows. Late tail; no reported count development. Select tail anchor 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence across all windows. Slope_5yr 0.0. Count development completely flat at this very late maturity. Use 1.0. Counts at ultimate closure.</t>
         </is>
       </c>
       <c r="M73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). No variance. Deep tail maturity; no development expected. Framework: select 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts finalized.</t>
         </is>
       </c>
       <c r="N73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). Perfect convergence; no development. Deep tail; framework guidance: select 1.000 anchor.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts at full completion.</t>
         </is>
       </c>
       <c r="O73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). No variance detected. Deep tail; no development. Framework: select tail anchor 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts final and stable.</t>
         </is>
       </c>
       <c r="P73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). Perfect stability. Deep tail maturity; no reported count development expected or observed. Select 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts at ultimate.</t>
         </is>
       </c>
       <c r="Q73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). No variance. Deep tail; framework guidance: select tail anchor 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts complete.</t>
         </is>
       </c>
       <c r="R73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). Perfect convergence; no variance. Deep tail; no development. Select 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts final.</t>
         </is>
       </c>
       <c r="S73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). No variance across all windows. Very deep tail (215–227mo); no development. Framework: select tail anchor 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts stable.</t>
         </is>
       </c>
       <c r="T73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). Perfect stability. Very deep tail; no reported count development. Select 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts finalized.</t>
         </is>
       </c>
       <c r="U73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). No variance. Very deep tail maturity; framework guidance: select tail anchor 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts at ultimate.</t>
         </is>
       </c>
       <c r="V73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). Perfect convergence; no variance. Extreme tail (251–263mo); sparse diagonals (2–3 origins); no development. Framework: use all-year when sparse. Select 1.000.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts complete.</t>
         </is>
       </c>
       <c r="W73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. All averages converge to 1.000 (CV_5yr 0.0000). Perfect stability. Extreme tail (263–275mo); minimal diagonals. No development. Framework: select 1.000 tail anchor.</t>
+          <t>Reported Count: 1.0. CV_5yr 0.0 (zero variability). All averages equal 1.0 exactly. Perfect convergence. Slope_5yr 0.0. Use 1.0. Counts final.</t>
         </is>
       </c>
       <c r="X73" s="22" t="inlineStr">
         <is>
-          <t>Reported Count: 1.0000. Only weighted_all (1.0000) available; all variants converge to 1.000. Extreme tail (280+ months); sparse data. Framework: use all-year average for tail; select 1.000 as development anchor. No further reported count development expected in this mature portfolio.</t>
+          <t>Reported Count: 1.0. Only weighted_all available (sparse final tail). Value is 1.0. Use weighted_all. Counts at ultimate closure.</t>
         </is>
       </c>
     </row>
@@ -18889,31 +18889,31 @@
         </is>
       </c>
       <c r="B75" s="23" t="n">
-        <v>1.102</v>
+        <v>1.11</v>
       </c>
       <c r="C75" s="23" t="n">
-        <v>1.005</v>
+        <v>1.003</v>
       </c>
       <c r="D75" s="23" t="n">
-        <v>1</v>
+        <v>1.0005</v>
       </c>
       <c r="E75" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="G75" s="23" t="n">
-        <v>1</v>
+        <v>1.0015</v>
       </c>
       <c r="H75" s="23" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="I75" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="K75" s="23" t="n">
         <v>1</v>
@@ -18966,117 +18966,117 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>1.102 selected. The all-years weighted is 1.0617, but recent years show substantial elevation (3yr: 1.133). Given the stable nature of claims counts (low volatility across time for this measure), recent emergence patterns should be trusted. The 5-year average of 1.118 and 10-year simple of 1.101 bound the estimate. Using 1.102 to reflect the recent claim reporting acceleration while staying near the long-run average.</t>
+          <t>LDF 1.110. Early reported count development. All-years weighted 1.062, simple 1.068, but these are pulled down by very early years with minimal count changes. The 5-year and 10-year weighted averages (1.118, 1.096) better reflect recent experience. Recent individual years (2020-2024) show 1.06-1.13, with 2024 showing 1.19. Selected above all-years averages to reflect recent years' slightly elevated late-report trickle, acknowledging claims management practices may have shifted toward more delayed reporting in recent cohorts.</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>1.005 selected. Extremely tight data (CV 0.0-0.0145). All averages cluster around 1.003-1.004. The reported counts stabilize quickly after initial reporting; this small factor reflects late-reported claims that emerged after month 23.</t>
+          <t>LDF 1.003. All-years weighted 1.0, simple 1.004. Negligible additional count development after age 23. CV is 0. The triangle shows counts are essentially locked at age 23 for most years, with only minimal late reports. Selected at the simple average, reflecting near-complete report realization by month 23.</t>
         </is>
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All-years weighted is 1.0004, with all values extremely close to 1.0 (CV 0.0-0.002). Claims are essentially fully reported by age 35 months; minimal additional reporting occurs.</t>
+          <t>LDF 1.0005. All-years weighted 1.0, simple 1.0. Development is literally nil. CV 0. Counts are fully reported by age 35. Selected at 1.0, rounding to reflect the virtually perfect maturity.</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All-years weighted is 0.9998, with the simple and exclude-high-low also at 0.9999. At this stage no additional claims are reported; using 1.0 reflects completion of the reporting process.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. CV near zero (0.002). No development. Counts are completely closed. Selected at 1.0.</t>
         </is>
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. The all-years weighted is 1.0019, but all values are extremely close to 1.0 (CV 0.001-0.002). Claims are fully reported; using 1.0 reflects the practical completion of the count triangle.</t>
+          <t>LDF 1.001. All-years weighted 1.0, simple 1.001. Minimal development. CV is 0.002. Nearly no additional reports expected at this maturity. Selected at the simple average, reflecting minute tail activity.</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All-years weighted is 1.0024 but simple is 1.0015 and exclude-high-low is 1.0002. The tight cluster around 1.0 indicates minimal development. Using 1.0 reflects the complete reporting achieved well before this interval.</t>
+          <t>LDF 1.0015. All-years weighted 1.002, simple 1.001. CV is 0. Very slight late-report trickle. Selected between the two averages, acknowledging minimal but non-zero development at this tail stage.</t>
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All-years weighted is 0.9998, with all other averages at or very near 1.0. Reported counts have fully stabilized; no meaningful development.</t>
+          <t>LDF 0.9995. All-years weighted 1.0, simple 1.0 approximately. CV 0.002. Some years show infinitesimal decreases (likely closure or duplication removal). Development is essentially flat. Selected slightly below 1.0 to reflect the rare decrements observed.</t>
         </is>
       </c>
       <c r="I76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All-years weighted, simple, and exclude-high-low are all exactly 1.0. Perfect stability at this stage.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development whatsoever. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="J76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. The all-years weighted is 0.9994, with slight recent variation (3yr: 0.9964) but all values extremely close to 1.0 (CV 0.004-0.007). Using 1.0 reflects the practical completion and stability of reported counts.</t>
+          <t>LDF 0.9990. All-years weighted 1.0, simple 1.0 approximately. CV is 0.007. Some years show minor count decreases. Development is negligible but occasionally slightly negative. Selected slightly below 1.0 to reflect the observed rare closures or corrections.</t>
         </is>
       </c>
       <c r="K76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All-years weighted, simple, and exclude-high-low are all exactly 1.0. Complete stability.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="L76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages are exactly 1.0 across all time windows. No development.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="M76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. Perfect stability with all averages at 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="N76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0; complete stability.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="O76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="P76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="Q76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="R76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="S76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="T76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="U76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="V76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="W76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. No development. CV is 0. Selected at 1.0.</t>
         </is>
       </c>
       <c r="X76" s="24" t="inlineStr">
         <is>
-          <t>1.0 selected. All averages exactly 1.0. The reported count triangle is essentially complete and flat from early in the development period.</t>
+          <t>LDF 1.000. All-years weighted 1.0, simple 1.0. Limited data at this extreme tail maturity; no development observed. Selected at 1.0.</t>
         </is>
       </c>
     </row>
@@ -19158,34 +19158,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19194,151 +19171,17 @@
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="3" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="X2" s="5" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="Y2" s="5" t="inlineStr">
-        <is>
-          <t>287</t>
+          <t>Exposure</t>
         </is>
       </c>
     </row>
@@ -19348,6 +19191,9 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B3" s="7" t="n">
+        <v>316377369.9688</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -19355,6 +19201,9 @@
           <t>2002</t>
         </is>
       </c>
+      <c r="B4" s="7" t="n">
+        <v>322704917.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -19362,6 +19211,9 @@
           <t>2003</t>
         </is>
       </c>
+      <c r="B5" s="7" t="n">
+        <v>329159015.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -19369,6 +19221,9 @@
           <t>2004</t>
         </is>
       </c>
+      <c r="B6" s="7" t="n">
+        <v>335742196</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -19376,6 +19231,9 @@
           <t>2005</t>
         </is>
       </c>
+      <c r="B7" s="7" t="n">
+        <v>342457040</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -19383,6 +19241,9 @@
           <t>2006</t>
         </is>
       </c>
+      <c r="B8" s="7" t="n">
+        <v>349306180.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -19390,6 +19251,9 @@
           <t>2007</t>
         </is>
       </c>
+      <c r="B9" s="7" t="n">
+        <v>356292304.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -19397,6 +19261,9 @@
           <t>2008</t>
         </is>
       </c>
+      <c r="B10" s="7" t="n">
+        <v>363418150.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -19404,6 +19271,9 @@
           <t>2009</t>
         </is>
       </c>
+      <c r="B11" s="7" t="n">
+        <v>370686513.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -19411,6 +19281,9 @@
           <t>2010</t>
         </is>
       </c>
+      <c r="B12" s="7" t="n">
+        <v>378100243.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -19418,6 +19291,9 @@
           <t>2011</t>
         </is>
       </c>
+      <c r="B13" s="7" t="n">
+        <v>385662248.6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -19425,6 +19301,9 @@
           <t>2012</t>
         </is>
       </c>
+      <c r="B14" s="7" t="n">
+        <v>393375493.6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -19432,6 +19311,9 @@
           <t>2013</t>
         </is>
       </c>
+      <c r="B15" s="7" t="n">
+        <v>401243003.4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -19439,6 +19321,9 @@
           <t>2014</t>
         </is>
       </c>
+      <c r="B16" s="7" t="n">
+        <v>409267863.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -19446,6 +19331,9 @@
           <t>2015</t>
         </is>
       </c>
+      <c r="B17" s="7" t="n">
+        <v>417453220.8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -19453,6 +19341,9 @@
           <t>2016</t>
         </is>
       </c>
+      <c r="B18" s="7" t="n">
+        <v>425802285.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -19460,6 +19351,9 @@
           <t>2017</t>
         </is>
       </c>
+      <c r="B19" s="7" t="n">
+        <v>434318330.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -19467,6 +19361,9 @@
           <t>2018</t>
         </is>
       </c>
+      <c r="B20" s="7" t="n">
+        <v>443004697.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -19474,6 +19371,9 @@
           <t>2019</t>
         </is>
       </c>
+      <c r="B21" s="7" t="n">
+        <v>451864791.5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -19481,6 +19381,9 @@
           <t>2020</t>
         </is>
       </c>
+      <c r="B22" s="7" t="n">
+        <v>460902087.3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -19488,6 +19391,9 @@
           <t>2021</t>
         </is>
       </c>
+      <c r="B23" s="7" t="n">
+        <v>470120129.1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -19495,6 +19401,9 @@
           <t>2022</t>
         </is>
       </c>
+      <c r="B24" s="7" t="n">
+        <v>479522531.6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -19502,6 +19411,9 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="B25" s="7" t="n">
+        <v>489112982.3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -19509,10 +19421,13 @@
           <t>2024</t>
         </is>
       </c>
+      <c r="B26" s="7" t="n">
+        <v>498895241.9</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample-data/sample-run/selections/Chain Ladder Selections - LDFs.xlsx
+++ b/sample-data/sample-run/selections/Chain Ladder Selections - LDFs.xlsx
@@ -400,27 +400,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -429,49 +414,49 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1952,95 +1937,95 @@
       </c>
       <c r="B28" s="4">
         <f>IFERROR(IF(B2="","",B2/A2),"")</f>
-        <v>0</v>
+        <v>2.7399</v>
       </c>
       <c r="C28" s="4">
         <f>IFERROR(IF(C2="","",C2/B2),"")</f>
-        <v>0</v>
+        <v>1.2238</v>
       </c>
       <c r="D28" s="4">
         <f>IFERROR(IF(D2="","",D2/C2),"")</f>
-        <v>0</v>
+        <v>1.1005</v>
       </c>
       <c r="E28" s="4">
         <f>IFERROR(IF(E2="","",E2/D2),"")</f>
-        <v>0</v>
+        <v>1.0751</v>
       </c>
       <c r="F28" s="4">
         <f>IFERROR(IF(F2="","",F2/E2),"")</f>
-        <v>0</v>
+        <v>1.0677</v>
       </c>
       <c r="G28" s="4">
         <f>IFERROR(IF(G2="","",G2/F2),"")</f>
-        <v>0</v>
+        <v>0.9976</v>
       </c>
       <c r="H28" s="4">
         <f>IFERROR(IF(H2="","",H2/G2),"")</f>
-        <v>0</v>
+        <v>1.0093</v>
       </c>
       <c r="I28" s="4">
         <f>IFERROR(IF(I2="","",I2/H2),"")</f>
-        <v>0</v>
+        <v>1.0073</v>
       </c>
       <c r="J28" s="4">
         <f>IFERROR(IF(J2="","",J2/I2),"")</f>
-        <v>0</v>
+        <v>1.0084</v>
       </c>
       <c r="K28" s="4">
         <f>IFERROR(IF(K2="","",K2/J2),"")</f>
-        <v>0</v>
+        <v>1.0214</v>
       </c>
       <c r="L28" s="4">
         <f>IFERROR(IF(L2="","",L2/K2),"")</f>
-        <v>0</v>
+        <v>1.0208</v>
       </c>
       <c r="M28" s="4">
         <f>IFERROR(IF(M2="","",M2/L2),"")</f>
-        <v>0</v>
+        <v>0.9989</v>
       </c>
       <c r="N28" s="4">
         <f>IFERROR(IF(N2="","",N2/M2),"")</f>
-        <v>0</v>
+        <v>1.0229</v>
       </c>
       <c r="O28" s="4">
         <f>IFERROR(IF(O2="","",O2/N2),"")</f>
-        <v>0</v>
+        <v>1.017</v>
       </c>
       <c r="P28" s="4">
         <f>IFERROR(IF(P2="","",P2/O2),"")</f>
-        <v>0</v>
+        <v>1.0532</v>
       </c>
       <c r="Q28" s="4">
         <f>IFERROR(IF(Q2="","",Q2/P2),"")</f>
-        <v>0</v>
+        <v>1.0236</v>
       </c>
       <c r="R28" s="4">
         <f>IFERROR(IF(R2="","",R2/Q2),"")</f>
-        <v>0</v>
+        <v>1.0309</v>
       </c>
       <c r="S28" s="4">
         <f>IFERROR(IF(S2="","",S2/R2),"")</f>
-        <v>0</v>
+        <v>1.018</v>
       </c>
       <c r="T28" s="4">
         <f>IFERROR(IF(T2="","",T2/S2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U28" s="4">
         <f>IFERROR(IF(U2="","",U2/T2),"")</f>
-        <v>0</v>
+        <v>1.0234</v>
       </c>
       <c r="V28" s="4">
         <f>IFERROR(IF(V2="","",V2/U2),"")</f>
-        <v>0</v>
+        <v>1.0139</v>
       </c>
       <c r="W28" s="4">
         <f>IFERROR(IF(W2="","",W2/V2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="X28" s="4">
         <f>IFERROR(IF(X2="","",X2/W2),"")</f>
-        <v>0</v>
+        <v>1.0119</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -2049,91 +2034,91 @@
       </c>
       <c r="B29" s="4">
         <f>IFERROR(IF(B3="","",B3/A3),"")</f>
-        <v>0</v>
+        <v>1.4304</v>
       </c>
       <c r="C29" s="4">
         <f>IFERROR(IF(C3="","",C3/B3),"")</f>
-        <v>0</v>
+        <v>1.0118</v>
       </c>
       <c r="D29" s="4">
         <f>IFERROR(IF(D3="","",D3/C3),"")</f>
-        <v>0</v>
+        <v>1.1947</v>
       </c>
       <c r="E29" s="4">
         <f>IFERROR(IF(E3="","",E3/D3),"")</f>
-        <v>0</v>
+        <v>1.0132</v>
       </c>
       <c r="F29" s="4">
         <f>IFERROR(IF(F3="","",F3/E3),"")</f>
-        <v>0</v>
+        <v>1.0627</v>
       </c>
       <c r="G29" s="4">
         <f>IFERROR(IF(G3="","",G3/F3),"")</f>
-        <v>0</v>
+        <v>1.019</v>
       </c>
       <c r="H29" s="4">
         <f>IFERROR(IF(H3="","",H3/G3),"")</f>
-        <v>0</v>
+        <v>1.0002</v>
       </c>
       <c r="I29" s="4">
         <f>IFERROR(IF(I3="","",I3/H3),"")</f>
-        <v>0</v>
+        <v>1.0219</v>
       </c>
       <c r="J29" s="4">
         <f>IFERROR(IF(J3="","",J3/I3),"")</f>
-        <v>0</v>
+        <v>1.0096</v>
       </c>
       <c r="K29" s="4">
         <f>IFERROR(IF(K3="","",K3/J3),"")</f>
-        <v>0</v>
+        <v>1.0103</v>
       </c>
       <c r="L29" s="4">
         <f>IFERROR(IF(L3="","",L3/K3),"")</f>
-        <v>0</v>
+        <v>1.0339</v>
       </c>
       <c r="M29" s="4">
         <f>IFERROR(IF(M3="","",M3/L3),"")</f>
-        <v>0</v>
+        <v>1.0013</v>
       </c>
       <c r="N29" s="4">
         <f>IFERROR(IF(N3="","",N3/M3),"")</f>
-        <v>0</v>
+        <v>1.0401</v>
       </c>
       <c r="O29" s="4">
         <f>IFERROR(IF(O3="","",O3/N3),"")</f>
-        <v>0</v>
+        <v>1.0264</v>
       </c>
       <c r="P29" s="4">
         <f>IFERROR(IF(P3="","",P3/O3),"")</f>
-        <v>0</v>
+        <v>1.0147</v>
       </c>
       <c r="Q29" s="4">
         <f>IFERROR(IF(Q3="","",Q3/P3),"")</f>
-        <v>0</v>
+        <v>1.0529</v>
       </c>
       <c r="R29" s="4">
         <f>IFERROR(IF(R3="","",R3/Q3),"")</f>
-        <v>0</v>
+        <v>1.0011</v>
       </c>
       <c r="S29" s="4">
         <f>IFERROR(IF(S3="","",S3/R3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T29" s="4">
         <f>IFERROR(IF(T3="","",T3/S3),"")</f>
-        <v>0</v>
+        <v>1.0424</v>
       </c>
       <c r="U29" s="4">
         <f>IFERROR(IF(U3="","",U3/T3),"")</f>
-        <v>0</v>
+        <v>0.9938</v>
       </c>
       <c r="V29" s="4">
         <f>IFERROR(IF(V3="","",V3/U3),"")</f>
-        <v>0</v>
+        <v>1.0359</v>
       </c>
       <c r="W29" s="4">
         <f>IFERROR(IF(W3="","",W3/V3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="X29" s="4">
         <f>IFERROR(IF(X3="","",X3/W3),"")</f>
@@ -2146,87 +2131,87 @@
       </c>
       <c r="B30" s="4">
         <f>IFERROR(IF(B4="","",B4/A4),"")</f>
-        <v>0</v>
+        <v>1.4452</v>
       </c>
       <c r="C30" s="4">
         <f>IFERROR(IF(C4="","",C4/B4),"")</f>
-        <v>0</v>
+        <v>1.0824</v>
       </c>
       <c r="D30" s="4">
         <f>IFERROR(IF(D4="","",D4/C4),"")</f>
-        <v>0</v>
+        <v>1.1887</v>
       </c>
       <c r="E30" s="4">
         <f>IFERROR(IF(E4="","",E4/D4),"")</f>
-        <v>0</v>
+        <v>0.9077</v>
       </c>
       <c r="F30" s="4">
         <f>IFERROR(IF(F4="","",F4/E4),"")</f>
-        <v>0</v>
+        <v>1.0678</v>
       </c>
       <c r="G30" s="4">
         <f>IFERROR(IF(G4="","",G4/F4),"")</f>
-        <v>0</v>
+        <v>0.9972</v>
       </c>
       <c r="H30" s="4">
         <f>IFERROR(IF(H4="","",H4/G4),"")</f>
-        <v>0</v>
+        <v>0.9925</v>
       </c>
       <c r="I30" s="4">
         <f>IFERROR(IF(I4="","",I4/H4),"")</f>
-        <v>0</v>
+        <v>0.9981</v>
       </c>
       <c r="J30" s="4">
         <f>IFERROR(IF(J4="","",J4/I4),"")</f>
-        <v>0</v>
+        <v>1.0022</v>
       </c>
       <c r="K30" s="4">
         <f>IFERROR(IF(K4="","",K4/J4),"")</f>
-        <v>0</v>
+        <v>0.9979</v>
       </c>
       <c r="L30" s="4">
         <f>IFERROR(IF(L4="","",L4/K4),"")</f>
-        <v>0</v>
+        <v>0.9923</v>
       </c>
       <c r="M30" s="4">
         <f>IFERROR(IF(M4="","",M4/L4),"")</f>
-        <v>0</v>
+        <v>0.9949</v>
       </c>
       <c r="N30" s="4">
         <f>IFERROR(IF(N4="","",N4/M4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O30" s="4">
         <f>IFERROR(IF(O4="","",O4/N4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P30" s="4">
         <f>IFERROR(IF(P4="","",P4/O4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q30" s="4">
         <f>IFERROR(IF(Q4="","",Q4/P4),"")</f>
-        <v>0</v>
+        <v>1.0021</v>
       </c>
       <c r="R30" s="4">
         <f>IFERROR(IF(R4="","",R4/Q4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S30" s="4">
         <f>IFERROR(IF(S4="","",S4/R4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T30" s="4">
         <f>IFERROR(IF(T4="","",T4/S4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U30" s="4">
         <f>IFERROR(IF(U4="","",U4/T4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="V30" s="4">
         <f>IFERROR(IF(V4="","",V4/U4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="W30" s="4">
         <f>IFERROR(IF(W4="","",W4/V4),"")</f>
@@ -2243,83 +2228,83 @@
       </c>
       <c r="B31" s="4">
         <f>IFERROR(IF(B5="","",B5/A5),"")</f>
-        <v>0</v>
+        <v>1.1416</v>
       </c>
       <c r="C31" s="4">
         <f>IFERROR(IF(C5="","",C5/B5),"")</f>
-        <v>0</v>
+        <v>1.1042</v>
       </c>
       <c r="D31" s="4">
         <f>IFERROR(IF(D5="","",D5/C5),"")</f>
-        <v>0</v>
+        <v>1.0474</v>
       </c>
       <c r="E31" s="4">
         <f>IFERROR(IF(E5="","",E5/D5),"")</f>
-        <v>0</v>
+        <v>1.1305</v>
       </c>
       <c r="F31" s="4">
         <f>IFERROR(IF(F5="","",F5/E5),"")</f>
-        <v>0</v>
+        <v>1.0056</v>
       </c>
       <c r="G31" s="4">
         <f>IFERROR(IF(G5="","",G5/F5),"")</f>
-        <v>0</v>
+        <v>1.0185</v>
       </c>
       <c r="H31" s="4">
         <f>IFERROR(IF(H5="","",H5/G5),"")</f>
-        <v>0</v>
+        <v>1.0077</v>
       </c>
       <c r="I31" s="4">
         <f>IFERROR(IF(I5="","",I5/H5),"")</f>
-        <v>0</v>
+        <v>1.0238</v>
       </c>
       <c r="J31" s="4">
         <f>IFERROR(IF(J5="","",J5/I5),"")</f>
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="K31" s="4">
         <f>IFERROR(IF(K5="","",K5/J5),"")</f>
-        <v>0</v>
+        <v>1.0231</v>
       </c>
       <c r="L31" s="4">
         <f>IFERROR(IF(L5="","",L5/K5),"")</f>
-        <v>0</v>
+        <v>0.9887</v>
       </c>
       <c r="M31" s="4">
         <f>IFERROR(IF(M5="","",M5/L5),"")</f>
-        <v>0</v>
+        <v>1.0004</v>
       </c>
       <c r="N31" s="4">
         <f>IFERROR(IF(N5="","",N5/M5),"")</f>
-        <v>0</v>
+        <v>1.0003</v>
       </c>
       <c r="O31" s="4">
         <f>IFERROR(IF(O5="","",O5/N5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P31" s="4">
         <f>IFERROR(IF(P5="","",P5/O5),"")</f>
-        <v>0</v>
+        <v>1.0038</v>
       </c>
       <c r="Q31" s="4">
         <f>IFERROR(IF(Q5="","",Q5/P5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R31" s="4">
         <f>IFERROR(IF(R5="","",R5/Q5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S31" s="4">
         <f>IFERROR(IF(S5="","",S5/R5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T31" s="4">
         <f>IFERROR(IF(T5="","",T5/S5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U31" s="4">
         <f>IFERROR(IF(U5="","",U5/T5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="V31" s="4">
         <f>IFERROR(IF(V5="","",V5/U5),"")</f>
@@ -2340,79 +2325,79 @@
       </c>
       <c r="B32" s="4">
         <f>IFERROR(IF(B6="","",B6/A6),"")</f>
-        <v>0</v>
+        <v>1.3029</v>
       </c>
       <c r="C32" s="4">
         <f>IFERROR(IF(C6="","",C6/B6),"")</f>
-        <v>0</v>
+        <v>1.0929</v>
       </c>
       <c r="D32" s="4">
         <f>IFERROR(IF(D6="","",D6/C6),"")</f>
-        <v>0</v>
+        <v>0.9755</v>
       </c>
       <c r="E32" s="4">
         <f>IFERROR(IF(E6="","",E6/D6),"")</f>
-        <v>0</v>
+        <v>1.0372</v>
       </c>
       <c r="F32" s="4">
         <f>IFERROR(IF(F6="","",F6/E6),"")</f>
-        <v>0</v>
+        <v>1.0163</v>
       </c>
       <c r="G32" s="4">
         <f>IFERROR(IF(G6="","",G6/F6),"")</f>
-        <v>0</v>
+        <v>1.0204</v>
       </c>
       <c r="H32" s="4">
         <f>IFERROR(IF(H6="","",H6/G6),"")</f>
-        <v>0</v>
+        <v>1.0056</v>
       </c>
       <c r="I32" s="4">
         <f>IFERROR(IF(I6="","",I6/H6),"")</f>
-        <v>0</v>
+        <v>1.0129</v>
       </c>
       <c r="J32" s="4">
         <f>IFERROR(IF(J6="","",J6/I6),"")</f>
-        <v>0</v>
+        <v>1.0273</v>
       </c>
       <c r="K32" s="4">
         <f>IFERROR(IF(K6="","",K6/J6),"")</f>
-        <v>0</v>
+        <v>1.0117</v>
       </c>
       <c r="L32" s="4">
         <f>IFERROR(IF(L6="","",L6/K6),"")</f>
-        <v>0</v>
+        <v>1.1194</v>
       </c>
       <c r="M32" s="4">
         <f>IFERROR(IF(M6="","",M6/L6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N32" s="4">
         <f>IFERROR(IF(N6="","",N6/M6),"")</f>
-        <v>0</v>
+        <v>0.9816</v>
       </c>
       <c r="O32" s="4">
         <f>IFERROR(IF(O6="","",O6/N6),"")</f>
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P32" s="4">
         <f>IFERROR(IF(P6="","",P6/O6),"")</f>
-        <v>0</v>
+        <v>1.007</v>
       </c>
       <c r="Q32" s="4">
         <f>IFERROR(IF(Q6="","",Q6/P6),"")</f>
-        <v>0</v>
+        <v>1.0151</v>
       </c>
       <c r="R32" s="4">
         <f>IFERROR(IF(R6="","",R6/Q6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S32" s="4">
         <f>IFERROR(IF(S6="","",S6/R6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T32" s="4">
         <f>IFERROR(IF(T6="","",T6/S6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U32" s="4">
         <f>IFERROR(IF(U6="","",U6/T6),"")</f>
@@ -2437,75 +2422,75 @@
       </c>
       <c r="B33" s="4">
         <f>IFERROR(IF(B7="","",B7/A7),"")</f>
-        <v>0</v>
+        <v>1.5119</v>
       </c>
       <c r="C33" s="4">
         <f>IFERROR(IF(C7="","",C7/B7),"")</f>
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="D33" s="4">
         <f>IFERROR(IF(D7="","",D7/C7),"")</f>
-        <v>0</v>
+        <v>1.0694</v>
       </c>
       <c r="E33" s="4">
         <f>IFERROR(IF(E7="","",E7/D7),"")</f>
-        <v>0</v>
+        <v>1.009</v>
       </c>
       <c r="F33" s="4">
         <f>IFERROR(IF(F7="","",F7/E7),"")</f>
-        <v>0</v>
+        <v>1.0504</v>
       </c>
       <c r="G33" s="4">
         <f>IFERROR(IF(G7="","",G7/F7),"")</f>
-        <v>0</v>
+        <v>1.0441</v>
       </c>
       <c r="H33" s="4">
         <f>IFERROR(IF(H7="","",H7/G7),"")</f>
-        <v>0</v>
+        <v>0.9816</v>
       </c>
       <c r="I33" s="4">
         <f>IFERROR(IF(I7="","",I7/H7),"")</f>
-        <v>0</v>
+        <v>1.026</v>
       </c>
       <c r="J33" s="4">
         <f>IFERROR(IF(J7="","",J7/I7),"")</f>
-        <v>0</v>
+        <v>1.0371</v>
       </c>
       <c r="K33" s="4">
         <f>IFERROR(IF(K7="","",K7/J7),"")</f>
-        <v>0</v>
+        <v>1.0832</v>
       </c>
       <c r="L33" s="4">
         <f>IFERROR(IF(L7="","",L7/K7),"")</f>
-        <v>0</v>
+        <v>1.0601</v>
       </c>
       <c r="M33" s="4">
         <f>IFERROR(IF(M7="","",M7/L7),"")</f>
-        <v>0</v>
+        <v>1.0275</v>
       </c>
       <c r="N33" s="4">
         <f>IFERROR(IF(N7="","",N7/M7),"")</f>
-        <v>0</v>
+        <v>1.0108</v>
       </c>
       <c r="O33" s="4">
         <f>IFERROR(IF(O7="","",O7/N7),"")</f>
-        <v>0</v>
+        <v>1.0006</v>
       </c>
       <c r="P33" s="4">
         <f>IFERROR(IF(P7="","",P7/O7),"")</f>
-        <v>0</v>
+        <v>1.0116</v>
       </c>
       <c r="Q33" s="4">
         <f>IFERROR(IF(Q7="","",Q7/P7),"")</f>
-        <v>0</v>
+        <v>1.0031</v>
       </c>
       <c r="R33" s="4">
         <f>IFERROR(IF(R7="","",R7/Q7),"")</f>
-        <v>0</v>
+        <v>1.0073</v>
       </c>
       <c r="S33" s="4">
         <f>IFERROR(IF(S7="","",S7/R7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T33" s="4">
         <f>IFERROR(IF(T7="","",T7/S7),"")</f>
@@ -2534,71 +2519,71 @@
       </c>
       <c r="B34" s="4">
         <f>IFERROR(IF(B8="","",B8/A8),"")</f>
-        <v>0</v>
+        <v>1.0888</v>
       </c>
       <c r="C34" s="4">
         <f>IFERROR(IF(C8="","",C8/B8),"")</f>
-        <v>0</v>
+        <v>1.0891</v>
       </c>
       <c r="D34" s="4">
         <f>IFERROR(IF(D8="","",D8/C8),"")</f>
-        <v>0</v>
+        <v>1.1204</v>
       </c>
       <c r="E34" s="4">
         <f>IFERROR(IF(E8="","",E8/D8),"")</f>
-        <v>0</v>
+        <v>1.1147</v>
       </c>
       <c r="F34" s="4">
         <f>IFERROR(IF(F8="","",F8/E8),"")</f>
-        <v>0</v>
+        <v>1.1938</v>
       </c>
       <c r="G34" s="4">
         <f>IFERROR(IF(G8="","",G8/F8),"")</f>
-        <v>0</v>
+        <v>1.0636</v>
       </c>
       <c r="H34" s="4">
         <f>IFERROR(IF(H8="","",H8/G8),"")</f>
-        <v>0</v>
+        <v>1.1095</v>
       </c>
       <c r="I34" s="4">
         <f>IFERROR(IF(I8="","",I8/H8),"")</f>
-        <v>0</v>
+        <v>1.0716</v>
       </c>
       <c r="J34" s="4">
         <f>IFERROR(IF(J8="","",J8/I8),"")</f>
-        <v>0</v>
+        <v>1.1016</v>
       </c>
       <c r="K34" s="4">
         <f>IFERROR(IF(K8="","",K8/J8),"")</f>
-        <v>0</v>
+        <v>1.0307</v>
       </c>
       <c r="L34" s="4">
         <f>IFERROR(IF(L8="","",L8/K8),"")</f>
-        <v>0</v>
+        <v>1.0289</v>
       </c>
       <c r="M34" s="4">
         <f>IFERROR(IF(M8="","",M8/L8),"")</f>
-        <v>0</v>
+        <v>1.0161</v>
       </c>
       <c r="N34" s="4">
         <f>IFERROR(IF(N8="","",N8/M8),"")</f>
-        <v>0</v>
+        <v>1.0009</v>
       </c>
       <c r="O34" s="4">
         <f>IFERROR(IF(O8="","",O8/N8),"")</f>
-        <v>0</v>
+        <v>1.0436</v>
       </c>
       <c r="P34" s="4">
         <f>IFERROR(IF(P8="","",P8/O8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q34" s="4">
         <f>IFERROR(IF(Q8="","",Q8/P8),"")</f>
-        <v>0</v>
+        <v>1.0036</v>
       </c>
       <c r="R34" s="4">
         <f>IFERROR(IF(R8="","",R8/Q8),"")</f>
-        <v>0</v>
+        <v>1.0025</v>
       </c>
       <c r="S34" s="4">
         <f>IFERROR(IF(S8="","",S8/R8),"")</f>
@@ -2631,67 +2616,67 @@
       </c>
       <c r="B35" s="4">
         <f>IFERROR(IF(B9="","",B9/A9),"")</f>
-        <v>0</v>
+        <v>1.3857</v>
       </c>
       <c r="C35" s="4">
         <f>IFERROR(IF(C9="","",C9/B9),"")</f>
-        <v>0</v>
+        <v>1.2105</v>
       </c>
       <c r="D35" s="4">
         <f>IFERROR(IF(D9="","",D9/C9),"")</f>
-        <v>0</v>
+        <v>1.391</v>
       </c>
       <c r="E35" s="4">
         <f>IFERROR(IF(E9="","",E9/D9),"")</f>
-        <v>0</v>
+        <v>0.9693</v>
       </c>
       <c r="F35" s="4">
         <f>IFERROR(IF(F9="","",F9/E9),"")</f>
-        <v>0</v>
+        <v>1.0168</v>
       </c>
       <c r="G35" s="4">
         <f>IFERROR(IF(G9="","",G9/F9),"")</f>
-        <v>0</v>
+        <v>1.0054</v>
       </c>
       <c r="H35" s="4">
         <f>IFERROR(IF(H9="","",H9/G9),"")</f>
-        <v>0</v>
+        <v>1.0132</v>
       </c>
       <c r="I35" s="4">
         <f>IFERROR(IF(I9="","",I9/H9),"")</f>
-        <v>0</v>
+        <v>1.0057</v>
       </c>
       <c r="J35" s="4">
         <f>IFERROR(IF(J9="","",J9/I9),"")</f>
-        <v>0</v>
+        <v>1.0347</v>
       </c>
       <c r="K35" s="4">
         <f>IFERROR(IF(K9="","",K9/J9),"")</f>
-        <v>0</v>
+        <v>1.0049</v>
       </c>
       <c r="L35" s="4">
         <f>IFERROR(IF(L9="","",L9/K9),"")</f>
-        <v>0</v>
+        <v>1.0002</v>
       </c>
       <c r="M35" s="4">
         <f>IFERROR(IF(M9="","",M9/L9),"")</f>
-        <v>0</v>
+        <v>0.9854</v>
       </c>
       <c r="N35" s="4">
         <f>IFERROR(IF(N9="","",N9/M9),"")</f>
-        <v>0</v>
+        <v>1.0002</v>
       </c>
       <c r="O35" s="4">
         <f>IFERROR(IF(O9="","",O9/N9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P35" s="4">
         <f>IFERROR(IF(P9="","",P9/O9),"")</f>
-        <v>0</v>
+        <v>1.0049</v>
       </c>
       <c r="Q35" s="4">
         <f>IFERROR(IF(Q9="","",Q9/P9),"")</f>
-        <v>0</v>
+        <v>1.021</v>
       </c>
       <c r="R35" s="4">
         <f>IFERROR(IF(R9="","",R9/Q9),"")</f>
@@ -2728,63 +2713,63 @@
       </c>
       <c r="B36" s="4">
         <f>IFERROR(IF(B10="","",B10/A10),"")</f>
-        <v>0</v>
+        <v>2.4408</v>
       </c>
       <c r="C36" s="4">
         <f>IFERROR(IF(C10="","",C10/B10),"")</f>
-        <v>0</v>
+        <v>0.9424</v>
       </c>
       <c r="D36" s="4">
         <f>IFERROR(IF(D10="","",D10/C10),"")</f>
-        <v>0</v>
+        <v>1.0249</v>
       </c>
       <c r="E36" s="4">
         <f>IFERROR(IF(E10="","",E10/D10),"")</f>
-        <v>0</v>
+        <v>1.0665</v>
       </c>
       <c r="F36" s="4">
         <f>IFERROR(IF(F10="","",F10/E10),"")</f>
-        <v>0</v>
+        <v>1.0513</v>
       </c>
       <c r="G36" s="4">
         <f>IFERROR(IF(G10="","",G10/F10),"")</f>
-        <v>0</v>
+        <v>1.0364</v>
       </c>
       <c r="H36" s="4">
         <f>IFERROR(IF(H10="","",H10/G10),"")</f>
-        <v>0</v>
+        <v>1.1441</v>
       </c>
       <c r="I36" s="4">
         <f>IFERROR(IF(I10="","",I10/H10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J36" s="4">
         <f>IFERROR(IF(J10="","",J10/I10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K36" s="4">
         <f>IFERROR(IF(K10="","",K10/J10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L36" s="4">
         <f>IFERROR(IF(L10="","",L10/K10),"")</f>
-        <v>0</v>
+        <v>1.0135</v>
       </c>
       <c r="M36" s="4">
         <f>IFERROR(IF(M10="","",M10/L10),"")</f>
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N36" s="4">
         <f>IFERROR(IF(N10="","",N10/M10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O36" s="4">
         <f>IFERROR(IF(O10="","",O10/N10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P36" s="4">
         <f>IFERROR(IF(P10="","",P10/O10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q36" s="4">
         <f>IFERROR(IF(Q10="","",Q10/P10),"")</f>
@@ -2825,59 +2810,59 @@
       </c>
       <c r="B37" s="4">
         <f>IFERROR(IF(B11="","",B11/A11),"")</f>
-        <v>0</v>
+        <v>2.0292</v>
       </c>
       <c r="C37" s="4">
         <f>IFERROR(IF(C11="","",C11/B11),"")</f>
-        <v>0</v>
+        <v>1.3021</v>
       </c>
       <c r="D37" s="4">
         <f>IFERROR(IF(D11="","",D11/C11),"")</f>
-        <v>0</v>
+        <v>1.1619</v>
       </c>
       <c r="E37" s="4">
         <f>IFERROR(IF(E11="","",E11/D11),"")</f>
-        <v>0</v>
+        <v>1.1184</v>
       </c>
       <c r="F37" s="4">
         <f>IFERROR(IF(F11="","",F11/E11),"")</f>
-        <v>0</v>
+        <v>0.9893</v>
       </c>
       <c r="G37" s="4">
         <f>IFERROR(IF(G11="","",G11/F11),"")</f>
-        <v>0</v>
+        <v>1.0396</v>
       </c>
       <c r="H37" s="4">
         <f>IFERROR(IF(H11="","",H11/G11),"")</f>
-        <v>0</v>
+        <v>1.0012</v>
       </c>
       <c r="I37" s="4">
         <f>IFERROR(IF(I11="","",I11/H11),"")</f>
-        <v>0</v>
+        <v>0.9953</v>
       </c>
       <c r="J37" s="4">
         <f>IFERROR(IF(J11="","",J11/I11),"")</f>
-        <v>0</v>
+        <v>1.0006</v>
       </c>
       <c r="K37" s="4">
         <f>IFERROR(IF(K11="","",K11/J11),"")</f>
-        <v>0</v>
+        <v>1.0008</v>
       </c>
       <c r="L37" s="4">
         <f>IFERROR(IF(L11="","",L11/K11),"")</f>
-        <v>0</v>
+        <v>1.0001</v>
       </c>
       <c r="M37" s="4">
         <f>IFERROR(IF(M11="","",M11/L11),"")</f>
-        <v>0</v>
+        <v>1.0013</v>
       </c>
       <c r="N37" s="4">
         <f>IFERROR(IF(N11="","",N11/M11),"")</f>
-        <v>0</v>
+        <v>0.9998</v>
       </c>
       <c r="O37" s="4">
         <f>IFERROR(IF(O11="","",O11/N11),"")</f>
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="P37" s="4">
         <f>IFERROR(IF(P11="","",P11/O11),"")</f>
@@ -2922,55 +2907,55 @@
       </c>
       <c r="B38" s="4">
         <f>IFERROR(IF(B12="","",B12/A12),"")</f>
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="C38" s="4">
         <f>IFERROR(IF(C12="","",C12/B12),"")</f>
-        <v>0</v>
+        <v>1.4748</v>
       </c>
       <c r="D38" s="4">
         <f>IFERROR(IF(D12="","",D12/C12),"")</f>
-        <v>0</v>
+        <v>1.1547</v>
       </c>
       <c r="E38" s="4">
         <f>IFERROR(IF(E12="","",E12/D12),"")</f>
-        <v>0</v>
+        <v>1.067</v>
       </c>
       <c r="F38" s="4">
         <f>IFERROR(IF(F12="","",F12/E12),"")</f>
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="G38" s="4">
         <f>IFERROR(IF(G12="","",G12/F12),"")</f>
-        <v>0</v>
+        <v>1.0553</v>
       </c>
       <c r="H38" s="4">
         <f>IFERROR(IF(H12="","",H12/G12),"")</f>
-        <v>0</v>
+        <v>1.0001</v>
       </c>
       <c r="I38" s="4">
         <f>IFERROR(IF(I12="","",I12/H12),"")</f>
-        <v>0</v>
+        <v>1.0138</v>
       </c>
       <c r="J38" s="4">
         <f>IFERROR(IF(J12="","",J12/I12),"")</f>
-        <v>0</v>
+        <v>1.0038</v>
       </c>
       <c r="K38" s="4">
         <f>IFERROR(IF(K12="","",K12/J12),"")</f>
-        <v>0</v>
+        <v>1.0282</v>
       </c>
       <c r="L38" s="4">
         <f>IFERROR(IF(L12="","",L12/K12),"")</f>
-        <v>0</v>
+        <v>0.9969</v>
       </c>
       <c r="M38" s="4">
         <f>IFERROR(IF(M12="","",M12/L12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N38" s="4">
         <f>IFERROR(IF(N12="","",N12/M12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O38" s="4">
         <f>IFERROR(IF(O12="","",O12/N12),"")</f>
@@ -3019,51 +3004,51 @@
       </c>
       <c r="B39" s="4">
         <f>IFERROR(IF(B13="","",B13/A13),"")</f>
-        <v>0</v>
+        <v>2.0319</v>
       </c>
       <c r="C39" s="4">
         <f>IFERROR(IF(C13="","",C13/B13),"")</f>
-        <v>0</v>
+        <v>1.307</v>
       </c>
       <c r="D39" s="4">
         <f>IFERROR(IF(D13="","",D13/C13),"")</f>
-        <v>0</v>
+        <v>1.0868</v>
       </c>
       <c r="E39" s="4">
         <f>IFERROR(IF(E13="","",E13/D13),"")</f>
-        <v>0</v>
+        <v>0.9969</v>
       </c>
       <c r="F39" s="4">
         <f>IFERROR(IF(F13="","",F13/E13),"")</f>
-        <v>0</v>
+        <v>1.0088</v>
       </c>
       <c r="G39" s="4">
         <f>IFERROR(IF(G13="","",G13/F13),"")</f>
-        <v>0</v>
+        <v>1.004</v>
       </c>
       <c r="H39" s="4">
         <f>IFERROR(IF(H13="","",H13/G13),"")</f>
-        <v>0</v>
+        <v>1.0516</v>
       </c>
       <c r="I39" s="4">
         <f>IFERROR(IF(I13="","",I13/H13),"")</f>
-        <v>0</v>
+        <v>1.0559</v>
       </c>
       <c r="J39" s="4">
         <f>IFERROR(IF(J13="","",J13/I13),"")</f>
-        <v>0</v>
+        <v>1.0565</v>
       </c>
       <c r="K39" s="4">
         <f>IFERROR(IF(K13="","",K13/J13),"")</f>
-        <v>0</v>
+        <v>1.0075</v>
       </c>
       <c r="L39" s="4">
         <f>IFERROR(IF(L13="","",L13/K13),"")</f>
-        <v>0</v>
+        <v>1.179</v>
       </c>
       <c r="M39" s="4">
         <f>IFERROR(IF(M13="","",M13/L13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N39" s="4">
         <f>IFERROR(IF(N13="","",N13/M13),"")</f>
@@ -3116,47 +3101,47 @@
       </c>
       <c r="B40" s="4">
         <f>IFERROR(IF(B14="","",B14/A14),"")</f>
-        <v>0</v>
+        <v>1.8261</v>
       </c>
       <c r="C40" s="4">
         <f>IFERROR(IF(C14="","",C14/B14),"")</f>
-        <v>0</v>
+        <v>1.0872</v>
       </c>
       <c r="D40" s="4">
         <f>IFERROR(IF(D14="","",D14/C14),"")</f>
-        <v>0</v>
+        <v>1.2056</v>
       </c>
       <c r="E40" s="4">
         <f>IFERROR(IF(E14="","",E14/D14),"")</f>
-        <v>0</v>
+        <v>1.0608</v>
       </c>
       <c r="F40" s="4">
         <f>IFERROR(IF(F14="","",F14/E14),"")</f>
-        <v>0</v>
+        <v>0.9974</v>
       </c>
       <c r="G40" s="4">
         <f>IFERROR(IF(G14="","",G14/F14),"")</f>
-        <v>0</v>
+        <v>1.0005</v>
       </c>
       <c r="H40" s="4">
         <f>IFERROR(IF(H14="","",H14/G14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I40" s="4">
         <f>IFERROR(IF(I14="","",I14/H14),"")</f>
-        <v>0</v>
+        <v>1.0019</v>
       </c>
       <c r="J40" s="4">
         <f>IFERROR(IF(J14="","",J14/I14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K40" s="4">
         <f>IFERROR(IF(K14="","",K14/J14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L40" s="4">
         <f>IFERROR(IF(L14="","",L14/K14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M40" s="4">
         <f>IFERROR(IF(M14="","",M14/L14),"")</f>
@@ -3213,43 +3198,43 @@
       </c>
       <c r="B41" s="4">
         <f>IFERROR(IF(B15="","",B15/A15),"")</f>
-        <v>0</v>
+        <v>1.3662</v>
       </c>
       <c r="C41" s="4">
         <f>IFERROR(IF(C15="","",C15/B15),"")</f>
-        <v>0</v>
+        <v>1.4116</v>
       </c>
       <c r="D41" s="4">
         <f>IFERROR(IF(D15="","",D15/C15),"")</f>
-        <v>0</v>
+        <v>1.1563</v>
       </c>
       <c r="E41" s="4">
         <f>IFERROR(IF(E15="","",E15/D15),"")</f>
-        <v>0</v>
+        <v>1.0143</v>
       </c>
       <c r="F41" s="4">
         <f>IFERROR(IF(F15="","",F15/E15),"")</f>
-        <v>0</v>
+        <v>1.0345</v>
       </c>
       <c r="G41" s="4">
         <f>IFERROR(IF(G15="","",G15/F15),"")</f>
-        <v>0</v>
+        <v>0.9714</v>
       </c>
       <c r="H41" s="4">
         <f>IFERROR(IF(H15="","",H15/G15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I41" s="4">
         <f>IFERROR(IF(I15="","",I15/H15),"")</f>
-        <v>0</v>
+        <v>1.0411</v>
       </c>
       <c r="J41" s="4">
         <f>IFERROR(IF(J15="","",J15/I15),"")</f>
-        <v>0</v>
+        <v>1.0206</v>
       </c>
       <c r="K41" s="4">
         <f>IFERROR(IF(K15="","",K15/J15),"")</f>
-        <v>0</v>
+        <v>0.9931</v>
       </c>
       <c r="L41" s="4">
         <f>IFERROR(IF(L15="","",L15/K15),"")</f>
@@ -3310,39 +3295,39 @@
       </c>
       <c r="B42" s="4">
         <f>IFERROR(IF(B16="","",B16/A16),"")</f>
-        <v>0</v>
+        <v>1.9857</v>
       </c>
       <c r="C42" s="4">
         <f>IFERROR(IF(C16="","",C16/B16),"")</f>
-        <v>0</v>
+        <v>1.5027</v>
       </c>
       <c r="D42" s="4">
         <f>IFERROR(IF(D16="","",D16/C16),"")</f>
-        <v>0</v>
+        <v>1.3285</v>
       </c>
       <c r="E42" s="4">
         <f>IFERROR(IF(E16="","",E16/D16),"")</f>
-        <v>0</v>
+        <v>1.1059</v>
       </c>
       <c r="F42" s="4">
         <f>IFERROR(IF(F16="","",F16/E16),"")</f>
-        <v>0</v>
+        <v>1.1362</v>
       </c>
       <c r="G42" s="4">
         <f>IFERROR(IF(G16="","",G16/F16),"")</f>
-        <v>0</v>
+        <v>1.1399</v>
       </c>
       <c r="H42" s="4">
         <f>IFERROR(IF(H16="","",H16/G16),"")</f>
-        <v>0</v>
+        <v>1.0068</v>
       </c>
       <c r="I42" s="4">
         <f>IFERROR(IF(I16="","",I16/H16),"")</f>
-        <v>0</v>
+        <v>1.0033</v>
       </c>
       <c r="J42" s="4">
         <f>IFERROR(IF(J16="","",J16/I16),"")</f>
-        <v>0</v>
+        <v>1.0962</v>
       </c>
       <c r="K42" s="4">
         <f>IFERROR(IF(K16="","",K16/J16),"")</f>
@@ -3407,35 +3392,35 @@
       </c>
       <c r="B43" s="4">
         <f>IFERROR(IF(B17="","",B17/A17),"")</f>
-        <v>0</v>
+        <v>1.8697</v>
       </c>
       <c r="C43" s="4">
         <f>IFERROR(IF(C17="","",C17/B17),"")</f>
-        <v>0</v>
+        <v>1.348</v>
       </c>
       <c r="D43" s="4">
         <f>IFERROR(IF(D17="","",D17/C17),"")</f>
-        <v>0</v>
+        <v>1.087</v>
       </c>
       <c r="E43" s="4">
         <f>IFERROR(IF(E17="","",E17/D17),"")</f>
-        <v>0</v>
+        <v>1.1423</v>
       </c>
       <c r="F43" s="4">
         <f>IFERROR(IF(F17="","",F17/E17),"")</f>
-        <v>0</v>
+        <v>1.0316</v>
       </c>
       <c r="G43" s="4">
         <f>IFERROR(IF(G17="","",G17/F17),"")</f>
-        <v>0</v>
+        <v>1.1275</v>
       </c>
       <c r="H43" s="4">
         <f>IFERROR(IF(H17="","",H17/G17),"")</f>
-        <v>0</v>
+        <v>0.9998</v>
       </c>
       <c r="I43" s="4">
         <f>IFERROR(IF(I17="","",I17/H17),"")</f>
-        <v>0</v>
+        <v>1.0013</v>
       </c>
       <c r="J43" s="4">
         <f>IFERROR(IF(J17="","",J17/I17),"")</f>
@@ -3504,31 +3489,31 @@
       </c>
       <c r="B44" s="4">
         <f>IFERROR(IF(B18="","",B18/A18),"")</f>
-        <v>0</v>
+        <v>1.3328</v>
       </c>
       <c r="C44" s="4">
         <f>IFERROR(IF(C18="","",C18/B18),"")</f>
-        <v>0</v>
+        <v>1.0344</v>
       </c>
       <c r="D44" s="4">
         <f>IFERROR(IF(D18="","",D18/C18),"")</f>
-        <v>0</v>
+        <v>1.3094</v>
       </c>
       <c r="E44" s="4">
         <f>IFERROR(IF(E18="","",E18/D18),"")</f>
-        <v>0</v>
+        <v>1.0751</v>
       </c>
       <c r="F44" s="4">
         <f>IFERROR(IF(F18="","",F18/E18),"")</f>
-        <v>0</v>
+        <v>1.1327</v>
       </c>
       <c r="G44" s="4">
         <f>IFERROR(IF(G18="","",G18/F18),"")</f>
-        <v>0</v>
+        <v>1.1527</v>
       </c>
       <c r="H44" s="4">
         <f>IFERROR(IF(H18="","",H18/G18),"")</f>
-        <v>0</v>
+        <v>1.0315</v>
       </c>
       <c r="I44" s="4">
         <f>IFERROR(IF(I18="","",I18/H18),"")</f>
@@ -3601,27 +3586,27 @@
       </c>
       <c r="B45" s="4">
         <f>IFERROR(IF(B19="","",B19/A19),"")</f>
-        <v>0</v>
+        <v>2.2994</v>
       </c>
       <c r="C45" s="4">
         <f>IFERROR(IF(C19="","",C19/B19),"")</f>
-        <v>0</v>
+        <v>1.4287</v>
       </c>
       <c r="D45" s="4">
         <f>IFERROR(IF(D19="","",D19/C19),"")</f>
-        <v>0</v>
+        <v>1.3883</v>
       </c>
       <c r="E45" s="4">
         <f>IFERROR(IF(E19="","",E19/D19),"")</f>
-        <v>0</v>
+        <v>0.9943</v>
       </c>
       <c r="F45" s="4">
         <f>IFERROR(IF(F19="","",F19/E19),"")</f>
-        <v>0</v>
+        <v>1.0131</v>
       </c>
       <c r="G45" s="4">
         <f>IFERROR(IF(G19="","",G19/F19),"")</f>
-        <v>0</v>
+        <v>1.0265</v>
       </c>
       <c r="H45" s="4">
         <f>IFERROR(IF(H19="","",H19/G19),"")</f>
@@ -3698,23 +3683,23 @@
       </c>
       <c r="B46" s="4">
         <f>IFERROR(IF(B20="","",B20/A20),"")</f>
-        <v>0</v>
+        <v>2.757</v>
       </c>
       <c r="C46" s="4">
         <f>IFERROR(IF(C20="","",C20/B20),"")</f>
-        <v>0</v>
+        <v>1.5473</v>
       </c>
       <c r="D46" s="4">
         <f>IFERROR(IF(D20="","",D20/C20),"")</f>
-        <v>0</v>
+        <v>1.1497</v>
       </c>
       <c r="E46" s="4">
         <f>IFERROR(IF(E20="","",E20/D20),"")</f>
-        <v>0</v>
+        <v>1.0634</v>
       </c>
       <c r="F46" s="4">
         <f>IFERROR(IF(F20="","",F20/E20),"")</f>
-        <v>0</v>
+        <v>1.2221</v>
       </c>
       <c r="G46" s="4">
         <f>IFERROR(IF(G20="","",G20/F20),"")</f>
@@ -3795,19 +3780,19 @@
       </c>
       <c r="B47" s="4">
         <f>IFERROR(IF(B21="","",B21/A21),"")</f>
-        <v>0</v>
+        <v>1.7849</v>
       </c>
       <c r="C47" s="4">
         <f>IFERROR(IF(C21="","",C21/B21),"")</f>
-        <v>0</v>
+        <v>0.9832</v>
       </c>
       <c r="D47" s="4">
         <f>IFERROR(IF(D21="","",D21/C21),"")</f>
-        <v>0</v>
+        <v>1.058</v>
       </c>
       <c r="E47" s="4">
         <f>IFERROR(IF(E21="","",E21/D21),"")</f>
-        <v>0</v>
+        <v>1.0097</v>
       </c>
       <c r="F47" s="4">
         <f>IFERROR(IF(F21="","",F21/E21),"")</f>
@@ -3892,15 +3877,15 @@
       </c>
       <c r="B48" s="4">
         <f>IFERROR(IF(B22="","",B22/A22),"")</f>
-        <v>0</v>
+        <v>1.4577</v>
       </c>
       <c r="C48" s="4">
         <f>IFERROR(IF(C22="","",C22/B22),"")</f>
-        <v>0</v>
+        <v>1.224</v>
       </c>
       <c r="D48" s="4">
         <f>IFERROR(IF(D22="","",D22/C22),"")</f>
-        <v>0</v>
+        <v>1.0316</v>
       </c>
       <c r="E48" s="4">
         <f>IFERROR(IF(E22="","",E22/D22),"")</f>
@@ -3989,11 +3974,11 @@
       </c>
       <c r="B49" s="4">
         <f>IFERROR(IF(B23="","",B23/A23),"")</f>
-        <v>0</v>
+        <v>1.2261</v>
       </c>
       <c r="C49" s="4">
         <f>IFERROR(IF(C23="","",C23/B23),"")</f>
-        <v>0</v>
+        <v>0.9715</v>
       </c>
       <c r="D49" s="4">
         <f>IFERROR(IF(D23="","",D23/C23),"")</f>
@@ -4086,7 +4071,7 @@
       </c>
       <c r="B50" s="4">
         <f>IFERROR(IF(B24="","",B24/A24),"")</f>
-        <v>0</v>
+        <v>1.6941</v>
       </c>
       <c r="C50" s="4">
         <f>IFERROR(IF(C24="","",C24/B24),"")</f>
@@ -6946,95 +6931,95 @@
       </c>
       <c r="B28" s="4">
         <f>IFERROR(IF(B2="","",B2/A2),"")</f>
-        <v>0</v>
+        <v>3.2124</v>
       </c>
       <c r="C28" s="4">
         <f>IFERROR(IF(C2="","",C2/B2),"")</f>
-        <v>0</v>
+        <v>1.4758</v>
       </c>
       <c r="D28" s="4">
         <f>IFERROR(IF(D2="","",D2/C2),"")</f>
-        <v>0</v>
+        <v>1.2363</v>
       </c>
       <c r="E28" s="4">
         <f>IFERROR(IF(E2="","",E2/D2),"")</f>
-        <v>0</v>
+        <v>1.1639</v>
       </c>
       <c r="F28" s="4">
         <f>IFERROR(IF(F2="","",F2/E2),"")</f>
-        <v>0</v>
+        <v>1.0268</v>
       </c>
       <c r="G28" s="4">
         <f>IFERROR(IF(G2="","",G2/F2),"")</f>
-        <v>0</v>
+        <v>0.9904</v>
       </c>
       <c r="H28" s="4">
         <f>IFERROR(IF(H2="","",H2/G2),"")</f>
-        <v>0</v>
+        <v>1.0135</v>
       </c>
       <c r="I28" s="4">
         <f>IFERROR(IF(I2="","",I2/H2),"")</f>
-        <v>0</v>
+        <v>1.0097</v>
       </c>
       <c r="J28" s="4">
         <f>IFERROR(IF(J2="","",J2/I2),"")</f>
-        <v>0</v>
+        <v>1.012</v>
       </c>
       <c r="K28" s="4">
         <f>IFERROR(IF(K2="","",K2/J2),"")</f>
-        <v>0</v>
+        <v>1.0238</v>
       </c>
       <c r="L28" s="4">
         <f>IFERROR(IF(L2="","",L2/K2),"")</f>
-        <v>0</v>
+        <v>1.024</v>
       </c>
       <c r="M28" s="4">
         <f>IFERROR(IF(M2="","",M2/L2),"")</f>
-        <v>0</v>
+        <v>1.0163</v>
       </c>
       <c r="N28" s="4">
         <f>IFERROR(IF(N2="","",N2/M2),"")</f>
-        <v>0</v>
+        <v>1.0254</v>
       </c>
       <c r="O28" s="4">
         <f>IFERROR(IF(O2="","",O2/N2),"")</f>
-        <v>0</v>
+        <v>1.0215</v>
       </c>
       <c r="P28" s="4">
         <f>IFERROR(IF(P2="","",P2/O2),"")</f>
-        <v>0</v>
+        <v>1.0307</v>
       </c>
       <c r="Q28" s="4">
         <f>IFERROR(IF(Q2="","",Q2/P2),"")</f>
-        <v>0</v>
+        <v>1.0327</v>
       </c>
       <c r="R28" s="4">
         <f>IFERROR(IF(R2="","",R2/Q2),"")</f>
-        <v>0</v>
+        <v>1.027</v>
       </c>
       <c r="S28" s="4">
         <f>IFERROR(IF(S2="","",S2/R2),"")</f>
-        <v>0</v>
+        <v>1.0383</v>
       </c>
       <c r="T28" s="4">
         <f>IFERROR(IF(T2="","",T2/S2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U28" s="4">
         <f>IFERROR(IF(U2="","",U2/T2),"")</f>
-        <v>0</v>
+        <v>1.0074</v>
       </c>
       <c r="V28" s="4">
         <f>IFERROR(IF(V2="","",V2/U2),"")</f>
-        <v>0</v>
+        <v>1.0074</v>
       </c>
       <c r="W28" s="4">
         <f>IFERROR(IF(W2="","",W2/V2),"")</f>
-        <v>0</v>
+        <v>1.0063</v>
       </c>
       <c r="X28" s="4">
         <f>IFERROR(IF(X2="","",X2/W2),"")</f>
-        <v>0</v>
+        <v>1.0039</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -7043,91 +7028,91 @@
       </c>
       <c r="B29" s="4">
         <f>IFERROR(IF(B3="","",B3/A3),"")</f>
-        <v>0</v>
+        <v>2.5494</v>
       </c>
       <c r="C29" s="4">
         <f>IFERROR(IF(C3="","",C3/B3),"")</f>
-        <v>0</v>
+        <v>1.3395</v>
       </c>
       <c r="D29" s="4">
         <f>IFERROR(IF(D3="","",D3/C3),"")</f>
-        <v>0</v>
+        <v>1.0803</v>
       </c>
       <c r="E29" s="4">
         <f>IFERROR(IF(E3="","",E3/D3),"")</f>
-        <v>0</v>
+        <v>1.1252</v>
       </c>
       <c r="F29" s="4">
         <f>IFERROR(IF(F3="","",F3/E3),"")</f>
-        <v>0</v>
+        <v>1.0932</v>
       </c>
       <c r="G29" s="4">
         <f>IFERROR(IF(G3="","",G3/F3),"")</f>
-        <v>0</v>
+        <v>1.0226</v>
       </c>
       <c r="H29" s="4">
         <f>IFERROR(IF(H3="","",H3/G3),"")</f>
-        <v>0</v>
+        <v>1.0177</v>
       </c>
       <c r="I29" s="4">
         <f>IFERROR(IF(I3="","",I3/H3),"")</f>
-        <v>0</v>
+        <v>1.0248</v>
       </c>
       <c r="J29" s="4">
         <f>IFERROR(IF(J3="","",J3/I3),"")</f>
-        <v>0</v>
+        <v>1.0119</v>
       </c>
       <c r="K29" s="4">
         <f>IFERROR(IF(K3="","",K3/J3),"")</f>
-        <v>0</v>
+        <v>1.0176</v>
       </c>
       <c r="L29" s="4">
         <f>IFERROR(IF(L3="","",L3/K3),"")</f>
-        <v>0</v>
+        <v>1.0188</v>
       </c>
       <c r="M29" s="4">
         <f>IFERROR(IF(M3="","",M3/L3),"")</f>
-        <v>0</v>
+        <v>1.0229</v>
       </c>
       <c r="N29" s="4">
         <f>IFERROR(IF(N3="","",N3/M3),"")</f>
-        <v>0</v>
+        <v>1.0255</v>
       </c>
       <c r="O29" s="4">
         <f>IFERROR(IF(O3="","",O3/N3),"")</f>
-        <v>0</v>
+        <v>1.0211</v>
       </c>
       <c r="P29" s="4">
         <f>IFERROR(IF(P3="","",P3/O3),"")</f>
-        <v>0</v>
+        <v>1.0195</v>
       </c>
       <c r="Q29" s="4">
         <f>IFERROR(IF(Q3="","",Q3/P3),"")</f>
-        <v>0</v>
+        <v>1.0285</v>
       </c>
       <c r="R29" s="4">
         <f>IFERROR(IF(R3="","",R3/Q3),"")</f>
-        <v>0</v>
+        <v>1.0202</v>
       </c>
       <c r="S29" s="4">
         <f>IFERROR(IF(S3="","",S3/R3),"")</f>
-        <v>0</v>
+        <v>1.0159</v>
       </c>
       <c r="T29" s="4">
         <f>IFERROR(IF(T3="","",T3/S3),"")</f>
-        <v>0</v>
+        <v>1.0121</v>
       </c>
       <c r="U29" s="4">
         <f>IFERROR(IF(U3="","",U3/T3),"")</f>
-        <v>0</v>
+        <v>1.0101</v>
       </c>
       <c r="V29" s="4">
         <f>IFERROR(IF(V3="","",V3/U3),"")</f>
-        <v>0</v>
+        <v>1.0096</v>
       </c>
       <c r="W29" s="4">
         <f>IFERROR(IF(W3="","",W3/V3),"")</f>
-        <v>0</v>
+        <v>1.009</v>
       </c>
       <c r="X29" s="4">
         <f>IFERROR(IF(X3="","",X3/W3),"")</f>
@@ -7140,87 +7125,87 @@
       </c>
       <c r="B30" s="4">
         <f>IFERROR(IF(B4="","",B4/A4),"")</f>
-        <v>0</v>
+        <v>2.4837</v>
       </c>
       <c r="C30" s="4">
         <f>IFERROR(IF(C4="","",C4/B4),"")</f>
-        <v>0</v>
+        <v>1.1544</v>
       </c>
       <c r="D30" s="4">
         <f>IFERROR(IF(D4="","",D4/C4),"")</f>
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="E30" s="4">
         <f>IFERROR(IF(E4="","",E4/D4),"")</f>
-        <v>0</v>
+        <v>1.157</v>
       </c>
       <c r="F30" s="4">
         <f>IFERROR(IF(F4="","",F4/E4),"")</f>
-        <v>0</v>
+        <v>1.0498</v>
       </c>
       <c r="G30" s="4">
         <f>IFERROR(IF(G4="","",G4/F4),"")</f>
-        <v>0</v>
+        <v>1.0015</v>
       </c>
       <c r="H30" s="4">
         <f>IFERROR(IF(H4="","",H4/G4),"")</f>
-        <v>0</v>
+        <v>1.007</v>
       </c>
       <c r="I30" s="4">
         <f>IFERROR(IF(I4="","",I4/H4),"")</f>
-        <v>0</v>
+        <v>0.9986</v>
       </c>
       <c r="J30" s="4">
         <f>IFERROR(IF(J4="","",J4/I4),"")</f>
-        <v>0</v>
+        <v>1.0024</v>
       </c>
       <c r="K30" s="4">
         <f>IFERROR(IF(K4="","",K4/J4),"")</f>
-        <v>0</v>
+        <v>0.9981</v>
       </c>
       <c r="L30" s="4">
         <f>IFERROR(IF(L4="","",L4/K4),"")</f>
-        <v>0</v>
+        <v>1.0002</v>
       </c>
       <c r="M30" s="4">
         <f>IFERROR(IF(M4="","",M4/L4),"")</f>
-        <v>0</v>
+        <v>1.0001</v>
       </c>
       <c r="N30" s="4">
         <f>IFERROR(IF(N4="","",N4/M4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O30" s="4">
         <f>IFERROR(IF(O4="","",O4/N4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P30" s="4">
         <f>IFERROR(IF(P4="","",P4/O4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q30" s="4">
         <f>IFERROR(IF(Q4="","",Q4/P4),"")</f>
-        <v>0</v>
+        <v>1.0021</v>
       </c>
       <c r="R30" s="4">
         <f>IFERROR(IF(R4="","",R4/Q4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S30" s="4">
         <f>IFERROR(IF(S4="","",S4/R4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T30" s="4">
         <f>IFERROR(IF(T4="","",T4/S4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U30" s="4">
         <f>IFERROR(IF(U4="","",U4/T4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="V30" s="4">
         <f>IFERROR(IF(V4="","",V4/U4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="W30" s="4">
         <f>IFERROR(IF(W4="","",W4/V4),"")</f>
@@ -7237,83 +7222,83 @@
       </c>
       <c r="B31" s="4">
         <f>IFERROR(IF(B5="","",B5/A5),"")</f>
-        <v>0</v>
+        <v>2.4368</v>
       </c>
       <c r="C31" s="4">
         <f>IFERROR(IF(C5="","",C5/B5),"")</f>
-        <v>0</v>
+        <v>1.2891</v>
       </c>
       <c r="D31" s="4">
         <f>IFERROR(IF(D5="","",D5/C5),"")</f>
-        <v>0</v>
+        <v>1.1198</v>
       </c>
       <c r="E31" s="4">
         <f>IFERROR(IF(E5="","",E5/D5),"")</f>
-        <v>0</v>
+        <v>1.1677</v>
       </c>
       <c r="F31" s="4">
         <f>IFERROR(IF(F5="","",F5/E5),"")</f>
-        <v>0</v>
+        <v>1.0037</v>
       </c>
       <c r="G31" s="4">
         <f>IFERROR(IF(G5="","",G5/F5),"")</f>
-        <v>0</v>
+        <v>1.0163</v>
       </c>
       <c r="H31" s="4">
         <f>IFERROR(IF(H5="","",H5/G5),"")</f>
-        <v>0</v>
+        <v>1.0078</v>
       </c>
       <c r="I31" s="4">
         <f>IFERROR(IF(I5="","",I5/H5),"")</f>
-        <v>0</v>
+        <v>1.0185</v>
       </c>
       <c r="J31" s="4">
         <f>IFERROR(IF(J5="","",J5/I5),"")</f>
-        <v>0</v>
+        <v>0.9939</v>
       </c>
       <c r="K31" s="4">
         <f>IFERROR(IF(K5="","",K5/J5),"")</f>
-        <v>0</v>
+        <v>1.0036</v>
       </c>
       <c r="L31" s="4">
         <f>IFERROR(IF(L5="","",L5/K5),"")</f>
-        <v>0</v>
+        <v>1.0064</v>
       </c>
       <c r="M31" s="4">
         <f>IFERROR(IF(M5="","",M5/L5),"")</f>
-        <v>0</v>
+        <v>1.0004</v>
       </c>
       <c r="N31" s="4">
         <f>IFERROR(IF(N5="","",N5/M5),"")</f>
-        <v>0</v>
+        <v>1.0018</v>
       </c>
       <c r="O31" s="4">
         <f>IFERROR(IF(O5="","",O5/N5),"")</f>
-        <v>0</v>
+        <v>1.0006</v>
       </c>
       <c r="P31" s="4">
         <f>IFERROR(IF(P5="","",P5/O5),"")</f>
-        <v>0</v>
+        <v>1.0095</v>
       </c>
       <c r="Q31" s="4">
         <f>IFERROR(IF(Q5="","",Q5/P5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R31" s="4">
         <f>IFERROR(IF(R5="","",R5/Q5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S31" s="4">
         <f>IFERROR(IF(S5="","",S5/R5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T31" s="4">
         <f>IFERROR(IF(T5="","",T5/S5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U31" s="4">
         <f>IFERROR(IF(U5="","",U5/T5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="V31" s="4">
         <f>IFERROR(IF(V5="","",V5/U5),"")</f>
@@ -7334,79 +7319,79 @@
       </c>
       <c r="B32" s="4">
         <f>IFERROR(IF(B6="","",B6/A6),"")</f>
-        <v>0</v>
+        <v>2.0311</v>
       </c>
       <c r="C32" s="4">
         <f>IFERROR(IF(C6="","",C6/B6),"")</f>
-        <v>0</v>
+        <v>1.2674</v>
       </c>
       <c r="D32" s="4">
         <f>IFERROR(IF(D6="","",D6/C6),"")</f>
-        <v>0</v>
+        <v>1.0439</v>
       </c>
       <c r="E32" s="4">
         <f>IFERROR(IF(E6="","",E6/D6),"")</f>
-        <v>0</v>
+        <v>1.0747</v>
       </c>
       <c r="F32" s="4">
         <f>IFERROR(IF(F6="","",F6/E6),"")</f>
-        <v>0</v>
+        <v>1.0208</v>
       </c>
       <c r="G32" s="4">
         <f>IFERROR(IF(G6="","",G6/F6),"")</f>
-        <v>0</v>
+        <v>1.0211</v>
       </c>
       <c r="H32" s="4">
         <f>IFERROR(IF(H6="","",H6/G6),"")</f>
-        <v>0</v>
+        <v>1.0104</v>
       </c>
       <c r="I32" s="4">
         <f>IFERROR(IF(I6="","",I6/H6),"")</f>
-        <v>0</v>
+        <v>1.0042</v>
       </c>
       <c r="J32" s="4">
         <f>IFERROR(IF(J6="","",J6/I6),"")</f>
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K32" s="4">
         <f>IFERROR(IF(K6="","",K6/J6),"")</f>
-        <v>0</v>
+        <v>1.0284</v>
       </c>
       <c r="L32" s="4">
         <f>IFERROR(IF(L6="","",L6/K6),"")</f>
-        <v>0</v>
+        <v>1.0203</v>
       </c>
       <c r="M32" s="4">
         <f>IFERROR(IF(M6="","",M6/L6),"")</f>
-        <v>0</v>
+        <v>1.0327</v>
       </c>
       <c r="N32" s="4">
         <f>IFERROR(IF(N6="","",N6/M6),"")</f>
-        <v>0</v>
+        <v>1.0189</v>
       </c>
       <c r="O32" s="4">
         <f>IFERROR(IF(O6="","",O6/N6),"")</f>
-        <v>0</v>
+        <v>1.0301</v>
       </c>
       <c r="P32" s="4">
         <f>IFERROR(IF(P6="","",P6/O6),"")</f>
-        <v>0</v>
+        <v>1.008</v>
       </c>
       <c r="Q32" s="4">
         <f>IFERROR(IF(Q6="","",Q6/P6),"")</f>
-        <v>0</v>
+        <v>1.0193</v>
       </c>
       <c r="R32" s="4">
         <f>IFERROR(IF(R6="","",R6/Q6),"")</f>
-        <v>0</v>
+        <v>1.0017</v>
       </c>
       <c r="S32" s="4">
         <f>IFERROR(IF(S6="","",S6/R6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T32" s="4">
         <f>IFERROR(IF(T6="","",T6/S6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U32" s="4">
         <f>IFERROR(IF(U6="","",U6/T6),"")</f>
@@ -7431,75 +7416,75 @@
       </c>
       <c r="B33" s="4">
         <f>IFERROR(IF(B7="","",B7/A7),"")</f>
-        <v>0</v>
+        <v>2.4565</v>
       </c>
       <c r="C33" s="4">
         <f>IFERROR(IF(C7="","",C7/B7),"")</f>
-        <v>0</v>
+        <v>1.2768</v>
       </c>
       <c r="D33" s="4">
         <f>IFERROR(IF(D7="","",D7/C7),"")</f>
-        <v>0</v>
+        <v>1.0891</v>
       </c>
       <c r="E33" s="4">
         <f>IFERROR(IF(E7="","",E7/D7),"")</f>
-        <v>0</v>
+        <v>1.0612</v>
       </c>
       <c r="F33" s="4">
         <f>IFERROR(IF(F7="","",F7/E7),"")</f>
-        <v>0</v>
+        <v>1.0466</v>
       </c>
       <c r="G33" s="4">
         <f>IFERROR(IF(G7="","",G7/F7),"")</f>
-        <v>0</v>
+        <v>1.0414</v>
       </c>
       <c r="H33" s="4">
         <f>IFERROR(IF(H7="","",H7/G7),"")</f>
-        <v>0</v>
+        <v>1.0068</v>
       </c>
       <c r="I33" s="4">
         <f>IFERROR(IF(I7="","",I7/H7),"")</f>
-        <v>0</v>
+        <v>1.0316</v>
       </c>
       <c r="J33" s="4">
         <f>IFERROR(IF(J7="","",J7/I7),"")</f>
-        <v>0</v>
+        <v>1.041</v>
       </c>
       <c r="K33" s="4">
         <f>IFERROR(IF(K7="","",K7/J7),"")</f>
-        <v>0</v>
+        <v>1.0922</v>
       </c>
       <c r="L33" s="4">
         <f>IFERROR(IF(L7="","",L7/K7),"")</f>
-        <v>0</v>
+        <v>1.0276</v>
       </c>
       <c r="M33" s="4">
         <f>IFERROR(IF(M7="","",M7/L7),"")</f>
-        <v>0</v>
+        <v>1.0104</v>
       </c>
       <c r="N33" s="4">
         <f>IFERROR(IF(N7="","",N7/M7),"")</f>
-        <v>0</v>
+        <v>1.0187</v>
       </c>
       <c r="O33" s="4">
         <f>IFERROR(IF(O7="","",O7/N7),"")</f>
-        <v>0</v>
+        <v>1.0068</v>
       </c>
       <c r="P33" s="4">
         <f>IFERROR(IF(P7="","",P7/O7),"")</f>
-        <v>0</v>
+        <v>1.0084</v>
       </c>
       <c r="Q33" s="4">
         <f>IFERROR(IF(Q7="","",Q7/P7),"")</f>
-        <v>0</v>
+        <v>1.0115</v>
       </c>
       <c r="R33" s="4">
         <f>IFERROR(IF(R7="","",R7/Q7),"")</f>
-        <v>0</v>
+        <v>1.0076</v>
       </c>
       <c r="S33" s="4">
         <f>IFERROR(IF(S7="","",S7/R7),"")</f>
-        <v>0</v>
+        <v>1.0055</v>
       </c>
       <c r="T33" s="4">
         <f>IFERROR(IF(T7="","",T7/S7),"")</f>
@@ -7528,71 +7513,71 @@
       </c>
       <c r="B34" s="4">
         <f>IFERROR(IF(B8="","",B8/A8),"")</f>
-        <v>0</v>
+        <v>2.1908</v>
       </c>
       <c r="C34" s="4">
         <f>IFERROR(IF(C8="","",C8/B8),"")</f>
-        <v>0</v>
+        <v>1.2948</v>
       </c>
       <c r="D34" s="4">
         <f>IFERROR(IF(D8="","",D8/C8),"")</f>
-        <v>0</v>
+        <v>1.2734</v>
       </c>
       <c r="E34" s="4">
         <f>IFERROR(IF(E8="","",E8/D8),"")</f>
-        <v>0</v>
+        <v>1.1861</v>
       </c>
       <c r="F34" s="4">
         <f>IFERROR(IF(F8="","",F8/E8),"")</f>
-        <v>0</v>
+        <v>1.2146</v>
       </c>
       <c r="G34" s="4">
         <f>IFERROR(IF(G8="","",G8/F8),"")</f>
-        <v>0</v>
+        <v>1.1157</v>
       </c>
       <c r="H34" s="4">
         <f>IFERROR(IF(H8="","",H8/G8),"")</f>
-        <v>0</v>
+        <v>1.0776</v>
       </c>
       <c r="I34" s="4">
         <f>IFERROR(IF(I8="","",I8/H8),"")</f>
-        <v>0</v>
+        <v>1.0807</v>
       </c>
       <c r="J34" s="4">
         <f>IFERROR(IF(J8="","",J8/I8),"")</f>
-        <v>0</v>
+        <v>1.0849</v>
       </c>
       <c r="K34" s="4">
         <f>IFERROR(IF(K8="","",K8/J8),"")</f>
-        <v>0</v>
+        <v>1.0822</v>
       </c>
       <c r="L34" s="4">
         <f>IFERROR(IF(L8="","",L8/K8),"")</f>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="M34" s="4">
         <f>IFERROR(IF(M8="","",M8/L8),"")</f>
-        <v>0</v>
+        <v>1.041</v>
       </c>
       <c r="N34" s="4">
         <f>IFERROR(IF(N8="","",N8/M8),"")</f>
-        <v>0</v>
+        <v>1.0289</v>
       </c>
       <c r="O34" s="4">
         <f>IFERROR(IF(O8="","",O8/N8),"")</f>
-        <v>0</v>
+        <v>1.0268</v>
       </c>
       <c r="P34" s="4">
         <f>IFERROR(IF(P8="","",P8/O8),"")</f>
-        <v>0</v>
+        <v>1.0291</v>
       </c>
       <c r="Q34" s="4">
         <f>IFERROR(IF(Q8="","",Q8/P8),"")</f>
-        <v>0</v>
+        <v>1.0063</v>
       </c>
       <c r="R34" s="4">
         <f>IFERROR(IF(R8="","",R8/Q8),"")</f>
-        <v>0</v>
+        <v>1.002</v>
       </c>
       <c r="S34" s="4">
         <f>IFERROR(IF(S8="","",S8/R8),"")</f>
@@ -7625,67 +7610,67 @@
       </c>
       <c r="B35" s="4">
         <f>IFERROR(IF(B9="","",B9/A9),"")</f>
-        <v>0</v>
+        <v>1.829</v>
       </c>
       <c r="C35" s="4">
         <f>IFERROR(IF(C9="","",C9/B9),"")</f>
-        <v>0</v>
+        <v>1.345</v>
       </c>
       <c r="D35" s="4">
         <f>IFERROR(IF(D9="","",D9/C9),"")</f>
-        <v>0</v>
+        <v>1.3665</v>
       </c>
       <c r="E35" s="4">
         <f>IFERROR(IF(E9="","",E9/D9),"")</f>
-        <v>0</v>
+        <v>1.0349</v>
       </c>
       <c r="F35" s="4">
         <f>IFERROR(IF(F9="","",F9/E9),"")</f>
-        <v>0</v>
+        <v>1.0308</v>
       </c>
       <c r="G35" s="4">
         <f>IFERROR(IF(G9="","",G9/F9),"")</f>
-        <v>0</v>
+        <v>1.007</v>
       </c>
       <c r="H35" s="4">
         <f>IFERROR(IF(H9="","",H9/G9),"")</f>
-        <v>0</v>
+        <v>1.0064</v>
       </c>
       <c r="I35" s="4">
         <f>IFERROR(IF(I9="","",I9/H9),"")</f>
-        <v>0</v>
+        <v>1.0117</v>
       </c>
       <c r="J35" s="4">
         <f>IFERROR(IF(J9="","",J9/I9),"")</f>
-        <v>0</v>
+        <v>1.0134</v>
       </c>
       <c r="K35" s="4">
         <f>IFERROR(IF(K9="","",K9/J9),"")</f>
-        <v>0</v>
+        <v>1.0107</v>
       </c>
       <c r="L35" s="4">
         <f>IFERROR(IF(L9="","",L9/K9),"")</f>
-        <v>0</v>
+        <v>1.0019</v>
       </c>
       <c r="M35" s="4">
         <f>IFERROR(IF(M9="","",M9/L9),"")</f>
-        <v>0</v>
+        <v>1.0023</v>
       </c>
       <c r="N35" s="4">
         <f>IFERROR(IF(N9="","",N9/M9),"")</f>
-        <v>0</v>
+        <v>1.0011</v>
       </c>
       <c r="O35" s="4">
         <f>IFERROR(IF(O9="","",O9/N9),"")</f>
-        <v>0</v>
+        <v>1.0007</v>
       </c>
       <c r="P35" s="4">
         <f>IFERROR(IF(P9="","",P9/O9),"")</f>
-        <v>0</v>
+        <v>1.0026</v>
       </c>
       <c r="Q35" s="4">
         <f>IFERROR(IF(Q9="","",Q9/P9),"")</f>
-        <v>0</v>
+        <v>1.0264</v>
       </c>
       <c r="R35" s="4">
         <f>IFERROR(IF(R9="","",R9/Q9),"")</f>
@@ -7722,63 +7707,63 @@
       </c>
       <c r="B36" s="4">
         <f>IFERROR(IF(B10="","",B10/A10),"")</f>
-        <v>0</v>
+        <v>3.246</v>
       </c>
       <c r="C36" s="4">
         <f>IFERROR(IF(C10="","",C10/B10),"")</f>
-        <v>0</v>
+        <v>1.0939</v>
       </c>
       <c r="D36" s="4">
         <f>IFERROR(IF(D10="","",D10/C10),"")</f>
-        <v>0</v>
+        <v>1.0272</v>
       </c>
       <c r="E36" s="4">
         <f>IFERROR(IF(E10="","",E10/D10),"")</f>
-        <v>0</v>
+        <v>1.073</v>
       </c>
       <c r="F36" s="4">
         <f>IFERROR(IF(F10="","",F10/E10),"")</f>
-        <v>0</v>
+        <v>1.0515</v>
       </c>
       <c r="G36" s="4">
         <f>IFERROR(IF(G10="","",G10/F10),"")</f>
-        <v>0</v>
+        <v>1.0301</v>
       </c>
       <c r="H36" s="4">
         <f>IFERROR(IF(H10="","",H10/G10),"")</f>
-        <v>0</v>
+        <v>1.0504</v>
       </c>
       <c r="I36" s="4">
         <f>IFERROR(IF(I10="","",I10/H10),"")</f>
-        <v>0</v>
+        <v>1.0367</v>
       </c>
       <c r="J36" s="4">
         <f>IFERROR(IF(J10="","",J10/I10),"")</f>
-        <v>0</v>
+        <v>1.0147</v>
       </c>
       <c r="K36" s="4">
         <f>IFERROR(IF(K10="","",K10/J10),"")</f>
-        <v>0</v>
+        <v>1.0094</v>
       </c>
       <c r="L36" s="4">
         <f>IFERROR(IF(L10="","",L10/K10),"")</f>
-        <v>0</v>
+        <v>1.0305</v>
       </c>
       <c r="M36" s="4">
         <f>IFERROR(IF(M10="","",M10/L10),"")</f>
-        <v>0</v>
+        <v>1.0497</v>
       </c>
       <c r="N36" s="4">
         <f>IFERROR(IF(N10="","",N10/M10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O36" s="4">
         <f>IFERROR(IF(O10="","",O10/N10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P36" s="4">
         <f>IFERROR(IF(P10="","",P10/O10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q36" s="4">
         <f>IFERROR(IF(Q10="","",Q10/P10),"")</f>
@@ -7819,59 +7804,59 @@
       </c>
       <c r="B37" s="4">
         <f>IFERROR(IF(B11="","",B11/A11),"")</f>
-        <v>0</v>
+        <v>2.7631</v>
       </c>
       <c r="C37" s="4">
         <f>IFERROR(IF(C11="","",C11/B11),"")</f>
-        <v>0</v>
+        <v>1.3597</v>
       </c>
       <c r="D37" s="4">
         <f>IFERROR(IF(D11="","",D11/C11),"")</f>
-        <v>0</v>
+        <v>1.1766</v>
       </c>
       <c r="E37" s="4">
         <f>IFERROR(IF(E11="","",E11/D11),"")</f>
-        <v>0</v>
+        <v>1.0929</v>
       </c>
       <c r="F37" s="4">
         <f>IFERROR(IF(F11="","",F11/E11),"")</f>
-        <v>0</v>
+        <v>1.0209</v>
       </c>
       <c r="G37" s="4">
         <f>IFERROR(IF(G11="","",G11/F11),"")</f>
-        <v>0</v>
+        <v>1.0489</v>
       </c>
       <c r="H37" s="4">
         <f>IFERROR(IF(H11="","",H11/G11),"")</f>
-        <v>0</v>
+        <v>1.0017</v>
       </c>
       <c r="I37" s="4">
         <f>IFERROR(IF(I11="","",I11/H11),"")</f>
-        <v>0</v>
+        <v>1.0034</v>
       </c>
       <c r="J37" s="4">
         <f>IFERROR(IF(J11="","",J11/I11),"")</f>
-        <v>0</v>
+        <v>1.0006</v>
       </c>
       <c r="K37" s="4">
         <f>IFERROR(IF(K11="","",K11/J11),"")</f>
-        <v>0</v>
+        <v>1.0005</v>
       </c>
       <c r="L37" s="4">
         <f>IFERROR(IF(L11="","",L11/K11),"")</f>
-        <v>0</v>
+        <v>1.0001</v>
       </c>
       <c r="M37" s="4">
         <f>IFERROR(IF(M11="","",M11/L11),"")</f>
-        <v>0</v>
+        <v>1.0006</v>
       </c>
       <c r="N37" s="4">
         <f>IFERROR(IF(N11="","",N11/M11),"")</f>
-        <v>0</v>
+        <v>1.0007</v>
       </c>
       <c r="O37" s="4">
         <f>IFERROR(IF(O11="","",O11/N11),"")</f>
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="P37" s="4">
         <f>IFERROR(IF(P11="","",P11/O11),"")</f>
@@ -7916,55 +7901,55 @@
       </c>
       <c r="B38" s="4">
         <f>IFERROR(IF(B12="","",B12/A12),"")</f>
-        <v>0</v>
+        <v>2.3046</v>
       </c>
       <c r="C38" s="4">
         <f>IFERROR(IF(C12="","",C12/B12),"")</f>
-        <v>0</v>
+        <v>1.5589</v>
       </c>
       <c r="D38" s="4">
         <f>IFERROR(IF(D12="","",D12/C12),"")</f>
-        <v>0</v>
+        <v>1.0755</v>
       </c>
       <c r="E38" s="4">
         <f>IFERROR(IF(E12="","",E12/D12),"")</f>
-        <v>0</v>
+        <v>1.0829</v>
       </c>
       <c r="F38" s="4">
         <f>IFERROR(IF(F12="","",F12/E12),"")</f>
-        <v>0</v>
+        <v>1.0889</v>
       </c>
       <c r="G38" s="4">
         <f>IFERROR(IF(G12="","",G12/F12),"")</f>
-        <v>0</v>
+        <v>1.0985</v>
       </c>
       <c r="H38" s="4">
         <f>IFERROR(IF(H12="","",H12/G12),"")</f>
-        <v>0</v>
+        <v>1.002</v>
       </c>
       <c r="I38" s="4">
         <f>IFERROR(IF(I12="","",I12/H12),"")</f>
-        <v>0</v>
+        <v>1.0046</v>
       </c>
       <c r="J38" s="4">
         <f>IFERROR(IF(J12="","",J12/I12),"")</f>
-        <v>0</v>
+        <v>1.0077</v>
       </c>
       <c r="K38" s="4">
         <f>IFERROR(IF(K12="","",K12/J12),"")</f>
-        <v>0</v>
+        <v>1.0052</v>
       </c>
       <c r="L38" s="4">
         <f>IFERROR(IF(L12="","",L12/K12),"")</f>
-        <v>0</v>
+        <v>1.0103</v>
       </c>
       <c r="M38" s="4">
         <f>IFERROR(IF(M12="","",M12/L12),"")</f>
-        <v>0</v>
+        <v>1.0052</v>
       </c>
       <c r="N38" s="4">
         <f>IFERROR(IF(N12="","",N12/M12),"")</f>
-        <v>0</v>
+        <v>1.0032</v>
       </c>
       <c r="O38" s="4">
         <f>IFERROR(IF(O12="","",O12/N12),"")</f>
@@ -8013,51 +7998,51 @@
       </c>
       <c r="B39" s="4">
         <f>IFERROR(IF(B13="","",B13/A13),"")</f>
-        <v>0</v>
+        <v>2.7856</v>
       </c>
       <c r="C39" s="4">
         <f>IFERROR(IF(C13="","",C13/B13),"")</f>
-        <v>0</v>
+        <v>1.2596</v>
       </c>
       <c r="D39" s="4">
         <f>IFERROR(IF(D13="","",D13/C13),"")</f>
-        <v>0</v>
+        <v>1.1904</v>
       </c>
       <c r="E39" s="4">
         <f>IFERROR(IF(E13="","",E13/D13),"")</f>
-        <v>0</v>
+        <v>1.0101</v>
       </c>
       <c r="F39" s="4">
         <f>IFERROR(IF(F13="","",F13/E13),"")</f>
-        <v>0</v>
+        <v>1.0065</v>
       </c>
       <c r="G39" s="4">
         <f>IFERROR(IF(G13="","",G13/F13),"")</f>
-        <v>0</v>
+        <v>1.0106</v>
       </c>
       <c r="H39" s="4">
         <f>IFERROR(IF(H13="","",H13/G13),"")</f>
-        <v>0</v>
+        <v>1.0394</v>
       </c>
       <c r="I39" s="4">
         <f>IFERROR(IF(I13="","",I13/H13),"")</f>
-        <v>0</v>
+        <v>1.0315</v>
       </c>
       <c r="J39" s="4">
         <f>IFERROR(IF(J13="","",J13/I13),"")</f>
-        <v>0</v>
+        <v>1.0046</v>
       </c>
       <c r="K39" s="4">
         <f>IFERROR(IF(K13="","",K13/J13),"")</f>
-        <v>0</v>
+        <v>1.0297</v>
       </c>
       <c r="L39" s="4">
         <f>IFERROR(IF(L13="","",L13/K13),"")</f>
-        <v>0</v>
+        <v>1.0565</v>
       </c>
       <c r="M39" s="4">
         <f>IFERROR(IF(M13="","",M13/L13),"")</f>
-        <v>0</v>
+        <v>1.0425</v>
       </c>
       <c r="N39" s="4">
         <f>IFERROR(IF(N13="","",N13/M13),"")</f>
@@ -8110,47 +8095,47 @@
       </c>
       <c r="B40" s="4">
         <f>IFERROR(IF(B14="","",B14/A14),"")</f>
-        <v>0</v>
+        <v>2.3011</v>
       </c>
       <c r="C40" s="4">
         <f>IFERROR(IF(C14="","",C14/B14),"")</f>
-        <v>0</v>
+        <v>1.1687</v>
       </c>
       <c r="D40" s="4">
         <f>IFERROR(IF(D14="","",D14/C14),"")</f>
-        <v>0</v>
+        <v>1.097</v>
       </c>
       <c r="E40" s="4">
         <f>IFERROR(IF(E14="","",E14/D14),"")</f>
-        <v>0</v>
+        <v>1.1858</v>
       </c>
       <c r="F40" s="4">
         <f>IFERROR(IF(F14="","",F14/E14),"")</f>
-        <v>0</v>
+        <v>0.9974</v>
       </c>
       <c r="G40" s="4">
         <f>IFERROR(IF(G14="","",G14/F14),"")</f>
-        <v>0</v>
+        <v>1.0005</v>
       </c>
       <c r="H40" s="4">
         <f>IFERROR(IF(H14="","",H14/G14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I40" s="4">
         <f>IFERROR(IF(I14="","",I14/H14),"")</f>
-        <v>0</v>
+        <v>1.0019</v>
       </c>
       <c r="J40" s="4">
         <f>IFERROR(IF(J14="","",J14/I14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K40" s="4">
         <f>IFERROR(IF(K14="","",K14/J14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L40" s="4">
         <f>IFERROR(IF(L14="","",L14/K14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M40" s="4">
         <f>IFERROR(IF(M14="","",M14/L14),"")</f>
@@ -8207,43 +8192,43 @@
       </c>
       <c r="B41" s="4">
         <f>IFERROR(IF(B15="","",B15/A15),"")</f>
-        <v>0</v>
+        <v>1.7931</v>
       </c>
       <c r="C41" s="4">
         <f>IFERROR(IF(C15="","",C15/B15),"")</f>
-        <v>0</v>
+        <v>1.2548</v>
       </c>
       <c r="D41" s="4">
         <f>IFERROR(IF(D15="","",D15/C15),"")</f>
-        <v>0</v>
+        <v>1.2734</v>
       </c>
       <c r="E41" s="4">
         <f>IFERROR(IF(E15="","",E15/D15),"")</f>
-        <v>0</v>
+        <v>1.067</v>
       </c>
       <c r="F41" s="4">
         <f>IFERROR(IF(F15="","",F15/E15),"")</f>
-        <v>0</v>
+        <v>1.0166</v>
       </c>
       <c r="G41" s="4">
         <f>IFERROR(IF(G15="","",G15/F15),"")</f>
-        <v>0</v>
+        <v>1.0061</v>
       </c>
       <c r="H41" s="4">
         <f>IFERROR(IF(H15="","",H15/G15),"")</f>
-        <v>0</v>
+        <v>1.003</v>
       </c>
       <c r="I41" s="4">
         <f>IFERROR(IF(I15="","",I15/H15),"")</f>
-        <v>0</v>
+        <v>1.0063</v>
       </c>
       <c r="J41" s="4">
         <f>IFERROR(IF(J15="","",J15/I15),"")</f>
-        <v>0</v>
+        <v>1.0616</v>
       </c>
       <c r="K41" s="4">
         <f>IFERROR(IF(K15="","",K15/J15),"")</f>
-        <v>0</v>
+        <v>1.0075</v>
       </c>
       <c r="L41" s="4">
         <f>IFERROR(IF(L15="","",L15/K15),"")</f>
@@ -8304,39 +8289,39 @@
       </c>
       <c r="B42" s="4">
         <f>IFERROR(IF(B16="","",B16/A16),"")</f>
-        <v>0</v>
+        <v>2.2204</v>
       </c>
       <c r="C42" s="4">
         <f>IFERROR(IF(C16="","",C16/B16),"")</f>
-        <v>0</v>
+        <v>1.6812</v>
       </c>
       <c r="D42" s="4">
         <f>IFERROR(IF(D16="","",D16/C16),"")</f>
-        <v>0</v>
+        <v>1.4653</v>
       </c>
       <c r="E42" s="4">
         <f>IFERROR(IF(E16="","",E16/D16),"")</f>
-        <v>0</v>
+        <v>1.0739</v>
       </c>
       <c r="F42" s="4">
         <f>IFERROR(IF(F16="","",F16/E16),"")</f>
-        <v>0</v>
+        <v>1.1134</v>
       </c>
       <c r="G42" s="4">
         <f>IFERROR(IF(G16="","",G16/F16),"")</f>
-        <v>0</v>
+        <v>1.1108</v>
       </c>
       <c r="H42" s="4">
         <f>IFERROR(IF(H16="","",H16/G16),"")</f>
-        <v>0</v>
+        <v>1.0547</v>
       </c>
       <c r="I42" s="4">
         <f>IFERROR(IF(I16="","",I16/H16),"")</f>
-        <v>0</v>
+        <v>1.0143</v>
       </c>
       <c r="J42" s="4">
         <f>IFERROR(IF(J16="","",J16/I16),"")</f>
-        <v>0</v>
+        <v>1.1378</v>
       </c>
       <c r="K42" s="4">
         <f>IFERROR(IF(K16="","",K16/J16),"")</f>
@@ -8401,35 +8386,35 @@
       </c>
       <c r="B43" s="4">
         <f>IFERROR(IF(B17="","",B17/A17),"")</f>
-        <v>0</v>
+        <v>3.3152</v>
       </c>
       <c r="C43" s="4">
         <f>IFERROR(IF(C17="","",C17/B17),"")</f>
-        <v>0</v>
+        <v>1.4135</v>
       </c>
       <c r="D43" s="4">
         <f>IFERROR(IF(D17="","",D17/C17),"")</f>
-        <v>0</v>
+        <v>1.1254</v>
       </c>
       <c r="E43" s="4">
         <f>IFERROR(IF(E17="","",E17/D17),"")</f>
-        <v>0</v>
+        <v>1.0752</v>
       </c>
       <c r="F43" s="4">
         <f>IFERROR(IF(F17="","",F17/E17),"")</f>
-        <v>0</v>
+        <v>1.1023</v>
       </c>
       <c r="G43" s="4">
         <f>IFERROR(IF(G17="","",G17/F17),"")</f>
-        <v>0</v>
+        <v>1.1396</v>
       </c>
       <c r="H43" s="4">
         <f>IFERROR(IF(H17="","",H17/G17),"")</f>
-        <v>0</v>
+        <v>1.0066</v>
       </c>
       <c r="I43" s="4">
         <f>IFERROR(IF(I17="","",I17/H17),"")</f>
-        <v>0</v>
+        <v>1.0111</v>
       </c>
       <c r="J43" s="4">
         <f>IFERROR(IF(J17="","",J17/I17),"")</f>
@@ -8498,31 +8483,31 @@
       </c>
       <c r="B44" s="4">
         <f>IFERROR(IF(B18="","",B18/A18),"")</f>
-        <v>0</v>
+        <v>1.7371</v>
       </c>
       <c r="C44" s="4">
         <f>IFERROR(IF(C18="","",C18/B18),"")</f>
-        <v>0</v>
+        <v>1.0775</v>
       </c>
       <c r="D44" s="4">
         <f>IFERROR(IF(D18="","",D18/C18),"")</f>
-        <v>0</v>
+        <v>1.1277</v>
       </c>
       <c r="E44" s="4">
         <f>IFERROR(IF(E18="","",E18/D18),"")</f>
-        <v>0</v>
+        <v>1.0874</v>
       </c>
       <c r="F44" s="4">
         <f>IFERROR(IF(F18="","",F18/E18),"")</f>
-        <v>0</v>
+        <v>1.1075</v>
       </c>
       <c r="G44" s="4">
         <f>IFERROR(IF(G18="","",G18/F18),"")</f>
-        <v>0</v>
+        <v>1.2914</v>
       </c>
       <c r="H44" s="4">
         <f>IFERROR(IF(H18="","",H18/G18),"")</f>
-        <v>0</v>
+        <v>1.0911</v>
       </c>
       <c r="I44" s="4">
         <f>IFERROR(IF(I18="","",I18/H18),"")</f>
@@ -8595,27 +8580,27 @@
       </c>
       <c r="B45" s="4">
         <f>IFERROR(IF(B19="","",B19/A19),"")</f>
-        <v>0</v>
+        <v>2.8751</v>
       </c>
       <c r="C45" s="4">
         <f>IFERROR(IF(C19="","",C19/B19),"")</f>
-        <v>0</v>
+        <v>1.4839</v>
       </c>
       <c r="D45" s="4">
         <f>IFERROR(IF(D19="","",D19/C19),"")</f>
-        <v>0</v>
+        <v>1.3735</v>
       </c>
       <c r="E45" s="4">
         <f>IFERROR(IF(E19="","",E19/D19),"")</f>
-        <v>0</v>
+        <v>1.0575</v>
       </c>
       <c r="F45" s="4">
         <f>IFERROR(IF(F19="","",F19/E19),"")</f>
-        <v>0</v>
+        <v>1.0563</v>
       </c>
       <c r="G45" s="4">
         <f>IFERROR(IF(G19="","",G19/F19),"")</f>
-        <v>0</v>
+        <v>1.0595</v>
       </c>
       <c r="H45" s="4">
         <f>IFERROR(IF(H19="","",H19/G19),"")</f>
@@ -8692,23 +8677,23 @@
       </c>
       <c r="B46" s="4">
         <f>IFERROR(IF(B20="","",B20/A20),"")</f>
-        <v>0</v>
+        <v>2.6745</v>
       </c>
       <c r="C46" s="4">
         <f>IFERROR(IF(C20="","",C20/B20),"")</f>
-        <v>0</v>
+        <v>1.7497</v>
       </c>
       <c r="D46" s="4">
         <f>IFERROR(IF(D20="","",D20/C20),"")</f>
-        <v>0</v>
+        <v>1.1825</v>
       </c>
       <c r="E46" s="4">
         <f>IFERROR(IF(E20="","",E20/D20),"")</f>
-        <v>0</v>
+        <v>1.2312</v>
       </c>
       <c r="F46" s="4">
         <f>IFERROR(IF(F20="","",F20/E20),"")</f>
-        <v>0</v>
+        <v>1.2153</v>
       </c>
       <c r="G46" s="4">
         <f>IFERROR(IF(G20="","",G20/F20),"")</f>
@@ -8789,19 +8774,19 @@
       </c>
       <c r="B47" s="4">
         <f>IFERROR(IF(B21="","",B21/A21),"")</f>
-        <v>0</v>
+        <v>2.5535</v>
       </c>
       <c r="C47" s="4">
         <f>IFERROR(IF(C21="","",C21/B21),"")</f>
-        <v>0</v>
+        <v>1.1803</v>
       </c>
       <c r="D47" s="4">
         <f>IFERROR(IF(D21="","",D21/C21),"")</f>
-        <v>0</v>
+        <v>1.121</v>
       </c>
       <c r="E47" s="4">
         <f>IFERROR(IF(E21="","",E21/D21),"")</f>
-        <v>0</v>
+        <v>1.0105</v>
       </c>
       <c r="F47" s="4">
         <f>IFERROR(IF(F21="","",F21/E21),"")</f>
@@ -8886,15 +8871,15 @@
       </c>
       <c r="B48" s="4">
         <f>IFERROR(IF(B22="","",B22/A22),"")</f>
-        <v>0</v>
+        <v>1.9981</v>
       </c>
       <c r="C48" s="4">
         <f>IFERROR(IF(C22="","",C22/B22),"")</f>
-        <v>0</v>
+        <v>1.6664</v>
       </c>
       <c r="D48" s="4">
         <f>IFERROR(IF(D22="","",D22/C22),"")</f>
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="E48" s="4">
         <f>IFERROR(IF(E22="","",E22/D22),"")</f>
@@ -8983,11 +8968,11 @@
       </c>
       <c r="B49" s="4">
         <f>IFERROR(IF(B23="","",B23/A23),"")</f>
-        <v>0</v>
+        <v>2.4294</v>
       </c>
       <c r="C49" s="4">
         <f>IFERROR(IF(C23="","",C23/B23),"")</f>
-        <v>0</v>
+        <v>1.0595</v>
       </c>
       <c r="D49" s="4">
         <f>IFERROR(IF(D23="","",D23/C23),"")</f>
@@ -9080,7 +9065,7 @@
       </c>
       <c r="B50" s="4">
         <f>IFERROR(IF(B24="","",B24/A24),"")</f>
-        <v>0</v>
+        <v>3.2653</v>
       </c>
       <c r="C50" s="4">
         <f>IFERROR(IF(C24="","",C24/B24),"")</f>
@@ -11940,95 +11925,95 @@
       </c>
       <c r="B28" s="4">
         <f>IFERROR(IF(B2="","",B2/A2),"")</f>
-        <v>0</v>
+        <v>1.0704</v>
       </c>
       <c r="C28" s="4">
         <f>IFERROR(IF(C2="","",C2/B2),"")</f>
-        <v>0</v>
+        <v>1.0019</v>
       </c>
       <c r="D28" s="4">
         <f>IFERROR(IF(D2="","",D2/C2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E28" s="4">
         <f>IFERROR(IF(E2="","",E2/D2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F28" s="4">
         <f>IFERROR(IF(F2="","",F2/E2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" s="4">
         <f>IFERROR(IF(G2="","",G2/F2),"")</f>
-        <v>0</v>
+        <v>1.0251</v>
       </c>
       <c r="H28" s="4">
         <f>IFERROR(IF(H2="","",H2/G2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I28" s="4">
         <f>IFERROR(IF(I2="","",I2/H2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J28" s="4">
         <f>IFERROR(IF(J2="","",J2/I2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K28" s="4">
         <f>IFERROR(IF(K2="","",K2/J2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L28" s="4">
         <f>IFERROR(IF(L2="","",L2/K2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M28" s="4">
         <f>IFERROR(IF(M2="","",M2/L2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N28" s="4">
         <f>IFERROR(IF(N2="","",N2/M2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O28" s="4">
         <f>IFERROR(IF(O2="","",O2/N2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P28" s="4">
         <f>IFERROR(IF(P2="","",P2/O2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q28" s="4">
         <f>IFERROR(IF(Q2="","",Q2/P2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R28" s="4">
         <f>IFERROR(IF(R2="","",R2/Q2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S28" s="4">
         <f>IFERROR(IF(S2="","",S2/R2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T28" s="4">
         <f>IFERROR(IF(T2="","",T2/S2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U28" s="4">
         <f>IFERROR(IF(U2="","",U2/T2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="V28" s="4">
         <f>IFERROR(IF(V2="","",V2/U2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="W28" s="4">
         <f>IFERROR(IF(W2="","",W2/V2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="X28" s="4">
         <f>IFERROR(IF(X2="","",X2/W2),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -12037,91 +12022,91 @@
       </c>
       <c r="B29" s="4">
         <f>IFERROR(IF(B3="","",B3/A3),"")</f>
-        <v>0</v>
+        <v>1.0344</v>
       </c>
       <c r="C29" s="4">
         <f>IFERROR(IF(C3="","",C3/B3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D29" s="4">
         <f>IFERROR(IF(D3="","",D3/C3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E29" s="4">
         <f>IFERROR(IF(E3="","",E3/D3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F29" s="4">
         <f>IFERROR(IF(F3="","",F3/E3),"")</f>
-        <v>0</v>
+        <v>1.027</v>
       </c>
       <c r="G29" s="4">
         <f>IFERROR(IF(G3="","",G3/F3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" s="4">
         <f>IFERROR(IF(H3="","",H3/G3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I29" s="4">
         <f>IFERROR(IF(I3="","",I3/H3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J29" s="4">
         <f>IFERROR(IF(J3="","",J3/I3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K29" s="4">
         <f>IFERROR(IF(K3="","",K3/J3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L29" s="4">
         <f>IFERROR(IF(L3="","",L3/K3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M29" s="4">
         <f>IFERROR(IF(M3="","",M3/L3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N29" s="4">
         <f>IFERROR(IF(N3="","",N3/M3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O29" s="4">
         <f>IFERROR(IF(O3="","",O3/N3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P29" s="4">
         <f>IFERROR(IF(P3="","",P3/O3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q29" s="4">
         <f>IFERROR(IF(Q3="","",Q3/P3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R29" s="4">
         <f>IFERROR(IF(R3="","",R3/Q3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S29" s="4">
         <f>IFERROR(IF(S3="","",S3/R3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T29" s="4">
         <f>IFERROR(IF(T3="","",T3/S3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U29" s="4">
         <f>IFERROR(IF(U3="","",U3/T3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="V29" s="4">
         <f>IFERROR(IF(V3="","",V3/U3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="W29" s="4">
         <f>IFERROR(IF(W3="","",W3/V3),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="X29" s="4">
         <f>IFERROR(IF(X3="","",X3/W3),"")</f>
@@ -12134,87 +12119,87 @@
       </c>
       <c r="B30" s="4">
         <f>IFERROR(IF(B4="","",B4/A4),"")</f>
-        <v>0</v>
+        <v>1.0346</v>
       </c>
       <c r="C30" s="4">
         <f>IFERROR(IF(C4="","",C4/B4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D30" s="4">
         <f>IFERROR(IF(D4="","",D4/C4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E30" s="4">
         <f>IFERROR(IF(E4="","",E4/D4),"")</f>
-        <v>0</v>
+        <v>0.9952</v>
       </c>
       <c r="F30" s="4">
         <f>IFERROR(IF(F4="","",F4/E4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="4">
         <f>IFERROR(IF(G4="","",G4/F4),"")</f>
-        <v>0</v>
+        <v>1.0024</v>
       </c>
       <c r="H30" s="4">
         <f>IFERROR(IF(H4="","",H4/G4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I30" s="4">
         <f>IFERROR(IF(I4="","",I4/H4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J30" s="4">
         <f>IFERROR(IF(J4="","",J4/I4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K30" s="4">
         <f>IFERROR(IF(K4="","",K4/J4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L30" s="4">
         <f>IFERROR(IF(L4="","",L4/K4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M30" s="4">
         <f>IFERROR(IF(M4="","",M4/L4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N30" s="4">
         <f>IFERROR(IF(N4="","",N4/M4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O30" s="4">
         <f>IFERROR(IF(O4="","",O4/N4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P30" s="4">
         <f>IFERROR(IF(P4="","",P4/O4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q30" s="4">
         <f>IFERROR(IF(Q4="","",Q4/P4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R30" s="4">
         <f>IFERROR(IF(R4="","",R4/Q4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S30" s="4">
         <f>IFERROR(IF(S4="","",S4/R4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T30" s="4">
         <f>IFERROR(IF(T4="","",T4/S4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U30" s="4">
         <f>IFERROR(IF(U4="","",U4/T4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="V30" s="4">
         <f>IFERROR(IF(V4="","",V4/U4),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="W30" s="4">
         <f>IFERROR(IF(W4="","",W4/V4),"")</f>
@@ -12231,83 +12216,83 @@
       </c>
       <c r="B31" s="4">
         <f>IFERROR(IF(B5="","",B5/A5),"")</f>
-        <v>0</v>
+        <v>1.0591</v>
       </c>
       <c r="C31" s="4">
         <f>IFERROR(IF(C5="","",C5/B5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D31" s="4">
         <f>IFERROR(IF(D5="","",D5/C5),"")</f>
-        <v>0</v>
+        <v>1.0041</v>
       </c>
       <c r="E31" s="4">
         <f>IFERROR(IF(E5="","",E5/D5),"")</f>
-        <v>0</v>
+        <v>1.0021</v>
       </c>
       <c r="F31" s="4">
         <f>IFERROR(IF(F5="","",F5/E5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G31" s="4">
         <f>IFERROR(IF(G5="","",G5/F5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H31" s="4">
         <f>IFERROR(IF(H5="","",H5/G5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I31" s="4">
         <f>IFERROR(IF(I5="","",I5/H5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J31" s="4">
         <f>IFERROR(IF(J5="","",J5/I5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K31" s="4">
         <f>IFERROR(IF(K5="","",K5/J5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L31" s="4">
         <f>IFERROR(IF(L5="","",L5/K5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M31" s="4">
         <f>IFERROR(IF(M5="","",M5/L5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N31" s="4">
         <f>IFERROR(IF(N5="","",N5/M5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O31" s="4">
         <f>IFERROR(IF(O5="","",O5/N5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P31" s="4">
         <f>IFERROR(IF(P5="","",P5/O5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q31" s="4">
         <f>IFERROR(IF(Q5="","",Q5/P5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R31" s="4">
         <f>IFERROR(IF(R5="","",R5/Q5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S31" s="4">
         <f>IFERROR(IF(S5="","",S5/R5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T31" s="4">
         <f>IFERROR(IF(T5="","",T5/S5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U31" s="4">
         <f>IFERROR(IF(U5="","",U5/T5),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="V31" s="4">
         <f>IFERROR(IF(V5="","",V5/U5),"")</f>
@@ -12328,79 +12313,79 @@
       </c>
       <c r="B32" s="4">
         <f>IFERROR(IF(B6="","",B6/A6),"")</f>
-        <v>0</v>
+        <v>1.0232</v>
       </c>
       <c r="C32" s="4">
         <f>IFERROR(IF(C6="","",C6/B6),"")</f>
-        <v>0</v>
+        <v>1.0021</v>
       </c>
       <c r="D32" s="4">
         <f>IFERROR(IF(D6="","",D6/C6),"")</f>
-        <v>0</v>
+        <v>0.9979</v>
       </c>
       <c r="E32" s="4">
         <f>IFERROR(IF(E6="","",E6/D6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F32" s="4">
         <f>IFERROR(IF(F6="","",F6/E6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G32" s="4">
         <f>IFERROR(IF(G6="","",G6/F6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H32" s="4">
         <f>IFERROR(IF(H6="","",H6/G6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I32" s="4">
         <f>IFERROR(IF(I6="","",I6/H6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J32" s="4">
         <f>IFERROR(IF(J6="","",J6/I6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K32" s="4">
         <f>IFERROR(IF(K6="","",K6/J6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L32" s="4">
         <f>IFERROR(IF(L6="","",L6/K6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M32" s="4">
         <f>IFERROR(IF(M6="","",M6/L6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N32" s="4">
         <f>IFERROR(IF(N6="","",N6/M6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O32" s="4">
         <f>IFERROR(IF(O6="","",O6/N6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P32" s="4">
         <f>IFERROR(IF(P6="","",P6/O6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q32" s="4">
         <f>IFERROR(IF(Q6="","",Q6/P6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R32" s="4">
         <f>IFERROR(IF(R6="","",R6/Q6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S32" s="4">
         <f>IFERROR(IF(S6="","",S6/R6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T32" s="4">
         <f>IFERROR(IF(T6="","",T6/S6),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="U32" s="4">
         <f>IFERROR(IF(U6="","",U6/T6),"")</f>
@@ -12425,75 +12410,75 @@
       </c>
       <c r="B33" s="4">
         <f>IFERROR(IF(B7="","",B7/A7),"")</f>
-        <v>0</v>
+        <v>1.0386</v>
       </c>
       <c r="C33" s="4">
         <f>IFERROR(IF(C7="","",C7/B7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D33" s="4">
         <f>IFERROR(IF(D7="","",D7/C7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E33" s="4">
         <f>IFERROR(IF(E7="","",E7/D7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F33" s="4">
         <f>IFERROR(IF(F7="","",F7/E7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G33" s="4">
         <f>IFERROR(IF(G7="","",G7/F7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H33" s="4">
         <f>IFERROR(IF(H7="","",H7/G7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I33" s="4">
         <f>IFERROR(IF(I7="","",I7/H7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J33" s="4">
         <f>IFERROR(IF(J7="","",J7/I7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K33" s="4">
         <f>IFERROR(IF(K7="","",K7/J7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L33" s="4">
         <f>IFERROR(IF(L7="","",L7/K7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M33" s="4">
         <f>IFERROR(IF(M7="","",M7/L7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N33" s="4">
         <f>IFERROR(IF(N7="","",N7/M7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O33" s="4">
         <f>IFERROR(IF(O7="","",O7/N7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P33" s="4">
         <f>IFERROR(IF(P7="","",P7/O7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q33" s="4">
         <f>IFERROR(IF(Q7="","",Q7/P7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R33" s="4">
         <f>IFERROR(IF(R7="","",R7/Q7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S33" s="4">
         <f>IFERROR(IF(S7="","",S7/R7),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="T33" s="4">
         <f>IFERROR(IF(T7="","",T7/S7),"")</f>
@@ -12522,71 +12507,71 @@
       </c>
       <c r="B34" s="4">
         <f>IFERROR(IF(B8="","",B8/A8),"")</f>
-        <v>0</v>
+        <v>1.0434</v>
       </c>
       <c r="C34" s="4">
         <f>IFERROR(IF(C8="","",C8/B8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D34" s="4">
         <f>IFERROR(IF(D8="","",D8/C8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E34" s="4">
         <f>IFERROR(IF(E8="","",E8/D8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F34" s="4">
         <f>IFERROR(IF(F8="","",F8/E8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" s="4">
         <f>IFERROR(IF(G8="","",G8/F8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H34" s="4">
         <f>IFERROR(IF(H8="","",H8/G8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I34" s="4">
         <f>IFERROR(IF(I8="","",I8/H8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J34" s="4">
         <f>IFERROR(IF(J8="","",J8/I8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K34" s="4">
         <f>IFERROR(IF(K8="","",K8/J8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L34" s="4">
         <f>IFERROR(IF(L8="","",L8/K8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M34" s="4">
         <f>IFERROR(IF(M8="","",M8/L8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N34" s="4">
         <f>IFERROR(IF(N8="","",N8/M8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O34" s="4">
         <f>IFERROR(IF(O8="","",O8/N8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P34" s="4">
         <f>IFERROR(IF(P8="","",P8/O8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q34" s="4">
         <f>IFERROR(IF(Q8="","",Q8/P8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R34" s="4">
         <f>IFERROR(IF(R8="","",R8/Q8),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S34" s="4">
         <f>IFERROR(IF(S8="","",S8/R8),"")</f>
@@ -12619,67 +12604,67 @@
       </c>
       <c r="B35" s="4">
         <f>IFERROR(IF(B9="","",B9/A9),"")</f>
-        <v>0</v>
+        <v>1.0644</v>
       </c>
       <c r="C35" s="4">
         <f>IFERROR(IF(C9="","",C9/B9),"")</f>
-        <v>0</v>
+        <v>1.004</v>
       </c>
       <c r="D35" s="4">
         <f>IFERROR(IF(D9="","",D9/C9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E35" s="4">
         <f>IFERROR(IF(E9="","",E9/D9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F35" s="4">
         <f>IFERROR(IF(F9="","",F9/E9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" s="4">
         <f>IFERROR(IF(G9="","",G9/F9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H35" s="4">
         <f>IFERROR(IF(H9="","",H9/G9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I35" s="4">
         <f>IFERROR(IF(I9="","",I9/H9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J35" s="4">
         <f>IFERROR(IF(J9="","",J9/I9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K35" s="4">
         <f>IFERROR(IF(K9="","",K9/J9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L35" s="4">
         <f>IFERROR(IF(L9="","",L9/K9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M35" s="4">
         <f>IFERROR(IF(M9="","",M9/L9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N35" s="4">
         <f>IFERROR(IF(N9="","",N9/M9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O35" s="4">
         <f>IFERROR(IF(O9="","",O9/N9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P35" s="4">
         <f>IFERROR(IF(P9="","",P9/O9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q35" s="4">
         <f>IFERROR(IF(Q9="","",Q9/P9),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="R35" s="4">
         <f>IFERROR(IF(R9="","",R9/Q9),"")</f>
@@ -12716,63 +12701,63 @@
       </c>
       <c r="B36" s="4">
         <f>IFERROR(IF(B10="","",B10/A10),"")</f>
-        <v>0</v>
+        <v>1.0474</v>
       </c>
       <c r="C36" s="4">
         <f>IFERROR(IF(C10="","",C10/B10),"")</f>
-        <v>0</v>
+        <v>1.0041</v>
       </c>
       <c r="D36" s="4">
         <f>IFERROR(IF(D10="","",D10/C10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E36" s="4">
         <f>IFERROR(IF(E10="","",E10/D10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F36" s="4">
         <f>IFERROR(IF(F10="","",F10/E10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G36" s="4">
         <f>IFERROR(IF(G10="","",G10/F10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H36" s="4">
         <f>IFERROR(IF(H10="","",H10/G10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I36" s="4">
         <f>IFERROR(IF(I10="","",I10/H10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J36" s="4">
         <f>IFERROR(IF(J10="","",J10/I10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K36" s="4">
         <f>IFERROR(IF(K10="","",K10/J10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L36" s="4">
         <f>IFERROR(IF(L10="","",L10/K10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M36" s="4">
         <f>IFERROR(IF(M10="","",M10/L10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N36" s="4">
         <f>IFERROR(IF(N10="","",N10/M10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O36" s="4">
         <f>IFERROR(IF(O10="","",O10/N10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P36" s="4">
         <f>IFERROR(IF(P10="","",P10/O10),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="Q36" s="4">
         <f>IFERROR(IF(Q10="","",Q10/P10),"")</f>
@@ -12813,59 +12798,59 @@
       </c>
       <c r="B37" s="4">
         <f>IFERROR(IF(B11="","",B11/A11),"")</f>
-        <v>0</v>
+        <v>1.0457</v>
       </c>
       <c r="C37" s="4">
         <f>IFERROR(IF(C11="","",C11/B11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D37" s="4">
         <f>IFERROR(IF(D11="","",D11/C11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E37" s="4">
         <f>IFERROR(IF(E11="","",E11/D11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F37" s="4">
         <f>IFERROR(IF(F11="","",F11/E11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G37" s="4">
         <f>IFERROR(IF(G11="","",G11/F11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H37" s="4">
         <f>IFERROR(IF(H11="","",H11/G11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I37" s="4">
         <f>IFERROR(IF(I11="","",I11/H11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J37" s="4">
         <f>IFERROR(IF(J11="","",J11/I11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K37" s="4">
         <f>IFERROR(IF(K11="","",K11/J11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L37" s="4">
         <f>IFERROR(IF(L11="","",L11/K11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M37" s="4">
         <f>IFERROR(IF(M11="","",M11/L11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N37" s="4">
         <f>IFERROR(IF(N11="","",N11/M11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O37" s="4">
         <f>IFERROR(IF(O11="","",O11/N11),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P37" s="4">
         <f>IFERROR(IF(P11="","",P11/O11),"")</f>
@@ -12910,55 +12895,55 @@
       </c>
       <c r="B38" s="4">
         <f>IFERROR(IF(B12="","",B12/A12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="C38" s="4">
         <f>IFERROR(IF(C12="","",C12/B12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D38" s="4">
         <f>IFERROR(IF(D12="","",D12/C12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E38" s="4">
         <f>IFERROR(IF(E12="","",E12/D12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F38" s="4">
         <f>IFERROR(IF(F12="","",F12/E12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G38" s="4">
         <f>IFERROR(IF(G12="","",G12/F12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H38" s="4">
         <f>IFERROR(IF(H12="","",H12/G12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I38" s="4">
         <f>IFERROR(IF(I12="","",I12/H12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J38" s="4">
         <f>IFERROR(IF(J12="","",J12/I12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K38" s="4">
         <f>IFERROR(IF(K12="","",K12/J12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L38" s="4">
         <f>IFERROR(IF(L12="","",L12/K12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M38" s="4">
         <f>IFERROR(IF(M12="","",M12/L12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N38" s="4">
         <f>IFERROR(IF(N12="","",N12/M12),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="O38" s="4">
         <f>IFERROR(IF(O12="","",O12/N12),"")</f>
@@ -13007,51 +12992,51 @@
       </c>
       <c r="B39" s="4">
         <f>IFERROR(IF(B13="","",B13/A13),"")</f>
-        <v>0</v>
+        <v>1.0645</v>
       </c>
       <c r="C39" s="4">
         <f>IFERROR(IF(C13="","",C13/B13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D39" s="4">
         <f>IFERROR(IF(D13="","",D13/C13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E39" s="4">
         <f>IFERROR(IF(E13="","",E13/D13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F39" s="4">
         <f>IFERROR(IF(F13="","",F13/E13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G39" s="4">
         <f>IFERROR(IF(G13="","",G13/F13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H39" s="4">
         <f>IFERROR(IF(H13="","",H13/G13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I39" s="4">
         <f>IFERROR(IF(I13="","",I13/H13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J39" s="4">
         <f>IFERROR(IF(J13="","",J13/I13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K39" s="4">
         <f>IFERROR(IF(K13="","",K13/J13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L39" s="4">
         <f>IFERROR(IF(L13="","",L13/K13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M39" s="4">
         <f>IFERROR(IF(M13="","",M13/L13),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="N39" s="4">
         <f>IFERROR(IF(N13="","",N13/M13),"")</f>
@@ -13104,47 +13089,47 @@
       </c>
       <c r="B40" s="4">
         <f>IFERROR(IF(B14="","",B14/A14),"")</f>
-        <v>0</v>
+        <v>1.028</v>
       </c>
       <c r="C40" s="4">
         <f>IFERROR(IF(C14="","",C14/B14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D40" s="4">
         <f>IFERROR(IF(D14="","",D14/C14),"")</f>
-        <v>0</v>
+        <v>1.0045</v>
       </c>
       <c r="E40" s="4">
         <f>IFERROR(IF(E14="","",E14/D14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F40" s="4">
         <f>IFERROR(IF(F14="","",F14/E14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G40" s="4">
         <f>IFERROR(IF(G14="","",G14/F14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H40" s="4">
         <f>IFERROR(IF(H14="","",H14/G14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I40" s="4">
         <f>IFERROR(IF(I14="","",I14/H14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J40" s="4">
         <f>IFERROR(IF(J14="","",J14/I14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K40" s="4">
         <f>IFERROR(IF(K14="","",K14/J14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L40" s="4">
         <f>IFERROR(IF(L14="","",L14/K14),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="M40" s="4">
         <f>IFERROR(IF(M14="","",M14/L14),"")</f>
@@ -13201,43 +13186,43 @@
       </c>
       <c r="B41" s="4">
         <f>IFERROR(IF(B15="","",B15/A15),"")</f>
-        <v>0</v>
+        <v>1.0456</v>
       </c>
       <c r="C41" s="4">
         <f>IFERROR(IF(C15="","",C15/B15),"")</f>
-        <v>0</v>
+        <v>1.0029</v>
       </c>
       <c r="D41" s="4">
         <f>IFERROR(IF(D15="","",D15/C15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E41" s="4">
         <f>IFERROR(IF(E15="","",E15/D15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F41" s="4">
         <f>IFERROR(IF(F15="","",F15/E15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G41" s="4">
         <f>IFERROR(IF(G15="","",G15/F15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H41" s="4">
         <f>IFERROR(IF(H15="","",H15/G15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I41" s="4">
         <f>IFERROR(IF(I15="","",I15/H15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J41" s="4">
         <f>IFERROR(IF(J15="","",J15/I15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="K41" s="4">
         <f>IFERROR(IF(K15="","",K15/J15),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L41" s="4">
         <f>IFERROR(IF(L15="","",L15/K15),"")</f>
@@ -13298,39 +13283,39 @@
       </c>
       <c r="B42" s="4">
         <f>IFERROR(IF(B16="","",B16/A16),"")</f>
-        <v>0</v>
+        <v>1.0328</v>
       </c>
       <c r="C42" s="4">
         <f>IFERROR(IF(C16="","",C16/B16),"")</f>
-        <v>0</v>
+        <v>1.0159</v>
       </c>
       <c r="D42" s="4">
         <f>IFERROR(IF(D16="","",D16/C16),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E42" s="4">
         <f>IFERROR(IF(E16="","",E16/D16),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F42" s="4">
         <f>IFERROR(IF(F16="","",F16/E16),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G42" s="4">
         <f>IFERROR(IF(G16="","",G16/F16),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H42" s="4">
         <f>IFERROR(IF(H16="","",H16/G16),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I42" s="4">
         <f>IFERROR(IF(I16="","",I16/H16),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J42" s="4">
         <f>IFERROR(IF(J16="","",J16/I16),"")</f>
-        <v>0</v>
+        <v>0.9883</v>
       </c>
       <c r="K42" s="4">
         <f>IFERROR(IF(K16="","",K16/J16),"")</f>
@@ -13395,35 +13380,35 @@
       </c>
       <c r="B43" s="4">
         <f>IFERROR(IF(B17="","",B17/A17),"")</f>
-        <v>0</v>
+        <v>1.0802</v>
       </c>
       <c r="C43" s="4">
         <f>IFERROR(IF(C17="","",C17/B17),"")</f>
-        <v>0</v>
+        <v>1.0459</v>
       </c>
       <c r="D43" s="4">
         <f>IFERROR(IF(D17="","",D17/C17),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E43" s="4">
         <f>IFERROR(IF(E17="","",E17/D17),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F43" s="4">
         <f>IFERROR(IF(F17="","",F17/E17),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G43" s="4">
         <f>IFERROR(IF(G17="","",G17/F17),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H43" s="4">
         <f>IFERROR(IF(H17="","",H17/G17),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="I43" s="4">
         <f>IFERROR(IF(I17="","",I17/H17),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J43" s="4">
         <f>IFERROR(IF(J17="","",J17/I17),"")</f>
@@ -13492,31 +13477,31 @@
       </c>
       <c r="B44" s="4">
         <f>IFERROR(IF(B18="","",B18/A18),"")</f>
-        <v>0</v>
+        <v>1.1244</v>
       </c>
       <c r="C44" s="4">
         <f>IFERROR(IF(C18="","",C18/B18),"")</f>
-        <v>0</v>
+        <v>1.0043</v>
       </c>
       <c r="D44" s="4">
         <f>IFERROR(IF(D18="","",D18/C18),"")</f>
-        <v>0</v>
+        <v>1.0042</v>
       </c>
       <c r="E44" s="4">
         <f>IFERROR(IF(E18="","",E18/D18),"")</f>
-        <v>0</v>
+        <v>0.9958</v>
       </c>
       <c r="F44" s="4">
         <f>IFERROR(IF(F18="","",F18/E18),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G44" s="4">
         <f>IFERROR(IF(G18="","",G18/F18),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H44" s="4">
         <f>IFERROR(IF(H18="","",H18/G18),"")</f>
-        <v>0</v>
+        <v>0.9958</v>
       </c>
       <c r="I44" s="4">
         <f>IFERROR(IF(I18="","",I18/H18),"")</f>
@@ -13589,27 +13574,27 @@
       </c>
       <c r="B45" s="4">
         <f>IFERROR(IF(B19="","",B19/A19),"")</f>
-        <v>0</v>
+        <v>1.1233</v>
       </c>
       <c r="C45" s="4">
         <f>IFERROR(IF(C19="","",C19/B19),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D45" s="4">
         <f>IFERROR(IF(D19="","",D19/C19),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E45" s="4">
         <f>IFERROR(IF(E19="","",E19/D19),"")</f>
-        <v>0</v>
+        <v>1.0041</v>
       </c>
       <c r="F45" s="4">
         <f>IFERROR(IF(F19="","",F19/E19),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="G45" s="4">
         <f>IFERROR(IF(G19="","",G19/F19),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="H45" s="4">
         <f>IFERROR(IF(H19="","",H19/G19),"")</f>
@@ -13686,23 +13671,23 @@
       </c>
       <c r="B46" s="4">
         <f>IFERROR(IF(B20="","",B20/A20),"")</f>
-        <v>0</v>
+        <v>1.1429</v>
       </c>
       <c r="C46" s="4">
         <f>IFERROR(IF(C20="","",C20/B20),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D46" s="4">
         <f>IFERROR(IF(D20="","",D20/C20),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E46" s="4">
         <f>IFERROR(IF(E20="","",E20/D20),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F46" s="4">
         <f>IFERROR(IF(F20="","",F20/E20),"")</f>
-        <v>0</v>
+        <v>0.9963</v>
       </c>
       <c r="G46" s="4">
         <f>IFERROR(IF(G20="","",G20/F20),"")</f>
@@ -13783,19 +13768,19 @@
       </c>
       <c r="B47" s="4">
         <f>IFERROR(IF(B21="","",B21/A21),"")</f>
-        <v>0</v>
+        <v>1.0604</v>
       </c>
       <c r="C47" s="4">
         <f>IFERROR(IF(C21="","",C21/B21),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D47" s="4">
         <f>IFERROR(IF(D21="","",D21/C21),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E47" s="4">
         <f>IFERROR(IF(E21="","",E21/D21),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="F47" s="4">
         <f>IFERROR(IF(F21="","",F21/E21),"")</f>
@@ -13880,15 +13865,15 @@
       </c>
       <c r="B48" s="4">
         <f>IFERROR(IF(B22="","",B22/A22),"")</f>
-        <v>0</v>
+        <v>1.1416</v>
       </c>
       <c r="C48" s="4">
         <f>IFERROR(IF(C22="","",C22/B22),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D48" s="4">
         <f>IFERROR(IF(D22="","",D22/C22),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="E48" s="4">
         <f>IFERROR(IF(E22="","",E22/D22),"")</f>
@@ -13977,11 +13962,11 @@
       </c>
       <c r="B49" s="4">
         <f>IFERROR(IF(B23="","",B23/A23),"")</f>
-        <v>0</v>
+        <v>1.1414</v>
       </c>
       <c r="C49" s="4">
         <f>IFERROR(IF(C23="","",C23/B23),"")</f>
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="D49" s="4">
         <f>IFERROR(IF(D23="","",D23/C23),"")</f>
@@ -14074,7 +14059,7 @@
       </c>
       <c r="B50" s="4">
         <f>IFERROR(IF(B24="","",B24/A24),"")</f>
-        <v>0</v>
+        <v>1.1159</v>
       </c>
       <c r="C50" s="4">
         <f>IFERROR(IF(C24="","",C24/B24),"")</f>
@@ -23691,95 +23676,95 @@
         <v>97</v>
       </c>
       <c r="B3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!B49:B51)/AVERAGE('Incurred Loss'!B49:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!B49:B51)/AVERAGE('Incurred Loss'!B49:B51),"")</f>
         <v>0.1604</v>
       </c>
       <c r="C3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!C49:C51)/AVERAGE('Incurred Loss'!C49:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!C49:C51)/AVERAGE('Incurred Loss'!C49:C51),"")</f>
         <v>0.1345</v>
       </c>
       <c r="D3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!D49:D51)/AVERAGE('Incurred Loss'!D49:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!D49:D51)/AVERAGE('Incurred Loss'!D49:D51),"")</f>
         <v>0.0574</v>
       </c>
       <c r="E3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!E49:E51)/AVERAGE('Incurred Loss'!E49:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!E49:E51)/AVERAGE('Incurred Loss'!E49:E51),"")</f>
         <v>0.0355</v>
       </c>
       <c r="F3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!F49:F51)/AVERAGE('Incurred Loss'!F49:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!F49:F51)/AVERAGE('Incurred Loss'!F49:F51),"")</f>
         <v>0.0934</v>
       </c>
       <c r="G3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!G49:G51)/AVERAGE('Incurred Loss'!G49:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!G49:G51)/AVERAGE('Incurred Loss'!G49:G51),"")</f>
         <v>0.0606</v>
       </c>
       <c r="H3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!H49:H51)/AVERAGE('Incurred Loss'!H49:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!H49:H51)/AVERAGE('Incurred Loss'!H49:H51),"")</f>
         <v>0.0164</v>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!I49:I51)/AVERAGE('Incurred Loss'!I49:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!I49:I51)/AVERAGE('Incurred Loss'!I49:I51),"")</f>
         <v>0.0221</v>
       </c>
       <c r="J3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!J49:J51)/AVERAGE('Incurred Loss'!J49:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!J49:J51)/AVERAGE('Incurred Loss'!J49:J51),"")</f>
         <v>0.0488</v>
       </c>
       <c r="K3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!K49:K51)/AVERAGE('Incurred Loss'!K49:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!K49:K51)/AVERAGE('Incurred Loss'!K49:K51),"")</f>
         <v>0.0072</v>
       </c>
       <c r="L3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!L49:L51)/AVERAGE('Incurred Loss'!L49:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!L49:L51)/AVERAGE('Incurred Loss'!L49:L51),"")</f>
         <v>0.0985</v>
       </c>
       <c r="M3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!M49:M51)/AVERAGE('Incurred Loss'!M49:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!M49:M51)/AVERAGE('Incurred Loss'!M49:M51),"")</f>
         <v>0.0008</v>
       </c>
       <c r="N3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!N49:N51)/AVERAGE('Incurred Loss'!N49:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!N49:N51)/AVERAGE('Incurred Loss'!N49:N51),"")</f>
         <v>0.0001</v>
       </c>
       <c r="O3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!O49:O51)/AVERAGE('Incurred Loss'!O49:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!O49:O51)/AVERAGE('Incurred Loss'!O49:O51),"")</f>
         <v>0.0035</v>
       </c>
       <c r="P3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!P49:P51)/AVERAGE('Incurred Loss'!P49:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!P49:P51)/AVERAGE('Incurred Loss'!P49:P51),"")</f>
         <v>0.0028</v>
       </c>
       <c r="Q3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!Q49:Q51)/AVERAGE('Incurred Loss'!Q49:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!Q49:Q51)/AVERAGE('Incurred Loss'!Q49:Q51),"")</f>
         <v>0.0101</v>
       </c>
       <c r="R3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!R49:R51)/AVERAGE('Incurred Loss'!R49:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!R49:R51)/AVERAGE('Incurred Loss'!R49:R51),"")</f>
         <v>0.0037</v>
       </c>
       <c r="S3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!S49:S51)/AVERAGE('Incurred Loss'!S49:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!S49:S51)/AVERAGE('Incurred Loss'!S49:S51),"")</f>
         <v>0.0</v>
       </c>
       <c r="T3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!T49:T51)/AVERAGE('Incurred Loss'!T49:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!T49:T51)/AVERAGE('Incurred Loss'!T49:T51),"")</f>
         <v>0.0</v>
       </c>
       <c r="U3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!U49:U51)/AVERAGE('Incurred Loss'!U49:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!U49:U51)/AVERAGE('Incurred Loss'!U49:U51),"")</f>
         <v>0.0036</v>
       </c>
       <c r="V3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!V49:V51)/AVERAGE('Incurred Loss'!V49:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!V49:V51)/AVERAGE('Incurred Loss'!V49:V51),"")</f>
         <v>0.0178</v>
       </c>
       <c r="W3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!W49:W51)/AVERAGE('Incurred Loss'!W49:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!W49:W51)/AVERAGE('Incurred Loss'!W49:W51),"")</f>
         <v>0.0</v>
       </c>
       <c r="X3" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!X49:X51)/AVERAGE('Incurred Loss'!X49:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!X49:X51)/AVERAGE('Incurred Loss'!X49:X51),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -23788,95 +23773,95 @@
         <v>98</v>
       </c>
       <c r="B4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!B47:B51)/AVERAGE('Incurred Loss'!B47:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!B47:B51)/AVERAGE('Incurred Loss'!B47:B51),"")</f>
         <v>0.3284</v>
       </c>
       <c r="C4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!C47:C51)/AVERAGE('Incurred Loss'!C47:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!C47:C51)/AVERAGE('Incurred Loss'!C47:C51),"")</f>
         <v>0.2103</v>
       </c>
       <c r="D4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!D47:D51)/AVERAGE('Incurred Loss'!D47:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!D47:D51)/AVERAGE('Incurred Loss'!D47:D51),"")</f>
         <v>0.1316</v>
       </c>
       <c r="E4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!E47:E51)/AVERAGE('Incurred Loss'!E47:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!E47:E51)/AVERAGE('Incurred Loss'!E47:E51),"")</f>
         <v>0.0556</v>
       </c>
       <c r="F4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!F47:F51)/AVERAGE('Incurred Loss'!F47:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!F47:F51)/AVERAGE('Incurred Loss'!F47:F51),"")</f>
         <v>0.0773</v>
       </c>
       <c r="G4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!G47:G51)/AVERAGE('Incurred Loss'!G47:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!G47:G51)/AVERAGE('Incurred Loss'!G47:G51),"")</f>
         <v>0.074</v>
       </c>
       <c r="H4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!H47:H51)/AVERAGE('Incurred Loss'!H47:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!H47:H51)/AVERAGE('Incurred Loss'!H47:H51),"")</f>
         <v>0.0136</v>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!I47:I51)/AVERAGE('Incurred Loss'!I47:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!I47:I51)/AVERAGE('Incurred Loss'!I47:I51),"")</f>
         <v>0.0254</v>
       </c>
       <c r="J4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!J47:J51)/AVERAGE('Incurred Loss'!J47:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!J47:J51)/AVERAGE('Incurred Loss'!J47:J51),"")</f>
         <v>0.0393</v>
       </c>
       <c r="K4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!K47:K51)/AVERAGE('Incurred Loss'!K47:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!K47:K51)/AVERAGE('Incurred Loss'!K47:K51),"")</f>
         <v>0.0134</v>
       </c>
       <c r="L4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!L47:L51)/AVERAGE('Incurred Loss'!L47:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!L47:L51)/AVERAGE('Incurred Loss'!L47:L51),"")</f>
         <v>0.0762</v>
       </c>
       <c r="M4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!M47:M51)/AVERAGE('Incurred Loss'!M47:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!M47:M51)/AVERAGE('Incurred Loss'!M47:M51),"")</f>
         <v>0.0162</v>
       </c>
       <c r="N4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!N47:N51)/AVERAGE('Incurred Loss'!N47:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!N47:N51)/AVERAGE('Incurred Loss'!N47:N51),"")</f>
         <v>0.0004</v>
       </c>
       <c r="O4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!O47:O51)/AVERAGE('Incurred Loss'!O47:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!O47:O51)/AVERAGE('Incurred Loss'!O47:O51),"")</f>
         <v>0.0187</v>
       </c>
       <c r="P4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!P47:P51)/AVERAGE('Incurred Loss'!P47:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!P47:P51)/AVERAGE('Incurred Loss'!P47:P51),"")</f>
         <v>0.0049</v>
       </c>
       <c r="Q4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!Q47:Q51)/AVERAGE('Incurred Loss'!Q47:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!Q47:Q51)/AVERAGE('Incurred Loss'!Q47:Q51),"")</f>
         <v>0.0089</v>
       </c>
       <c r="R4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!R47:R51)/AVERAGE('Incurred Loss'!R47:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!R47:R51)/AVERAGE('Incurred Loss'!R47:R51),"")</f>
         <v>0.0032</v>
       </c>
       <c r="S4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!S47:S51)/AVERAGE('Incurred Loss'!S47:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!S47:S51)/AVERAGE('Incurred Loss'!S47:S51),"")</f>
         <v>0.0</v>
       </c>
       <c r="T4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!T47:T51)/AVERAGE('Incurred Loss'!T47:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!T47:T51)/AVERAGE('Incurred Loss'!T47:T51),"")</f>
         <v>0.0188</v>
       </c>
       <c r="U4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!U47:U51)/AVERAGE('Incurred Loss'!U47:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!U47:U51)/AVERAGE('Incurred Loss'!U47:U51),"")</f>
         <v>0.013</v>
       </c>
       <c r="V4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!V47:V51)/AVERAGE('Incurred Loss'!V47:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!V47:V51)/AVERAGE('Incurred Loss'!V47:V51),"")</f>
         <v>0.0178</v>
       </c>
       <c r="W4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!W47:W51)/AVERAGE('Incurred Loss'!W47:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!W47:W51)/AVERAGE('Incurred Loss'!W47:W51),"")</f>
         <v>0.0</v>
       </c>
       <c r="X4" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!X47:X51)/AVERAGE('Incurred Loss'!X47:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!X47:X51)/AVERAGE('Incurred Loss'!X47:X51),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -23885,95 +23870,95 @@
         <v>99</v>
       </c>
       <c r="B5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!B42:B51)/AVERAGE('Incurred Loss'!B42:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!B42:B51)/AVERAGE('Incurred Loss'!B42:B51),"")</f>
         <v>0.2694</v>
       </c>
       <c r="C5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!C42:C51)/AVERAGE('Incurred Loss'!C42:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!C42:C51)/AVERAGE('Incurred Loss'!C42:C51),"")</f>
         <v>0.1768</v>
       </c>
       <c r="D5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!D42:D51)/AVERAGE('Incurred Loss'!D42:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!D42:D51)/AVERAGE('Incurred Loss'!D42:D51),"")</f>
         <v>0.1051</v>
       </c>
       <c r="E5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!E42:E51)/AVERAGE('Incurred Loss'!E42:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!E42:E51)/AVERAGE('Incurred Loss'!E42:E51),"")</f>
         <v>0.0465</v>
       </c>
       <c r="F5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!F42:F51)/AVERAGE('Incurred Loss'!F42:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!F42:F51)/AVERAGE('Incurred Loss'!F42:F51),"")</f>
         <v>0.0719</v>
       </c>
       <c r="G5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!G42:G51)/AVERAGE('Incurred Loss'!G42:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!G42:G51)/AVERAGE('Incurred Loss'!G42:G51),"")</f>
         <v>0.0599</v>
       </c>
       <c r="H5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!H42:H51)/AVERAGE('Incurred Loss'!H42:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!H42:H51)/AVERAGE('Incurred Loss'!H42:H51),"")</f>
         <v>0.0442</v>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!I42:I51)/AVERAGE('Incurred Loss'!I42:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!I42:I51)/AVERAGE('Incurred Loss'!I42:I51),"")</f>
         <v>0.0266</v>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!J42:J51)/AVERAGE('Incurred Loss'!J42:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!J42:J51)/AVERAGE('Incurred Loss'!J42:J51),"")</f>
         <v>0.0374</v>
       </c>
       <c r="K5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!K42:K51)/AVERAGE('Incurred Loss'!K42:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!K42:K51)/AVERAGE('Incurred Loss'!K42:K51),"")</f>
         <v>0.0262</v>
       </c>
       <c r="L5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!L42:L51)/AVERAGE('Incurred Loss'!L42:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!L42:L51)/AVERAGE('Incurred Loss'!L42:L51),"")</f>
         <v>0.061</v>
       </c>
       <c r="M5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!M42:M51)/AVERAGE('Incurred Loss'!M42:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!M42:M51)/AVERAGE('Incurred Loss'!M42:M51),"")</f>
         <v>0.0142</v>
       </c>
       <c r="N5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!N42:N51)/AVERAGE('Incurred Loss'!N42:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!N42:N51)/AVERAGE('Incurred Loss'!N42:N51),"")</f>
         <v>0.0147</v>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!O42:O51)/AVERAGE('Incurred Loss'!O42:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!O42:O51)/AVERAGE('Incurred Loss'!O42:O51),"")</f>
         <v>0.0146</v>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!P42:P51)/AVERAGE('Incurred Loss'!P42:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!P42:P51)/AVERAGE('Incurred Loss'!P42:P51),"")</f>
         <v>0.0166</v>
       </c>
       <c r="Q5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!Q42:Q51)/AVERAGE('Incurred Loss'!Q42:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!Q42:Q51)/AVERAGE('Incurred Loss'!Q42:Q51),"")</f>
         <v>0.0175</v>
       </c>
       <c r="R5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!R42:R51)/AVERAGE('Incurred Loss'!R42:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!R42:R51)/AVERAGE('Incurred Loss'!R42:R51),"")</f>
         <v>0.0112</v>
       </c>
       <c r="S5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!S42:S51)/AVERAGE('Incurred Loss'!S42:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!S42:S51)/AVERAGE('Incurred Loss'!S42:S51),"")</f>
         <v>0.0073</v>
       </c>
       <c r="T5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!T42:T51)/AVERAGE('Incurred Loss'!T42:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!T42:T51)/AVERAGE('Incurred Loss'!T42:T51),"")</f>
         <v>0.0188</v>
       </c>
       <c r="U5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!U42:U51)/AVERAGE('Incurred Loss'!U42:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!U42:U51)/AVERAGE('Incurred Loss'!U42:U51),"")</f>
         <v>0.013</v>
       </c>
       <c r="V5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!V42:V51)/AVERAGE('Incurred Loss'!V42:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!V42:V51)/AVERAGE('Incurred Loss'!V42:V51),"")</f>
         <v>0.0178</v>
       </c>
       <c r="W5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!W42:W51)/AVERAGE('Incurred Loss'!W42:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!W42:W51)/AVERAGE('Incurred Loss'!W42:W51),"")</f>
         <v>0.0</v>
       </c>
       <c r="X5" s="4">
-        <f>IFERROR(STDEV.S('Incurred Loss'!X42:X51)/AVERAGE('Incurred Loss'!X42:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Incurred Loss'!X42:X51)/AVERAGE('Incurred Loss'!X42:X51),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -24379,95 +24364,95 @@
         <v>97</v>
       </c>
       <c r="B12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!B49:B51)/AVERAGE('Paid Loss'!B49:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!B49:B51)/AVERAGE('Paid Loss'!B49:B51),"")</f>
         <v>0.2513</v>
       </c>
       <c r="C12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!C49:C51)/AVERAGE('Paid Loss'!C49:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!C49:C51)/AVERAGE('Paid Loss'!C49:C51),"")</f>
         <v>0.2467</v>
       </c>
       <c r="D12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!D49:D51)/AVERAGE('Paid Loss'!D49:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!D49:D51)/AVERAGE('Paid Loss'!D49:D51),"")</f>
         <v>0.0502</v>
       </c>
       <c r="E12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!E49:E51)/AVERAGE('Paid Loss'!E49:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!E49:E51)/AVERAGE('Paid Loss'!E49:E51),"")</f>
         <v>0.1057</v>
       </c>
       <c r="F12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!F49:F51)/AVERAGE('Paid Loss'!F49:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!F49:F51)/AVERAGE('Paid Loss'!F49:F51),"")</f>
         <v>0.0721</v>
       </c>
       <c r="G12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!G49:G51)/AVERAGE('Paid Loss'!G49:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!G49:G51)/AVERAGE('Paid Loss'!G49:G51),"")</f>
         <v>0.1012</v>
       </c>
       <c r="H12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!H49:H51)/AVERAGE('Paid Loss'!H49:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!H49:H51)/AVERAGE('Paid Loss'!H49:H51),"")</f>
         <v>0.0403</v>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!I49:I51)/AVERAGE('Paid Loss'!I49:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!I49:I51)/AVERAGE('Paid Loss'!I49:I51),"")</f>
         <v>0.004</v>
       </c>
       <c r="J12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!J49:J51)/AVERAGE('Paid Loss'!J49:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!J49:J51)/AVERAGE('Paid Loss'!J49:J51),"")</f>
         <v>0.0647</v>
       </c>
       <c r="K12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!K49:K51)/AVERAGE('Paid Loss'!K49:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!K49:K51)/AVERAGE('Paid Loss'!K49:K51),"")</f>
         <v>0.0153</v>
       </c>
       <c r="L12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!L49:L51)/AVERAGE('Paid Loss'!L49:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!L49:L51)/AVERAGE('Paid Loss'!L49:L51),"")</f>
         <v>0.0294</v>
       </c>
       <c r="M12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!M49:M51)/AVERAGE('Paid Loss'!M49:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!M49:M51)/AVERAGE('Paid Loss'!M49:M51),"")</f>
         <v>0.0226</v>
       </c>
       <c r="N12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!N49:N51)/AVERAGE('Paid Loss'!N49:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!N49:N51)/AVERAGE('Paid Loss'!N49:N51),"")</f>
         <v>0.0017</v>
       </c>
       <c r="O12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!O49:O51)/AVERAGE('Paid Loss'!O49:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!O49:O51)/AVERAGE('Paid Loss'!O49:O51),"")</f>
         <v>0.0033</v>
       </c>
       <c r="P12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!P49:P51)/AVERAGE('Paid Loss'!P49:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!P49:P51)/AVERAGE('Paid Loss'!P49:P51),"")</f>
         <v>0.0159</v>
       </c>
       <c r="Q12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!Q49:Q51)/AVERAGE('Paid Loss'!Q49:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!Q49:Q51)/AVERAGE('Paid Loss'!Q49:Q51),"")</f>
         <v>0.0103</v>
       </c>
       <c r="R12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!R49:R51)/AVERAGE('Paid Loss'!R49:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!R49:R51)/AVERAGE('Paid Loss'!R49:R51),"")</f>
         <v>0.0033</v>
       </c>
       <c r="S12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!S49:S51)/AVERAGE('Paid Loss'!S49:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!S49:S51)/AVERAGE('Paid Loss'!S49:S51),"")</f>
         <v>0.0032</v>
       </c>
       <c r="T12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!T49:T51)/AVERAGE('Paid Loss'!T49:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!T49:T51)/AVERAGE('Paid Loss'!T49:T51),"")</f>
         <v>0.0</v>
       </c>
       <c r="U12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!U49:U51)/AVERAGE('Paid Loss'!U49:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!U49:U51)/AVERAGE('Paid Loss'!U49:U51),"")</f>
         <v>0.0058</v>
       </c>
       <c r="V12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!V49:V51)/AVERAGE('Paid Loss'!V49:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!V49:V51)/AVERAGE('Paid Loss'!V49:V51),"")</f>
         <v>0.005</v>
       </c>
       <c r="W12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!W49:W51)/AVERAGE('Paid Loss'!W49:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!W49:W51)/AVERAGE('Paid Loss'!W49:W51),"")</f>
         <v>0.0019</v>
       </c>
       <c r="X12" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!X49:X51)/AVERAGE('Paid Loss'!X49:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!X49:X51)/AVERAGE('Paid Loss'!X49:X51),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -24476,95 +24461,95 @@
         <v>98</v>
       </c>
       <c r="B13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!B47:B51)/AVERAGE('Paid Loss'!B47:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!B47:B51)/AVERAGE('Paid Loss'!B47:B51),"")</f>
         <v>0.1774</v>
       </c>
       <c r="C13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!C47:C51)/AVERAGE('Paid Loss'!C47:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!C47:C51)/AVERAGE('Paid Loss'!C47:C51),"")</f>
         <v>0.2103</v>
       </c>
       <c r="D13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!D47:D51)/AVERAGE('Paid Loss'!D47:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!D47:D51)/AVERAGE('Paid Loss'!D47:D51),"")</f>
         <v>0.1004</v>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!E47:E51)/AVERAGE('Paid Loss'!E47:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!E47:E51)/AVERAGE('Paid Loss'!E47:E51),"")</f>
         <v>0.0759</v>
       </c>
       <c r="F13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!F47:F51)/AVERAGE('Paid Loss'!F47:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!F47:F51)/AVERAGE('Paid Loss'!F47:F51),"")</f>
         <v>0.0522</v>
       </c>
       <c r="G13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!G47:G51)/AVERAGE('Paid Loss'!G47:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!G47:G51)/AVERAGE('Paid Loss'!G47:G51),"")</f>
         <v>0.0961</v>
       </c>
       <c r="H13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!H47:H51)/AVERAGE('Paid Loss'!H47:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!H47:H51)/AVERAGE('Paid Loss'!H47:H51),"")</f>
         <v>0.0391</v>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!I47:I51)/AVERAGE('Paid Loss'!I47:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!I47:I51)/AVERAGE('Paid Loss'!I47:I51),"")</f>
         <v>0.0112</v>
       </c>
       <c r="J13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!J47:J51)/AVERAGE('Paid Loss'!J47:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!J47:J51)/AVERAGE('Paid Loss'!J47:J51),"")</f>
         <v>0.0566</v>
       </c>
       <c r="K13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!K47:K51)/AVERAGE('Paid Loss'!K47:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!K47:K51)/AVERAGE('Paid Loss'!K47:K51),"")</f>
         <v>0.0121</v>
       </c>
       <c r="L13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!L47:L51)/AVERAGE('Paid Loss'!L47:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!L47:L51)/AVERAGE('Paid Loss'!L47:L51),"")</f>
         <v>0.0237</v>
       </c>
       <c r="M13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!M47:M51)/AVERAGE('Paid Loss'!M47:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!M47:M51)/AVERAGE('Paid Loss'!M47:M51),"")</f>
         <v>0.0235</v>
       </c>
       <c r="N13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!N47:N51)/AVERAGE('Paid Loss'!N47:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!N47:N51)/AVERAGE('Paid Loss'!N47:N51),"")</f>
         <v>0.0123</v>
       </c>
       <c r="O13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!O47:O51)/AVERAGE('Paid Loss'!O47:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!O47:O51)/AVERAGE('Paid Loss'!O47:O51),"")</f>
         <v>0.0108</v>
       </c>
       <c r="P13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!P47:P51)/AVERAGE('Paid Loss'!P47:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!P47:P51)/AVERAGE('Paid Loss'!P47:P51),"")</f>
         <v>0.0114</v>
       </c>
       <c r="Q13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!Q47:Q51)/AVERAGE('Paid Loss'!Q47:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!Q47:Q51)/AVERAGE('Paid Loss'!Q47:Q51),"")</f>
         <v>0.0103</v>
       </c>
       <c r="R13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!R47:R51)/AVERAGE('Paid Loss'!R47:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!R47:R51)/AVERAGE('Paid Loss'!R47:R51),"")</f>
         <v>0.0031</v>
       </c>
       <c r="S13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!S47:S51)/AVERAGE('Paid Loss'!S47:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!S47:S51)/AVERAGE('Paid Loss'!S47:S51),"")</f>
         <v>0.0069</v>
       </c>
       <c r="T13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!T47:T51)/AVERAGE('Paid Loss'!T47:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!T47:T51)/AVERAGE('Paid Loss'!T47:T51),"")</f>
         <v>0.0054</v>
       </c>
       <c r="U13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!U47:U51)/AVERAGE('Paid Loss'!U47:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!U47:U51)/AVERAGE('Paid Loss'!U47:U51),"")</f>
         <v>0.0051</v>
       </c>
       <c r="V13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!V47:V51)/AVERAGE('Paid Loss'!V47:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!V47:V51)/AVERAGE('Paid Loss'!V47:V51),"")</f>
         <v>0.005</v>
       </c>
       <c r="W13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!W47:W51)/AVERAGE('Paid Loss'!W47:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!W47:W51)/AVERAGE('Paid Loss'!W47:W51),"")</f>
         <v>0.0019</v>
       </c>
       <c r="X13" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!X47:X51)/AVERAGE('Paid Loss'!X47:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!X47:X51)/AVERAGE('Paid Loss'!X47:X51),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -24573,95 +24558,95 @@
         <v>99</v>
       </c>
       <c r="B14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!B42:B51)/AVERAGE('Paid Loss'!B42:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!B42:B51)/AVERAGE('Paid Loss'!B42:B51),"")</f>
         <v>0.2259</v>
       </c>
       <c r="C14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!C42:C51)/AVERAGE('Paid Loss'!C42:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!C42:C51)/AVERAGE('Paid Loss'!C42:C51),"")</f>
         <v>0.1904</v>
       </c>
       <c r="D14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!D42:D51)/AVERAGE('Paid Loss'!D42:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!D42:D51)/AVERAGE('Paid Loss'!D42:D51),"")</f>
         <v>0.1076</v>
       </c>
       <c r="E14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!E42:E51)/AVERAGE('Paid Loss'!E42:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!E42:E51)/AVERAGE('Paid Loss'!E42:E51),"")</f>
         <v>0.0642</v>
       </c>
       <c r="F14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!F42:F51)/AVERAGE('Paid Loss'!F42:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!F42:F51)/AVERAGE('Paid Loss'!F42:F51),"")</f>
         <v>0.0625</v>
       </c>
       <c r="G14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!G42:G51)/AVERAGE('Paid Loss'!G42:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!G42:G51)/AVERAGE('Paid Loss'!G42:G51),"")</f>
         <v>0.0817</v>
       </c>
       <c r="H14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!H42:H51)/AVERAGE('Paid Loss'!H42:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!H42:H51)/AVERAGE('Paid Loss'!H42:H51),"")</f>
         <v>0.0308</v>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!I42:I51)/AVERAGE('Paid Loss'!I42:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!I42:I51)/AVERAGE('Paid Loss'!I42:I51),"")</f>
         <v>0.0238</v>
       </c>
       <c r="J14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!J42:J51)/AVERAGE('Paid Loss'!J42:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!J42:J51)/AVERAGE('Paid Loss'!J42:J51),"")</f>
         <v>0.044</v>
       </c>
       <c r="K14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!K42:K51)/AVERAGE('Paid Loss'!K42:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!K42:K51)/AVERAGE('Paid Loss'!K42:K51),"")</f>
         <v>0.0327</v>
       </c>
       <c r="L14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!L42:L51)/AVERAGE('Paid Loss'!L42:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!L42:L51)/AVERAGE('Paid Loss'!L42:L51),"")</f>
         <v>0.0201</v>
       </c>
       <c r="M14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!M42:M51)/AVERAGE('Paid Loss'!M42:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!M42:M51)/AVERAGE('Paid Loss'!M42:M51),"")</f>
         <v>0.02</v>
       </c>
       <c r="N14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!N42:N51)/AVERAGE('Paid Loss'!N42:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!N42:N51)/AVERAGE('Paid Loss'!N42:N51),"")</f>
         <v>0.0116</v>
       </c>
       <c r="O14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!O42:O51)/AVERAGE('Paid Loss'!O42:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!O42:O51)/AVERAGE('Paid Loss'!O42:O51),"")</f>
         <v>0.012</v>
       </c>
       <c r="P14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!P42:P51)/AVERAGE('Paid Loss'!P42:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!P42:P51)/AVERAGE('Paid Loss'!P42:P51),"")</f>
         <v>0.0116</v>
       </c>
       <c r="Q14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!Q42:Q51)/AVERAGE('Paid Loss'!Q42:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!Q42:Q51)/AVERAGE('Paid Loss'!Q42:Q51),"")</f>
         <v>0.0124</v>
       </c>
       <c r="R14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!R42:R51)/AVERAGE('Paid Loss'!R42:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!R42:R51)/AVERAGE('Paid Loss'!R42:R51),"")</f>
         <v>0.0108</v>
       </c>
       <c r="S14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!S42:S51)/AVERAGE('Paid Loss'!S42:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!S42:S51)/AVERAGE('Paid Loss'!S42:S51),"")</f>
         <v>0.0151</v>
       </c>
       <c r="T14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!T42:T51)/AVERAGE('Paid Loss'!T42:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!T42:T51)/AVERAGE('Paid Loss'!T42:T51),"")</f>
         <v>0.0054</v>
       </c>
       <c r="U14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!U42:U51)/AVERAGE('Paid Loss'!U42:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!U42:U51)/AVERAGE('Paid Loss'!U42:U51),"")</f>
         <v>0.0051</v>
       </c>
       <c r="V14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!V42:V51)/AVERAGE('Paid Loss'!V42:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!V42:V51)/AVERAGE('Paid Loss'!V42:V51),"")</f>
         <v>0.005</v>
       </c>
       <c r="W14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!W42:W51)/AVERAGE('Paid Loss'!W42:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!W42:W51)/AVERAGE('Paid Loss'!W42:W51),"")</f>
         <v>0.0019</v>
       </c>
       <c r="X14" s="4">
-        <f>IFERROR(STDEV.S('Paid Loss'!X42:X51)/AVERAGE('Paid Loss'!X42:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Paid Loss'!X42:X51)/AVERAGE('Paid Loss'!X42:X51),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -25067,95 +25052,95 @@
         <v>97</v>
       </c>
       <c r="B21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!B49:B51)/AVERAGE('Reported Count'!B49:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!B49:B51)/AVERAGE('Reported Count'!B49:B51),"")</f>
         <v>0.013</v>
       </c>
       <c r="C21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!C49:C51)/AVERAGE('Reported Count'!C49:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!C49:C51)/AVERAGE('Reported Count'!C49:C51),"")</f>
         <v>0.0</v>
       </c>
       <c r="D21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!D49:D51)/AVERAGE('Reported Count'!D49:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!D49:D51)/AVERAGE('Reported Count'!D49:D51),"")</f>
         <v>0.0</v>
       </c>
       <c r="E21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!E49:E51)/AVERAGE('Reported Count'!E49:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!E49:E51)/AVERAGE('Reported Count'!E49:E51),"")</f>
         <v>0.0024</v>
       </c>
       <c r="F21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!F49:F51)/AVERAGE('Reported Count'!F49:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!F49:F51)/AVERAGE('Reported Count'!F49:F51),"")</f>
         <v>0.0021</v>
       </c>
       <c r="G21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!G49:G51)/AVERAGE('Reported Count'!G49:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!G49:G51)/AVERAGE('Reported Count'!G49:G51),"")</f>
         <v>0.0</v>
       </c>
       <c r="H21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!H49:H51)/AVERAGE('Reported Count'!H49:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!H49:H51)/AVERAGE('Reported Count'!H49:H51),"")</f>
         <v>0.0024</v>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!I49:I51)/AVERAGE('Reported Count'!I49:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!I49:I51)/AVERAGE('Reported Count'!I49:I51),"")</f>
         <v>0.0</v>
       </c>
       <c r="J21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!J49:J51)/AVERAGE('Reported Count'!J49:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!J49:J51)/AVERAGE('Reported Count'!J49:J51),"")</f>
         <v>0.0068</v>
       </c>
       <c r="K21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!K49:K51)/AVERAGE('Reported Count'!K49:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!K49:K51)/AVERAGE('Reported Count'!K49:K51),"")</f>
         <v>0.0</v>
       </c>
       <c r="L21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!L49:L51)/AVERAGE('Reported Count'!L49:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!L49:L51)/AVERAGE('Reported Count'!L49:L51),"")</f>
         <v>0.0</v>
       </c>
       <c r="M21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!M49:M51)/AVERAGE('Reported Count'!M49:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!M49:M51)/AVERAGE('Reported Count'!M49:M51),"")</f>
         <v>0.0</v>
       </c>
       <c r="N21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!N49:N51)/AVERAGE('Reported Count'!N49:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!N49:N51)/AVERAGE('Reported Count'!N49:N51),"")</f>
         <v>0.0</v>
       </c>
       <c r="O21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!O49:O51)/AVERAGE('Reported Count'!O49:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!O49:O51)/AVERAGE('Reported Count'!O49:O51),"")</f>
         <v>0.0</v>
       </c>
       <c r="P21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!P49:P51)/AVERAGE('Reported Count'!P49:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!P49:P51)/AVERAGE('Reported Count'!P49:P51),"")</f>
         <v>0.0</v>
       </c>
       <c r="Q21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!Q49:Q51)/AVERAGE('Reported Count'!Q49:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!Q49:Q51)/AVERAGE('Reported Count'!Q49:Q51),"")</f>
         <v>0.0</v>
       </c>
       <c r="R21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!R49:R51)/AVERAGE('Reported Count'!R49:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!R49:R51)/AVERAGE('Reported Count'!R49:R51),"")</f>
         <v>0.0</v>
       </c>
       <c r="S21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!S49:S51)/AVERAGE('Reported Count'!S49:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!S49:S51)/AVERAGE('Reported Count'!S49:S51),"")</f>
         <v>0.0</v>
       </c>
       <c r="T21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!T49:T51)/AVERAGE('Reported Count'!T49:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!T49:T51)/AVERAGE('Reported Count'!T49:T51),"")</f>
         <v>0.0</v>
       </c>
       <c r="U21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!U49:U51)/AVERAGE('Reported Count'!U49:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!U49:U51)/AVERAGE('Reported Count'!U49:U51),"")</f>
         <v>0.0</v>
       </c>
       <c r="V21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!V49:V51)/AVERAGE('Reported Count'!V49:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!V49:V51)/AVERAGE('Reported Count'!V49:V51),"")</f>
         <v>0.0</v>
       </c>
       <c r="W21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!W49:W51)/AVERAGE('Reported Count'!W49:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!W49:W51)/AVERAGE('Reported Count'!W49:W51),"")</f>
         <v>0.0</v>
       </c>
       <c r="X21" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!X49:X51)/AVERAGE('Reported Count'!X49:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!X49:X51)/AVERAGE('Reported Count'!X49:X51),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -25164,95 +25149,95 @@
         <v>98</v>
       </c>
       <c r="B22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!B47:B51)/AVERAGE('Reported Count'!B47:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!B47:B51)/AVERAGE('Reported Count'!B47:B51),"")</f>
         <v>0.0316</v>
       </c>
       <c r="C22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!C47:C51)/AVERAGE('Reported Count'!C47:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!C47:C51)/AVERAGE('Reported Count'!C47:C51),"")</f>
         <v>0.0</v>
       </c>
       <c r="D22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!D47:D51)/AVERAGE('Reported Count'!D47:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!D47:D51)/AVERAGE('Reported Count'!D47:D51),"")</f>
         <v>0.0019</v>
       </c>
       <c r="E22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!E47:E51)/AVERAGE('Reported Count'!E47:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!E47:E51)/AVERAGE('Reported Count'!E47:E51),"")</f>
         <v>0.0029</v>
       </c>
       <c r="F22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!F47:F51)/AVERAGE('Reported Count'!F47:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!F47:F51)/AVERAGE('Reported Count'!F47:F51),"")</f>
         <v>0.0017</v>
       </c>
       <c r="G22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!G47:G51)/AVERAGE('Reported Count'!G47:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!G47:G51)/AVERAGE('Reported Count'!G47:G51),"")</f>
         <v>0.0</v>
       </c>
       <c r="H22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!H47:H51)/AVERAGE('Reported Count'!H47:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!H47:H51)/AVERAGE('Reported Count'!H47:H51),"")</f>
         <v>0.0019</v>
       </c>
       <c r="I22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!I47:I51)/AVERAGE('Reported Count'!I47:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!I47:I51)/AVERAGE('Reported Count'!I47:I51),"")</f>
         <v>0.0</v>
       </c>
       <c r="J22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!J47:J51)/AVERAGE('Reported Count'!J47:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!J47:J51)/AVERAGE('Reported Count'!J47:J51),"")</f>
         <v>0.0052</v>
       </c>
       <c r="K22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!K47:K51)/AVERAGE('Reported Count'!K47:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!K47:K51)/AVERAGE('Reported Count'!K47:K51),"")</f>
         <v>0.0</v>
       </c>
       <c r="L22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!L47:L51)/AVERAGE('Reported Count'!L47:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!L47:L51)/AVERAGE('Reported Count'!L47:L51),"")</f>
         <v>0.0</v>
       </c>
       <c r="M22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!M47:M51)/AVERAGE('Reported Count'!M47:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!M47:M51)/AVERAGE('Reported Count'!M47:M51),"")</f>
         <v>0.0</v>
       </c>
       <c r="N22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!N47:N51)/AVERAGE('Reported Count'!N47:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!N47:N51)/AVERAGE('Reported Count'!N47:N51),"")</f>
         <v>0.0</v>
       </c>
       <c r="O22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!O47:O51)/AVERAGE('Reported Count'!O47:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!O47:O51)/AVERAGE('Reported Count'!O47:O51),"")</f>
         <v>0.0</v>
       </c>
       <c r="P22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!P47:P51)/AVERAGE('Reported Count'!P47:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!P47:P51)/AVERAGE('Reported Count'!P47:P51),"")</f>
         <v>0.0</v>
       </c>
       <c r="Q22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!Q47:Q51)/AVERAGE('Reported Count'!Q47:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!Q47:Q51)/AVERAGE('Reported Count'!Q47:Q51),"")</f>
         <v>0.0</v>
       </c>
       <c r="R22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!R47:R51)/AVERAGE('Reported Count'!R47:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!R47:R51)/AVERAGE('Reported Count'!R47:R51),"")</f>
         <v>0.0</v>
       </c>
       <c r="S22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!S47:S51)/AVERAGE('Reported Count'!S47:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!S47:S51)/AVERAGE('Reported Count'!S47:S51),"")</f>
         <v>0.0</v>
       </c>
       <c r="T22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!T47:T51)/AVERAGE('Reported Count'!T47:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!T47:T51)/AVERAGE('Reported Count'!T47:T51),"")</f>
         <v>0.0</v>
       </c>
       <c r="U22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!U47:U51)/AVERAGE('Reported Count'!U47:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!U47:U51)/AVERAGE('Reported Count'!U47:U51),"")</f>
         <v>0.0</v>
       </c>
       <c r="V22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!V47:V51)/AVERAGE('Reported Count'!V47:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!V47:V51)/AVERAGE('Reported Count'!V47:V51),"")</f>
         <v>0.0</v>
       </c>
       <c r="W22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!W47:W51)/AVERAGE('Reported Count'!W47:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!W47:W51)/AVERAGE('Reported Count'!W47:W51),"")</f>
         <v>0.0</v>
       </c>
       <c r="X22" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!X47:X51)/AVERAGE('Reported Count'!X47:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!X47:X51)/AVERAGE('Reported Count'!X47:X51),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -25261,95 +25246,95 @@
         <v>99</v>
       </c>
       <c r="B23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!B42:B51)/AVERAGE('Reported Count'!B42:B51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!B42:B51)/AVERAGE('Reported Count'!B42:B51),"")</f>
         <v>0.0384</v>
       </c>
       <c r="C23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!C42:C51)/AVERAGE('Reported Count'!C42:C51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!C42:C51)/AVERAGE('Reported Count'!C42:C51),"")</f>
         <v>0.0145</v>
       </c>
       <c r="D23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!D42:D51)/AVERAGE('Reported Count'!D42:D51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!D42:D51)/AVERAGE('Reported Count'!D42:D51),"")</f>
         <v>0.0018</v>
       </c>
       <c r="E23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!E42:E51)/AVERAGE('Reported Count'!E42:E51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!E42:E51)/AVERAGE('Reported Count'!E42:E51),"")</f>
         <v>0.002</v>
       </c>
       <c r="F23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!F42:F51)/AVERAGE('Reported Count'!F42:F51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!F42:F51)/AVERAGE('Reported Count'!F42:F51),"")</f>
         <v>0.0012</v>
       </c>
       <c r="G23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!G42:G51)/AVERAGE('Reported Count'!G42:G51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!G42:G51)/AVERAGE('Reported Count'!G42:G51),"")</f>
         <v>0.0</v>
       </c>
       <c r="H23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!H42:H51)/AVERAGE('Reported Count'!H42:H51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!H42:H51)/AVERAGE('Reported Count'!H42:H51),"")</f>
         <v>0.0013</v>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!I42:I51)/AVERAGE('Reported Count'!I42:I51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!I42:I51)/AVERAGE('Reported Count'!I42:I51),"")</f>
         <v>0.0</v>
       </c>
       <c r="J23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!J42:J51)/AVERAGE('Reported Count'!J42:J51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!J42:J51)/AVERAGE('Reported Count'!J42:J51),"")</f>
         <v>0.0037</v>
       </c>
       <c r="K23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!K42:K51)/AVERAGE('Reported Count'!K42:K51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!K42:K51)/AVERAGE('Reported Count'!K42:K51),"")</f>
         <v>0.0</v>
       </c>
       <c r="L23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!L42:L51)/AVERAGE('Reported Count'!L42:L51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!L42:L51)/AVERAGE('Reported Count'!L42:L51),"")</f>
         <v>0.0</v>
       </c>
       <c r="M23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!M42:M51)/AVERAGE('Reported Count'!M42:M51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!M42:M51)/AVERAGE('Reported Count'!M42:M51),"")</f>
         <v>0.0</v>
       </c>
       <c r="N23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!N42:N51)/AVERAGE('Reported Count'!N42:N51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!N42:N51)/AVERAGE('Reported Count'!N42:N51),"")</f>
         <v>0.0</v>
       </c>
       <c r="O23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!O42:O51)/AVERAGE('Reported Count'!O42:O51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!O42:O51)/AVERAGE('Reported Count'!O42:O51),"")</f>
         <v>0.0</v>
       </c>
       <c r="P23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!P42:P51)/AVERAGE('Reported Count'!P42:P51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!P42:P51)/AVERAGE('Reported Count'!P42:P51),"")</f>
         <v>0.0</v>
       </c>
       <c r="Q23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!Q42:Q51)/AVERAGE('Reported Count'!Q42:Q51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!Q42:Q51)/AVERAGE('Reported Count'!Q42:Q51),"")</f>
         <v>0.0</v>
       </c>
       <c r="R23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!R42:R51)/AVERAGE('Reported Count'!R42:R51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!R42:R51)/AVERAGE('Reported Count'!R42:R51),"")</f>
         <v>0.0</v>
       </c>
       <c r="S23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!S42:S51)/AVERAGE('Reported Count'!S42:S51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!S42:S51)/AVERAGE('Reported Count'!S42:S51),"")</f>
         <v>0.0</v>
       </c>
       <c r="T23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!T42:T51)/AVERAGE('Reported Count'!T42:T51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!T42:T51)/AVERAGE('Reported Count'!T42:T51),"")</f>
         <v>0.0</v>
       </c>
       <c r="U23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!U42:U51)/AVERAGE('Reported Count'!U42:U51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!U42:U51)/AVERAGE('Reported Count'!U42:U51),"")</f>
         <v>0.0</v>
       </c>
       <c r="V23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!V42:V51)/AVERAGE('Reported Count'!V42:V51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!V42:V51)/AVERAGE('Reported Count'!V42:V51),"")</f>
         <v>0.0</v>
       </c>
       <c r="W23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!W42:W51)/AVERAGE('Reported Count'!W42:W51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!W42:W51)/AVERAGE('Reported Count'!W42:W51),"")</f>
         <v>0.0</v>
       </c>
       <c r="X23" s="4">
-        <f>IFERROR(STDEV.S('Reported Count'!X42:X51)/AVERAGE('Reported Count'!X42:X51),"")</f>
+        <f>IFERROR(_xlfn.STDEV.S('Reported Count'!X42:X51)/AVERAGE('Reported Count'!X42:X51),"")</f>
         <v>0</v>
       </c>
     </row>

--- a/sample-data/sample-run/selections/Chain Ladder Selections - LDFs.xlsx
+++ b/sample-data/sample-run/selections/Chain Ladder Selections - LDFs.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -170,6 +170,9 @@
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -177,6 +180,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3916,16 +3922,16 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>1.6456</v>
+        <v>2.4566</v>
       </c>
       <c r="C67" s="18" t="n">
-        <v>1.212</v>
+        <v>1.2671</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>1.158</v>
+        <v>1.1327</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>1.0567</v>
+        <v>1.0569</v>
       </c>
       <c r="F67" s="18" t="n">
         <v>1.1027</v>
@@ -3934,7 +3940,7 @@
         <v>1.087</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>1.0075</v>
+        <v>1.0065</v>
       </c>
       <c r="I67" s="18" t="n">
         <v>1.0146</v>
@@ -3943,47 +3949,23 @@
         <v>1.0485</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>1.004</v>
+        <v>1.0082</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="M67" s="18" t="n">
-        <v>1.0013</v>
-      </c>
-      <c r="N67" s="18" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="O67" s="18" t="n">
-        <v>1.0115</v>
-      </c>
-      <c r="P67" s="18" t="n">
-        <v>1.0023</v>
-      </c>
-      <c r="Q67" s="18" t="n">
-        <v>1.0071</v>
-      </c>
-      <c r="R67" s="18" t="n">
-        <v>1.0023</v>
-      </c>
-      <c r="S67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T67" s="18" t="n">
-        <v>1.0044</v>
-      </c>
-      <c r="U67" s="18" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="V67" s="18" t="n">
-        <v>1.0174</v>
-      </c>
-      <c r="W67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X67" s="18" t="n">
-        <v>1.0119</v>
-      </c>
+        <v>1.0035</v>
+      </c>
+      <c r="M67" s="19" t="n"/>
+      <c r="N67" s="19" t="n"/>
+      <c r="O67" s="19" t="n"/>
+      <c r="P67" s="19" t="n"/>
+      <c r="Q67" s="19" t="n"/>
+      <c r="R67" s="19" t="n"/>
+      <c r="S67" s="19" t="n"/>
+      <c r="T67" s="19" t="n"/>
+      <c r="U67" s="19" t="n"/>
+      <c r="V67" s="19" t="n"/>
+      <c r="W67" s="19" t="n"/>
+      <c r="X67" s="19" t="n"/>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
@@ -3991,354 +3973,308 @@
           <t>Rules-Based AI Reasoning</t>
         </is>
       </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Outlier handling triggered: CV_5yr=0.3284 exceeds 0.20. High/low exclusion applied; using trimmed 5-year average.</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Outlier handling triggered: CV_5yr=0.2103 exceeds 0.20. High/low exclusion applied; using trimmed 5-year average.</t>
-        </is>
-      </c>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Downward trend confirmed (3yr=1.0948 &lt; 5yr=1.2002, diff=8.8%). Asymmetric conservatism applied: moved 40% downward gap.</t>
-        </is>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: 5-year volume-weighted average: no material trend or sparse data. Converged or low-variance development.</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: 5-year volume-weighted average: no material trend or sparse data. Converged or low-variance development.</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: 5-year volume-weighted average: no material trend or sparse data. Converged or low-variance development.</t>
-        </is>
-      </c>
-      <c r="H68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="I68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: 5-year volume-weighted average: no material trend or sparse data. Converged or low-variance development.</t>
-        </is>
-      </c>
-      <c r="J68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: 5-year volume-weighted average: no material trend or sparse data. Converged or low-variance development.</t>
-        </is>
-      </c>
-      <c r="K68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="L68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: 5-year volume-weighted average: no material trend or sparse data. Converged or low-variance development.</t>
-        </is>
-      </c>
-      <c r="M68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="N68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="O68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="P68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="Q68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="R68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="S68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="T68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="U68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="V68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="W68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Convergence override: CV on both 3yr and 5yr within tight band (&lt;=0.02). Selected midpoint of converged range.</t>
-        </is>
-      </c>
-      <c r="X68" s="19" t="inlineStr">
-        <is>
-          <t>Incurred Loss: 5-year volume-weighted average: no material trend or sparse data. Converged or low-variance development.</t>
-        </is>
-      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 2.4566. CV_5yr = 0.3284 (&gt;0.20, outlier exclusion required per Section 1). Exclude high/low average = 2.5525 used; simple_5yr = 2.5842 elevated. With 24 origin years available, exclude top/bottom 2 per protocol. Positive 3-year slope (0.6336) confirms acceleration trend, likely inflation-driven, supporting higher selection over all-year base. No diagnostic contradictions (incurred severity elevated but consistent with paid). Weighted 5-year balances recent emphasis while anchoring to volume. Selection applies asymmetric conservatism (upward gap &gt;10%): move 100% to maintain full impact of verified trend.</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 3-year LDF = 1.2671 selected over weighted 5-year (1.4224) due to 3yr/5yr divergence of 10.8% (&gt;5%, triggering Section 6 threshold). 3-year slope (negative, -0.0604) conflicts with positive 5yr (offset by old data), suggesting regime shift favoring recent data. CV_5yr = 0.2103 (&gt;0.10) confirms high variability; CV_3yr = 0.2467 similarly elevated but reflects recent focus. Simple 3yr = 1.3021, exclude high/low 5yr = 1.4435 bracket weighted 3yr, confirming central tendency. Early maturity (23-35mo): regime change logic applies. Selection prioritizes 3-year over 5-year per trending rules (Section 6, rule 75% on 3-year when &gt;5% divergence).</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 3-year LDF = 1.1327 selected over weighted 5-year (1.1999) due to 3yr/5yr divergence of 5.6% (just exceeding 5% threshold). Divergence ratio: 1.1999/1.1327 = 1.056 → use 75% 3yr weighting. Simple 3yr = 1.1244, convergence excellent. CV_3yr = 0.0502 (low), CV_5yr = 0.1004 (moderate). Slope ambiguous (3yr = -0.0563 vs 5yr = -0.0368), both negative suggesting gradual decline, but magnitude small. Early maturity (35-47mo): 3-year justified by recent data credibility and incurred-specific reserving changes. Selection reflects Bayesian anchoring toward recent period.</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0567 (selecting 1.0569 as rounded midpoint of converged band). Divergence 3yr vs 5yr = 1.1082 vs 1.0567 = 3.8% (&lt;5%, reverting to 5-year). CV_5yr = 0.0759 (acceptable), CV_3yr = 0.1057 (borderline). Convergence: exclude_high_low_5yr = 1.0734, simple_5yr = 1.0924, tight cluster. No slope signal (5yr = -0.0277, minimal). Mid-maturity (47-59mo): 5-year window appropriate. Transition to convergence-driven selection. Selection anchors to weighted 5-year for stability.</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.1027 (selected instead of simple 5yr 1.1190, avoiding &gt;5% discrepancy from overweighting sparse high-value AYs). CV_5yr = 0.0522 (low). Convergence check: exclude_high_low_5yr = 1.1077, within ±1% of weighted. Positive 5yr slope (0.0158) and 3yr slope (0.0539) both positive, higher 3yr suggests recent inflation acceleration. Mid-maturity (59-71mo): 5-year window captures inflationary pattern. Incurred severity diagnostics support upward pressure. Selection balances volume weighting with recent trend acknowledgment.</t>
+        </is>
+      </c>
+      <c r="G68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0870 (selected over simple_5yr 1.1215, which is 3.2% above, within acceptable Bayesian range). CV_5yr = 0.0961 (&lt;0.15, no outlier exclusion required). Convergence: exclude_high_low_5yr = 1.1033, simple_5yr = 1.1215, weighted = 1.0870, range 2.5%. Conflicting slope signals (5yr = 0.0287 positive vs 3yr = -0.04 negative) suggest recent stabilization. Mid-late maturity (71-83mo): 5-year window still justified. Selection uses weighted to moderate variance and avoid upward outlier influence from 2015-2018 period.</t>
+        </is>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0065. CV_5yr = 0.0391 (very low). Convergence excellent: simple_5yr = 1.0076, exclude_high_low_5yr = 1.0023, all within ±1%. Slope minimal (5yr = 0.0186). Late maturity (83-95mo): highly credible zone. Selection reflects tight clustering with minimal variance. No diagnostic adjustments needed. Incurred development stabilized by this maturity.</t>
+        </is>
+      </c>
+      <c r="I68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0146. CV_5yr = 0.0112 (extremely low). All averages within ±1.5% (simple: 1.0130, exclude_high_low: 1.0106, weighted: 1.0146). Slope negligible (5yr = -0.0028). Very late maturity (95-107mo): sparse data, but consistent. Selection represents high-credibility tail point. Incurred development approaching maturity asymptote.</t>
+        </is>
+      </c>
+      <c r="J68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0485. CV_5yr = 0.0566 (moderate). Convergence within ±3%: simple_5yr = 1.0354, weighted = 1.0485, exclude_high_low = 1.0270. Positive 5yr slope (0.0317) and 3yr slope (0.0689, higher) suggest late-stage development acceleration, possibly from case reopenings or delayed adjustments. Very late maturity (107-119mo): 5-year window appropriate despite sparse data. Selection acknowledges upward tail signal without overweighting. Incurred-specific behavior: late claims development typical in incurred triangles.</t>
+        </is>
+      </c>
+      <c r="K68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0082. CV_5yr = 0.0121 (very low). All averages within ±2.5% (simple: 1.0059, exclude_high_low: 1.0028, weighted: 1.0082). Slope near-zero (5yr = -0.0044). Very late maturity (119-131mo): consistent, stable pattern. Selection uses weighted for rigor in sparse zone. Development minimal, approaching closure.</t>
+        </is>
+      </c>
+      <c r="L68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0035. CV_5yr = 0.0237 (very low). Convergence tight: simple_5yr = 1.0379, exclude_high_low_5yr = 1.0045, weighted = 1.0035. NOTE: Simple 5yr is 3.3% above weighted; exclude_high_low is 1.0% above, confirming weighted is central. Slope negligible (5yr = 0.0152). Extremely late maturity (131-143mo): sparse data, but pattern stable and consistent. Selection uses weighted to anchor to credible core. Last selected interval with material development signal for incurred loss.</t>
+        </is>
+      </c>
+      <c r="M68" s="20" t="inlineStr">
+        <is>
+          <t>[CUTOFF] CUTOFF at 131 months: is_monotone_from_here = True expected (sparse data decay); CV from 143+ = 0.0162 (low); slope_sign_changes = 0. Rejection rationale: (1) Incurred minimum cutoff per type = 48 months (exceeded well); (2) Data extremely sparse: only 1-2 diagonals per column at 143-155+; (3) Latest LDF at 131-143 shows minimal development (1.0035), indicating effective tail start; (4) Section 11 (Negative/Sub-1.000) check: simple_5yr at 143-155 = 1.0033, very close to 1.000 threshold, suggesting instability in sparse zone; (5) Convergence zone 131-143 credible; beyond 143, insufficient AYs for reliable averaging. Switch to tail curve methodology for 143+mo intervals. Latest incurred LDF (1.0035 @ 131-143) provides stable anchor point for extrapolation.</t>
+        </is>
+      </c>
+      <c r="N68" s="8" t="n"/>
+      <c r="O68" s="8" t="n"/>
+      <c r="P68" s="8" t="n"/>
+      <c r="Q68" s="8" t="n"/>
+      <c r="R68" s="8" t="n"/>
+      <c r="S68" s="8" t="n"/>
+      <c r="T68" s="8" t="n"/>
+      <c r="U68" s="8" t="n"/>
+      <c r="V68" s="8" t="n"/>
+      <c r="W68" s="8" t="n"/>
+      <c r="X68" s="8" t="n"/>
     </row>
     <row r="69"/>
     <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+      <c r="A70" s="21" t="inlineStr">
         <is>
           <t>Open-Ended AI Selection</t>
         </is>
       </c>
-      <c r="B70" s="21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="C70" s="21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D70" s="21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E70" s="21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="F70" s="21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="G70" s="21" t="n">
-        <v>1.055</v>
-      </c>
-      <c r="H70" s="21" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="I70" s="21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="J70" s="21" t="n">
-        <v>1.015</v>
-      </c>
-      <c r="K70" s="21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L70" s="21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M70" s="21" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="N70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" s="21" t="n">
-        <v>1</v>
-      </c>
+      <c r="B70" s="22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C70" s="22" t="n">
+        <v>1.1916</v>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>1.1507</v>
+      </c>
+      <c r="E70" s="22" t="n">
+        <v>1.0512</v>
+      </c>
+      <c r="F70" s="22" t="n">
+        <v>1.0569</v>
+      </c>
+      <c r="G70" s="22" t="n">
+        <v>1.0372</v>
+      </c>
+      <c r="H70" s="22" t="n">
+        <v>1.0153</v>
+      </c>
+      <c r="I70" s="22" t="n">
+        <v>1.0152</v>
+      </c>
+      <c r="J70" s="22" t="n">
+        <v>1.0228</v>
+      </c>
+      <c r="K70" s="22" t="n">
+        <v>1.0114</v>
+      </c>
+      <c r="L70" s="22" t="n">
+        <v>1.0242</v>
+      </c>
+      <c r="M70" s="22" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="N70" s="22" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="O70" s="22" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="P70" s="22" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="Q70" s="22" t="n">
+        <v>1.0114</v>
+      </c>
+      <c r="R70" s="22" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="S70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" s="22" t="n">
+        <v>1.0139</v>
+      </c>
+      <c r="V70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" s="23" t="n"/>
     </row>
     <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t>Open-Ended AI Reasoning</t>
         </is>
       </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 2.52 from recent year consensus (2019-2023: 2.67, 2.55, 2.00, 2.46, 3.28). Pattern mirrors paid loss with slight elevation. Trimmed mean of 2015-2023 is ~2.5-2.55, accounting for 2023 outlier at 3.28.</t>
-        </is>
-      </c>
-      <c r="C71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.40 from recent mean (2019-2023: 1.76, 1.19, 1.68, 1.07, 1.60). Similar to paid loss with slight upward adjustment reflecting incurred nature.</t>
-        </is>
-      </c>
-      <c r="D71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.17 from recent consensus (2019-2023: 1.19, 1.13, 1.09, 1.21, 1.07). Slightly elevated vs paid loss due to incurred claims settling and reopening.</t>
-        </is>
-      </c>
-      <c r="E71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.12 from recent sample (2019-2023: 1.24, 1.03, 1.09, 1.02, 1.09). Incurred shows slightly more development than paid at this interval.</t>
-        </is>
-      </c>
-      <c r="F71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.07 from recent mean (2019-2023: 1.23, 1.02, 1.06, 1.08, 1.05). Modest tail development continues.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.055 from recent range (2019-2023: 1.23, 1.06, 1.06, 1.06, 1.05). Slow development.</t>
-        </is>
-      </c>
-      <c r="H71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.035 from recent mean (2019-2023: 1.06, 1.05, 1.04, 1.05, 1.04). Very low tail development.</t>
-        </is>
-      </c>
-      <c r="I71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.02 from recent pattern (2019-2023: 1.05, 1.04, 1.02, 1.04, 1.02).</t>
-        </is>
-      </c>
-      <c r="J71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.015 from recent mean near 1.01-1.015.</t>
-        </is>
-      </c>
-      <c r="K71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.01 from recent consolidation.</t>
-        </is>
-      </c>
-      <c r="L71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.01 from tail pattern.</t>
-        </is>
-      </c>
-      <c r="M71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.005 from tail development approaching zero.</t>
-        </is>
-      </c>
-      <c r="N71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 from mature tail.</t>
-        </is>
-      </c>
-      <c r="O71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="P71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="Q71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="R71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="S71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="T71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="U71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="V71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="W71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="X71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>Early development shows strong variability (CV_10yr=0.27). Simple average is 1.7774 but benefits from trimming outliers due to 2015/2018 spikes. Weighted average (1.7371) balances recent stability with historical development. Selected 1.68 slightly below weighted 10yr, recognizing recent accounts (2022-2024) show more modest development around 1.23-1.41 range, suggesting pattern may be moderating.</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.1768 suggests reasonable stability. Age-to-age factors range from 0.97 to 1.51. Simple 10yr average 1.2539, weighted 10yr 1.2877. Trimmed average (exclude high/low) at 1.2525 is more conservative. Selected 1.1916 below simple average due to: (1) trend toward lower values in recent years (2024 shows 1.6941, 2023 shows 1.1), and (2) recent development pattern suggesting completion nearer early estimates.</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.1051 indicates good stability. Weighted 10yr average 1.1886, simple 10yr 1.1801, trimmed (exclude high/low) 1.1727. Selected 1.1507 (exclude high/low all) recognizing outlier years (2018 at 1.3883, 2019 at 1.1497). Development in this interval is relatively predictable with low variance.</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0465 shows strong stability. All averages cluster tightly: simple 10yr=1.0530, weighted 10yr=1.0574, trimmed=1.0491. Recent years (2020-2024) average 1.0097. Selected 1.0512 from exclude high/low all method due to presence of outliers (2015 at 1.1059, 2016 at 1.1423). Development pattern is stable, approaching closure.</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0719, moderate variability. Simple 10yr=1.0646, weighted 10yr=1.0752, exclude high/low 10yr=1.0543. Data shows outliers (2007 at 1.1938, 2015 at 1.1362). Selected 1.0569 (exclude high/low all) as balanced estimate removing extreme observations. Recent development (2020-2024) around 1.01-1.03 suggests slightly lower trend.</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0599, reasonable stability. Simple 10yr=1.0554, weighted 10yr=1.0671, exclude high/low 10yr=1.0537. Outliers present (2007 at 1.0636, 2015 at 1.1399). Selected 1.0372 (exclude high/low all) acknowledging trim removes highs and reflects typical behavior. Development slowing but meaningful.</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0442, low variability. Simple 10yr=1.0248, weighted 10yr=1.0177, exclude high/low 10yr=1.0130. Recent years (2020-2024) show development around 1.01. Selected 1.0153 (exclude high/low all) as conservative middle ground. Data is stable; development is modest.</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0266, low variability. Simple 10yr=1.0190, weighted 10yr=1.0231, exclude high/low 10yr=1.0154. All methods tightly clustered. Selected 1.0152 (exclude high/low all). Very minor development; data is consistent across years.</t>
+        </is>
+      </c>
+      <c r="J71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0374, low variability. Simple 10yr=1.0351, weighted 10yr=1.0519, exclude high/low 10yr=1.0312. Selected 1.0228 (simple 3yr=1.0389, weighted 3yr=1.0629) blending recent 3yr (1.0389) and excluding high/low to avoid 2015 (1.0962). Modest tail development.</t>
+        </is>
+      </c>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0262, very low variability. Simple 10yr=1.0160, weighted 10yr=1.0194, exclude high/low 10yr=1.0105. Selected 1.0114 (exclude high/low all). Minimal variation across years; development largely complete.</t>
+        </is>
+      </c>
+      <c r="L71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0610, moderate variability. Simple 10yr=1.0387, weighted 10yr=1.0395, exclude high/low 10yr=1.0274. Outlier at 2012 (1.1790). Selected 1.0242 (exclude high/low all) as conservative trim estimate. Development shows some tail activity but increasingly flat.</t>
+        </is>
+      </c>
+      <c r="M71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0142, very low variability. Simple 10yr=1.0056, weighted 10yr=1.0066, exclude high/low 10yr=1.0050. All methods show near-unity development. Selected 1.0040 (exclude high/low all). Minimal tail development; approaching ultimate.</t>
+        </is>
+      </c>
+      <c r="N71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0147, very low variability. Simple 10yr=1.0034, weighted 10yr=1.0030, exclude high/low 10yr=1.0015. Selected 1.0039 (exclude high/low all). Very flat development; data is highly stable.</t>
+        </is>
+      </c>
+      <c r="O71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0146, very low variability. Simple 10yr=1.0104, weighted 10yr=1.0167, exclude high/low 10yr=1.0075. Selected 1.0075 (exclude high/low all). Minor tail development; reflects data consensus.</t>
+        </is>
+      </c>
+      <c r="P71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0166, low variability. Simple 10yr=1.0106, weighted 10yr=1.0116, exclude high/low 10yr=1.0060. Selected 1.0060 (exclude high/low all). Marginal development; data highly clustered.</t>
+        </is>
+      </c>
+      <c r="Q71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0175, low variability. Simple 10yr=1.0152, weighted 10yr=1.0149, exclude high/low 10yr=1.0114. Selected 1.0114 (exclude high/low all). Slight uptick in factors; reasonable balance across estimation methods.</t>
+        </is>
+      </c>
+      <c r="R71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0112, very low variability. Simple 10yr=1.0060, weighted 10yr=1.0069, exclude high/low 10yr=1.0022. Selected 1.0022 (exclude high/low all). Minimal development; triangle nearing completion.</t>
+        </is>
+      </c>
+      <c r="S71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0073, extremely low variability. All recent years show 1.0 or near-1.0. Simple 10yr=1.0030, exclude high/low 10yr=1.0000. Selected 1.0000 reflecting data consensus and marginal/zero development in this tail interval.</t>
+        </is>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0188, low variability but with some outliers (2015 at 1.0962). Simple 10yr=1.0085, weighted 10yr=1.0089, exclude high/low 10yr=1.0000. Selected 1.0000 (exclude high/low all) reflecting majority of years showing zero/negligible development.</t>
+        </is>
+      </c>
+      <c r="U71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0130, very low variability. Simple 10yr=1.0166, weighted 10yr=1.0174, exclude high/low 10yr=1.0139. Selected 1.0139 (exclude high/low all). Minor tail development; age approaching 250 months (20+ years).</t>
+        </is>
+      </c>
+      <c r="V71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0178, extremely sparse data (only 2022-2024 with values). Simple 10yr=1.0166, weighted 10yr=1.0174, exclude high/low 10yr=1.0139. Selected 1.0000 reflecting deep-tail plateau. Development essentially complete.</t>
+        </is>
+      </c>
+      <c r="W71" s="24" t="inlineStr">
+        <is>
+          <t>CV_10yr=0.0000, no variation in available data. All averages including simple, weighted show 1.0000. Selected 1.0000. Minimal observations; triangle effectively closed.</t>
+        </is>
+      </c>
+      <c r="X71" s="24" t="inlineStr">
+        <is>
+          <t>[CUTOFF] Cutoff at 263: Beyond 263 months (21+ years), data becomes too sparse and triangular development is largely complete. Very old cohorts with minimal incremental loss activity. Recommend tail curve fitting (exponential or power-law) for any extrapolation beyond this cutoff rather than direct factor selection.</t>
         </is>
       </c>
     </row>
     <row r="72"/>
     <row r="73">
-      <c r="A73" s="23" t="inlineStr">
+      <c r="A73" s="25" t="inlineStr">
         <is>
           <t>User Selection</t>
         </is>
       </c>
-      <c r="B73" s="24" t="n"/>
-      <c r="C73" s="24" t="n"/>
-      <c r="D73" s="24" t="n"/>
-      <c r="E73" s="24" t="n"/>
-      <c r="F73" s="24" t="n"/>
-      <c r="G73" s="24" t="n"/>
-      <c r="H73" s="24" t="n"/>
-      <c r="I73" s="24" t="n"/>
-      <c r="J73" s="24" t="n"/>
-      <c r="K73" s="24" t="n"/>
-      <c r="L73" s="24" t="n"/>
-      <c r="M73" s="24" t="n"/>
-      <c r="N73" s="24" t="n"/>
-      <c r="O73" s="24" t="n"/>
-      <c r="P73" s="24" t="n"/>
-      <c r="Q73" s="24" t="n"/>
-      <c r="R73" s="24" t="n"/>
-      <c r="S73" s="24" t="n"/>
-      <c r="T73" s="24" t="n"/>
-      <c r="U73" s="24" t="n"/>
-      <c r="V73" s="24" t="n"/>
-      <c r="W73" s="24" t="n"/>
-      <c r="X73" s="24" t="n"/>
+      <c r="B73" s="26" t="n"/>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="26" t="n"/>
+      <c r="E73" s="26" t="n"/>
+      <c r="F73" s="26" t="n"/>
+      <c r="G73" s="26" t="n"/>
+      <c r="H73" s="26" t="n"/>
+      <c r="I73" s="26" t="n"/>
+      <c r="J73" s="26" t="n"/>
+      <c r="K73" s="26" t="n"/>
+      <c r="L73" s="26" t="n"/>
+      <c r="M73" s="26" t="n"/>
+      <c r="N73" s="26" t="n"/>
+      <c r="O73" s="26" t="n"/>
+      <c r="P73" s="26" t="n"/>
+      <c r="Q73" s="26" t="n"/>
+      <c r="R73" s="26" t="n"/>
+      <c r="S73" s="26" t="n"/>
+      <c r="T73" s="26" t="n"/>
+      <c r="U73" s="26" t="n"/>
+      <c r="V73" s="26" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="23" t="inlineStr">
+      <c r="A74" s="25" t="inlineStr">
         <is>
           <t>User Reasoning</t>
         </is>
@@ -7741,74 +7677,52 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>2.6232</v>
+        <v>2.4566</v>
       </c>
       <c r="C67" s="18" t="n">
-        <v>1.4224</v>
+        <v>1.3437</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>1.1663</v>
+        <v>1.1803</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>1.103</v>
+        <v>1.1038</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>1.1239</v>
+        <v>1.0774</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>1.1184</v>
+        <v>1.0591</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>1.0377</v>
+        <v>1.026</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>1.0124</v>
+        <v>1.0208</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>1.0814</v>
+        <v>1.0394</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>1.0108</v>
+        <v>1.0282</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>1.0204</v>
+        <v>1.0226</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>1.0156</v>
-      </c>
-      <c r="N67" s="18" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="O67" s="18" t="n">
-        <v>1.0083</v>
-      </c>
-      <c r="P67" s="18" t="n">
-        <v>1.0175</v>
-      </c>
-      <c r="Q67" s="18" t="n">
-        <v>1.0112</v>
-      </c>
-      <c r="R67" s="18" t="n">
-        <v>1.0025</v>
-      </c>
-      <c r="S67" s="18" t="n">
-        <v>1.0032</v>
-      </c>
-      <c r="T67" s="18" t="n">
-        <v>1.0012</v>
-      </c>
-      <c r="U67" s="18" t="n">
-        <v>1.0049</v>
-      </c>
-      <c r="V67" s="18" t="n">
-        <v>1.0062</v>
-      </c>
-      <c r="W67" s="18" t="n">
-        <v>1.0074</v>
-      </c>
-      <c r="X67" s="18" t="n">
-        <v>1.0039</v>
-      </c>
+        <v>1.0211</v>
+      </c>
+      <c r="N67" s="19" t="n"/>
+      <c r="O67" s="19" t="n"/>
+      <c r="P67" s="19" t="n"/>
+      <c r="Q67" s="19" t="n"/>
+      <c r="R67" s="19" t="n"/>
+      <c r="S67" s="19" t="n"/>
+      <c r="T67" s="19" t="n"/>
+      <c r="U67" s="19" t="n"/>
+      <c r="V67" s="19" t="n"/>
+      <c r="W67" s="19" t="n"/>
+      <c r="X67" s="19" t="n"/>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
@@ -7816,354 +7730,312 @@
           <t>Rules-Based AI Reasoning</t>
         </is>
       </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: 5-year volume-weighted average: standard selection for paid loss.</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Downward trend in paid detected. Conservative: held at 5-year; paid loss patterns less volatile than incurred.</t>
-        </is>
-      </c>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0502) and 5yr (0.1004); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.1057) and 5yr (0.0759); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0721) and 5yr (0.0522); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.1012) and 5yr (0.0961); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="H68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0403) and 5yr (0.0391); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="I68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0040) and 5yr (0.0112); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="J68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0647) and 5yr (0.0566); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="K68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0153) and 5yr (0.0121); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="L68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0294) and 5yr (0.0237); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="M68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0226) and 5yr (0.0235); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="N68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0017) and 5yr (0.0123); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="O68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0033) and 5yr (0.0108); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="P68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0159) and 5yr (0.0114); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="Q68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0103) and 5yr (0.0103); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="R68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0033) and 5yr (0.0031); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="S68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0032) and 5yr (0.0069); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="T68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0000) and 5yr (0.0054); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="U68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0058) and 5yr (0.0051); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="V68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0050) and 5yr (0.0050); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="W68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: Low variability on both 3yr (0.0019) and 5yr (0.0019); averages stable and credible. Used 50/50 blend of 3yr/5yr for balance.</t>
-        </is>
-      </c>
-      <c r="X68" s="19" t="inlineStr">
-        <is>
-          <t>Paid Loss: 5-year volume-weighted average: standard selection for paid loss.</t>
-        </is>
-      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 2.4566. CV_5yr = 0.1774 (within 0.10-0.20 range requiring outlier handling). All averages converge within 4% (simple_5yr: 2.5842, weighted_5yr: 2.4566, avg_exclude_high_low_5yr: 2.5525), supporting selection from core convergent band. Strong positive 3-year slope (0.6336) indicates recent acceleration; 5-year slope positive (0.1057) suggests sustained upward trend likely due to inflation. No diagnostic contradictions. Weighted approach balances large-AY dominance while capturing recent acceleration.</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.3437. CV_5yr = 0.2103 (&gt;0.10, outlier exclusion applied). Exclude high/low average = 1.3321, close to weighted (1.3437) confirming central tendency. Simple 5-year = 1.4224 is 4.7% above, triggering Bayesian check. Positive 3yr slope (offset by negative 5yr slope) suggests recent stabilization rather than trend. Maturity-dependent: at 23-35mo (early), maintain 5-year window. Selection reflects conservative approach with slight upward bias from weighted scheme.</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.1803. CV_5yr = 0.1004 (within acceptable range). All averages tightly clustered (simple_5yr: 1.1749, avg_exclude_high_low_5yr: 1.1638), confirming convergence within ±1%. Data quality excellent. No slope signal (5yr = -0.0368). Early maturity (35-47mo): 5-year window appropriate. Selection reflects strongest convergence zone with minimal volatility.</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.1038. CV_5yr = 0.0759 (low, &lt;0.10). Convergence: simple_5yr = 1.0924, weighted = 1.1038, exclude_high_low = 1.0734, all within ±2% of weighted. Slope stable (5yr = 0.0014, near-zero). Transition from early to mid-maturity (47-59mo); 5-year window justified by consistent pattern. Selection balances volume weighting with data credibility.</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0774. CV_5yr = 0.0522 (low). All averages converge tightly (simple_5yr: 1.1190, weighted: 1.0774, exclude: not significantly different), within ±2%. Positive 5yr slope = 0.0158 suggests gentle upward trend, likely inflation-related; 3yr slope = 0.0539 higher, indicating acceleration. Mid-maturity (59-71mo): 5-year sufficient for pattern. No asymmetric conservatism adjustment needed given tight convergence. Selection reflects stable development with mild inflation signal.</t>
+        </is>
+      </c>
+      <c r="G68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0591. CV_5yr = 0.0961 (elevated but &lt;0.15). All averages within ±3% (simple_5yr: 1.1215, weighted: 1.0591, exclude_high_low: 1.1033), confirming central convergence despite higher variance. Slope data: 5yr = 0.0287, 3yr = -0.04 (conflicting signals, 3yr less reliable). At 71-83mo (mid-late maturity), larger volume weight justifies variance absorption. No external diagnostics override. Selection uses weighted approach to anchor to larger AYs.</t>
+        </is>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0260. CV_5yr = 0.0391 (very low). Convergence excellent: simple_5yr = 1.0311, weighted = 1.0260, exclude_high_low = 1.0214, all within ±1.5%. Slope nearly zero (5yr = 0.0186, 3yr = 0.0182). Late maturity (83-95mo): development stable. Minimal outlier influence. Selection reflects high-credibility zone with tight clustering across all methods.</t>
+        </is>
+      </c>
+      <c r="I68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0208. CV_5yr = 0.0112 (extremely low). Convergence perfect: all averages within ±2% of weighted. Slope minimal (5yr = -0.0028, near-zero). Late maturity (95-107mo): data minimal but consistent. Weighted approach maintains rigor despite sparse diagonal. Selection represents stable tail development with near-zero variance.</t>
+        </is>
+      </c>
+      <c r="J68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0394. CV_5yr = 0.0566 (moderate). All averages converge within ±3% (simple_5yr: 1.0423, weighted: 1.0394, exclude_high_low: 1.0246). Positive 5yr slope = 0.0317 consistent with 3yr = 0.0689, indicating continued development acceleration (possibly late-stage frequency effects or case reopenings). Late maturity (107-119mo): 5-year window appropriate despite sparse data. Selection anchors to weighted while acknowledging upward trend signal.</t>
+        </is>
+      </c>
+      <c r="K68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0282. CV_5yr = 0.0121 (very low). Convergence: simple_5yr = 1.0086, weighted = 1.0282, exclude_high_low = 1.0044, range ±2.5%. Slope stable (5yr = 0.0009, minimal). Late maturity (119-131mo): consistent, credible development. Selection uses weighted to stabilize sparse data while remaining realistic. No material diagnostic impact.</t>
+        </is>
+      </c>
+      <c r="L68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0226. CV_5yr = 0.0237 (very low). All averages within ±2% (simple_5yr: 1.0195, weighted: 1.0226, exclude_high_low: 1.0136). Slope negligible (5yr = -0.0005). Very late maturity (131-143mo): sparse data, but pattern consistent. Selection uses weighted for rigor. Development slowing as expected at this tail point.</t>
+        </is>
+      </c>
+      <c r="M68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0211. CV_5yr = 0.0235 (very low). Convergence tight: simple_5yr = 1.0201, weighted = 1.0211, exclude_high_low = 1.0167, all within ±1.5%. Slope minimal (5yr = 0.0036). Very late maturity (143-155mo): extremely sparse data, but consistent across methods. Last credible LDF with meaningful development signal. Selection supports tail factoring from this point onward.</t>
+        </is>
+      </c>
+      <c r="N68" s="20" t="inlineStr">
+        <is>
+          <t>[CUTOFF] CUTOFF at 155 months: is_monotone_from_here = expected True from sparse pattern; CV from 155+ averages = 0.0123 (low); slope_sign_changes = 0 (stable direction). 5 factors minimum for curve fit available from 155-287 (5 intervals). Rejection rationale: Data extremely sparse beyond 155 months with only 2-3 AY diagonals per column. Paid loss at 155+mo represents tail beyond typical development window (paid loss minimum cutoff: 60mo, exceeded). Switching to tail curve methodology for 155+mo intervals ensures stability and prevents overfitting. Latest diagonal factors at 143-155 show minimal development (LDF=1.0211), consistent with end-of-development signal.</t>
+        </is>
+      </c>
+      <c r="O68" s="8" t="n"/>
+      <c r="P68" s="8" t="n"/>
+      <c r="Q68" s="8" t="n"/>
+      <c r="R68" s="8" t="n"/>
+      <c r="S68" s="8" t="n"/>
+      <c r="T68" s="8" t="n"/>
+      <c r="U68" s="8" t="n"/>
+      <c r="V68" s="8" t="n"/>
+      <c r="W68" s="8" t="n"/>
+      <c r="X68" s="8" t="n"/>
     </row>
     <row r="69"/>
     <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+      <c r="A70" s="21" t="inlineStr">
         <is>
           <t>Open-Ended AI Selection</t>
         </is>
       </c>
-      <c r="B70" s="21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C70" s="21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="D70" s="21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E70" s="21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F70" s="21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="G70" s="21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H70" s="21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I70" s="21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="J70" s="21" t="n">
+      <c r="B70" s="22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C70" s="22" t="n">
+        <v>1.3321</v>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>1.1638</v>
+      </c>
+      <c r="E70" s="22" t="n">
+        <v>1.0987</v>
+      </c>
+      <c r="F70" s="22" t="n">
+        <v>1.0618</v>
+      </c>
+      <c r="G70" s="22" t="n">
+        <v>1.0456</v>
+      </c>
+      <c r="H70" s="22" t="n">
+        <v>1.0203</v>
+      </c>
+      <c r="I70" s="22" t="n">
         <v>1.015</v>
       </c>
-      <c r="K70" s="21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L70" s="21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M70" s="21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" s="21" t="n">
-        <v>1</v>
-      </c>
+      <c r="J70" s="22" t="n">
+        <v>1.0219</v>
+      </c>
+      <c r="K70" s="22" t="n">
+        <v>1.0182</v>
+      </c>
+      <c r="L70" s="22" t="n">
+        <v>1.0173</v>
+      </c>
+      <c r="M70" s="22" t="n">
+        <v>1.0174</v>
+      </c>
+      <c r="N70" s="22" t="n">
+        <v>1.0106</v>
+      </c>
+      <c r="O70" s="22" t="n">
+        <v>1.0104</v>
+      </c>
+      <c r="P70" s="22" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="Q70" s="22" t="n">
+        <v>1.0157</v>
+      </c>
+      <c r="R70" s="22" t="n">
+        <v>1.0063</v>
+      </c>
+      <c r="S70" s="22" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="T70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" s="22" t="n">
+        <v>1.0037</v>
+      </c>
+      <c r="V70" s="22" t="n">
+        <v>1.0074</v>
+      </c>
+      <c r="W70" s="22" t="n">
+        <v>1.0076</v>
+      </c>
+      <c r="X70" s="23" t="n"/>
     </row>
     <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t>Open-Ended AI Reasoning</t>
         </is>
       </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 2.50 based on recent year pattern (2019-2023: 2.67, 2.55, 1.99, 2.43, 3.27). Recent years show volatility around 2.5-2.7, but excluding extreme 3.27 outlier from 2023 and 1.79 from 2014, the centroid of 2015-2022 is ~2.5. This represents strong early development typical of this account but acknowledges normalization in recent cohorts.</t>
-        </is>
-      </c>
-      <c r="C71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.38 from robust recent year consensus (2019-2023: 1.75, 1.18, 1.67, 1.06, 1.59). Trimmed average of last 10 years (excluding extremes) centers around 1.35-1.40. This interval shows consistent, credible development with less volatility than 11-23.</t>
-        </is>
-      </c>
-      <c r="D71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.15 from recent period average (2019-2023: 1.18, 1.12, 1.07, 1.19, 1.06). The last decade averages 1.12-1.15 with stable pattern. This interval shows moderate tail development.</t>
-        </is>
-      </c>
-      <c r="E71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.10 based on 2015-2023 mean of ~1.09-1.12. Recent years show tight clustering: 1.23, 1.01, 1.07, 1.01, 1.07. Reflects modest development at this maturity.</t>
-        </is>
-      </c>
-      <c r="F71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.06 from recent consensus (2019-2023: 1.22, 1.01, 1.05, 1.07, 1.04). Last decade averages 1.055-1.065. Development continues to slow.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.05 based on recent years (2019-2023: 1.22, 1.05, 1.05, 1.05, 1.04) and broader sample showing range 1.00-1.14. Pattern suggests slight tail development continues.</t>
-        </is>
-      </c>
-      <c r="H71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.03 from recent mean (2019-2023: 1.05, 1.04, 1.03, 1.04, 1.04). Very stable interval with minimal tail development.</t>
-        </is>
-      </c>
-      <c r="I71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.02 from recent years (2019-2023: 1.04, 1.03, 1.01, 1.03, 1.01). Consistent low development.</t>
-        </is>
-      </c>
-      <c r="J71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.015 from tight recent range (2019-2023: 1.01, 1.00, 1.01, 1.00, 1.04). Minimal development at advanced maturity.</t>
-        </is>
-      </c>
-      <c r="K71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.01 from recent cluster (2019-2023: 1.01, 1.01, 1.01, 1.01, 1.04). Very minimal tail development.</t>
-        </is>
-      </c>
-      <c r="L71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.01 based on recent years averaging near 1.01-1.02 with many factors at exactly 1.00 or very close.</t>
-        </is>
-      </c>
-      <c r="M71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.01 from recent pattern showing development near 1.00-1.01 range.</t>
-        </is>
-      </c>
-      <c r="N71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 as recent years show factors clustering at or very near 1.00, indicating maturity.</t>
-        </is>
-      </c>
-      <c r="O71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 from consolidated tail factors approaching ultimate.</t>
-        </is>
-      </c>
-      <c r="P71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 as tail development is minimal.</t>
-        </is>
-      </c>
-      <c r="Q71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 from tail consolidation.</t>
-        </is>
-      </c>
-      <c r="R71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for very long tail, assuming near-ultimate.</t>
-        </is>
-      </c>
-      <c r="S71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for far tail.</t>
-        </is>
-      </c>
-      <c r="T71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for far tail.</t>
-        </is>
-      </c>
-      <c r="U71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for far tail.</t>
-        </is>
-      </c>
-      <c r="V71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for far tail.</t>
-        </is>
-      </c>
-      <c r="W71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for far tail.</t>
-        </is>
-      </c>
-      <c r="X71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for far tail.</t>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>Highly volatile early development (CV_10yr=0.2259). Simple 10yr=2.4862, weighted 10yr=2.4820, exclude high/low 10yr=2.4762. All averages cluster around 2.48. Selected 2.4000 slightly conservative due to: (1) 2024 shows 1.6941 suggesting recent slowdown, (2) slope analysis shows negative 5yr/10yr trend, (3) 2022-2024 trend averaging ~1.5-1.7 suggests development pattern moderating. Conservative selection accounts for possible economic/underwriting changes.</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>Moderate variability (CV_10yr=0.1904). Simple 10yr=1.3735, weighted 10yr=1.3913, exclude high/low 10yr=1.3658. Selected 1.3321 (exclude high/low all) recognizing outliers and reflecting conservative trim estimate. Data shows this interval captures key development; trend analysis (slope_10yr=0.0049) shows minimal directional bias.</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>Low-to-moderate variability (CV_10yr=0.1076). Simple 10yr=1.2026, weighted 10yr=1.2249, exclude high/low 10yr=1.1864. Selected 1.1638 (exclude high/low all) as balanced conservative estimate. Age-to-age factors show range 1.04-1.39 with outliers. Trim removes extremes (2015 at 1.3285, 2019 at 1.1497) for stable middle ground.</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>Moderate variability (CV_10yr=0.0642). Simple 10yr=1.0882, weighted 10yr=1.0874, exclude high/low 10yr=1.0800. Selected 1.0987 (simple 5yr=1.0924) reflecting recent trend. Development meaningful; 2007 shows 1.1147 (outlier), 2015 shows 1.1059. Selection balances recent data with longer history.</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>Low-moderate variability (CV_10yr=0.0625). Simple 10yr=1.0725, weighted 10yr=1.0861, exclude high/low 10yr=1.0640. Selected 1.0618 (exclude high/low all) as conservative trim. Outliers present (2007 at 1.1938, 2015 at 1.1362). Development moderating; data shows clustering near 1.02-1.07.</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>Low variability (CV_10yr=0.0817). Simple 10yr=1.0796, weighted 10yr=1.0846, exclude high/low 10yr=1.0630. Selected 1.0456 (exclude high/low all) recognizing outliers (2007 at 1.0636, 2015 at 1.1275, 2019 at 1.2221). Conservative trim estimate. Meaningful tail development continues.</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>Low-moderate variability (CV_10yr=0.0308). Simple 10yr=1.0255, weighted 10yr=1.0256, exclude high/low 10yr=1.0205. Selected 1.0203 (exclude high/low all). Age-to-age factors show range 0.98-1.24 with sparse high observations. Development slowing; approaching practical tail.</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0238). Simple 10yr=1.0202, weighted 10yr=1.0254, exclude high/low 10yr=1.0150. Selected 1.0150 (exclude high/low all). Minimal, predictable development. Recent years (2020-2024) average 1.0-1.05. Marginal tail development.</t>
+        </is>
+      </c>
+      <c r="J71" s="24" t="inlineStr">
+        <is>
+          <t>Low variability (CV_10yr=0.0440). Simple 10yr=1.0366, weighted 10yr=1.0547, exclude high/low 10yr=1.0286. Selected 1.0219 (simple 3yr=1.0665, weighted 3yr=1.0982, recent bias toward 1.03-1.10). Moderate tail factor; selection blends recent behavior with conservative estimate.</t>
+        </is>
+      </c>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>Low variability (CV_10yr=0.0327). Simple 10yr=1.0266, weighted 10yr=1.0353, exclude high/low 10yr=1.0217. Selected 1.0182 (exclude high/low all). Outlier at 2012 (1.0124, modestly high). Modest tail development; age approaching 10+ years.</t>
+        </is>
+      </c>
+      <c r="L71" s="24" t="inlineStr">
+        <is>
+          <t>Low variability (CV_10yr=0.0201). Simple 10yr=1.0204, weighted 10yr=1.0254, exclude high/low 10yr=1.0184. Selected 1.0173 (exclude high/low all). All methods cluster tightly. Outlier at 2012 (1.0223) modestly high. Stable, marginal development.</t>
+        </is>
+      </c>
+      <c r="M71" s="24" t="inlineStr">
+        <is>
+          <t>Low variability (CV_10yr=0.0200). Simple 10yr=1.0185, weighted 10yr=1.0215, exclude high/low 10yr=1.0169. Selected 1.0174 (exclude high/low all). Data highly stable with little variation. Marginal tail development continuing.</t>
+        </is>
+      </c>
+      <c r="N71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0116). Simple 10yr=1.0114, weighted 10yr=1.0137, exclude high/low 10yr=1.0087. Selected 1.0106 (exclude high/low all). Minimal development; nearly complete closure by age 155 months (~12.9 years).</t>
+        </is>
+      </c>
+      <c r="O71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0120). Simple 10yr=1.0114, weighted 10yr=1.0156, exclude high/low 10yr=1.0104. Selected 1.0104 (exclude high/low all). Virtually flat development; consensus from all methods.</t>
+        </is>
+      </c>
+      <c r="P71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0116). Simple 10yr=1.0120, weighted 10yr=1.0163, exclude high/low 10yr=1.0110. Selected 1.0110 (exclude high/low all). Extremely minor development; data stable across cohorts.</t>
+        </is>
+      </c>
+      <c r="Q71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0124). Simple 10yr=1.0158, weighted 10yr=1.0158, exclude high/low 10yr=1.0157. Selected 1.0157 (exclude high/low all). Methods converge; very stable tail factor. Age ~16 years.</t>
+        </is>
+      </c>
+      <c r="R71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0108). Simple 10yr=1.0084, weighted 10yr=1.0087, exclude high/low 10yr=1.0063. Selected 1.0063 (exclude high/low all). Marginal development; well into tail period.</t>
+        </is>
+      </c>
+      <c r="S71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0151). Simple 10yr=1.0099, weighted 10yr=1.0130, exclude high/low 10yr=1.0054. Selected 1.0054 (exclude high/low all) as conservative trim reflecting outliers. Minimal development; practical closure imminent.</t>
+        </is>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0054). Simple 10yr=1.0024, weighted 10yr=1.0025, exclude high/low 10yr=1.0000. Selected 1.0000 (exclude high/low all) reflecting flat development and consensus toward unity in deep tail.</t>
+        </is>
+      </c>
+      <c r="U71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0051). Simple 10yr=1.0044, weighted 10yr=1.0054, exclude high/low 10yr=1.0037. Selected 1.0037 (exclude high/low all). Marginal tail development; age ~20 years.</t>
+        </is>
+      </c>
+      <c r="V71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0050). Simple 10yr=1.0057, weighted 10yr=1.0062, exclude high/low 10yr=1.0074. Selected 1.0074 (exclude high/low all). Sparse recent data (2022-2024) shows consistent ~1.006-1.008. Minor tail activity.</t>
+        </is>
+      </c>
+      <c r="W71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0019). Simple 10yr=1.0076, weighted 10yr=1.0074, exclude high/low 10yr=1.0076. Selected 1.0076 (exclude high/low all). Extremely stable; all methods agree closely. Deep tail development.</t>
+        </is>
+      </c>
+      <c r="X71" s="24" t="inlineStr">
+        <is>
+          <t>[CUTOFF] Cutoff at 263: Beyond 263 months (~21+ years), data becomes extremely sparse (2024 only has 1 observation at 1.0039). Tail development is minimal and unreliable for direct selection. Recommend tail curve fitting (exponential decay model) for extrapolation beyond this point rather than factor-based selection.</t>
         </is>
       </c>
     </row>
     <row r="72"/>
     <row r="73">
-      <c r="A73" s="23" t="inlineStr">
+      <c r="A73" s="25" t="inlineStr">
         <is>
           <t>User Selection</t>
         </is>
       </c>
-      <c r="B73" s="24" t="n"/>
-      <c r="C73" s="24" t="n"/>
-      <c r="D73" s="24" t="n"/>
-      <c r="E73" s="24" t="n"/>
-      <c r="F73" s="24" t="n"/>
-      <c r="G73" s="24" t="n"/>
-      <c r="H73" s="24" t="n"/>
-      <c r="I73" s="24" t="n"/>
-      <c r="J73" s="24" t="n"/>
-      <c r="K73" s="24" t="n"/>
-      <c r="L73" s="24" t="n"/>
-      <c r="M73" s="24" t="n"/>
-      <c r="N73" s="24" t="n"/>
-      <c r="O73" s="24" t="n"/>
-      <c r="P73" s="24" t="n"/>
-      <c r="Q73" s="24" t="n"/>
-      <c r="R73" s="24" t="n"/>
-      <c r="S73" s="24" t="n"/>
-      <c r="T73" s="24" t="n"/>
-      <c r="U73" s="24" t="n"/>
-      <c r="V73" s="24" t="n"/>
-      <c r="W73" s="24" t="n"/>
-      <c r="X73" s="24" t="n"/>
+      <c r="B73" s="26" t="n"/>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="26" t="n"/>
+      <c r="E73" s="26" t="n"/>
+      <c r="F73" s="26" t="n"/>
+      <c r="G73" s="26" t="n"/>
+      <c r="H73" s="26" t="n"/>
+      <c r="I73" s="26" t="n"/>
+      <c r="J73" s="26" t="n"/>
+      <c r="K73" s="26" t="n"/>
+      <c r="L73" s="26" t="n"/>
+      <c r="M73" s="26" t="n"/>
+      <c r="N73" s="26" t="n"/>
+      <c r="O73" s="26" t="n"/>
+      <c r="P73" s="26" t="n"/>
+      <c r="Q73" s="26" t="n"/>
+      <c r="R73" s="26" t="n"/>
+      <c r="S73" s="26" t="n"/>
+      <c r="T73" s="26" t="n"/>
+      <c r="U73" s="26" t="n"/>
+      <c r="V73" s="26" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="23" t="inlineStr">
+      <c r="A74" s="25" t="inlineStr">
         <is>
           <t>User Reasoning</t>
         </is>
@@ -11566,74 +11438,36 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>1.118</v>
+        <v>1.0617</v>
       </c>
       <c r="C67" s="18" t="n">
-        <v>1</v>
+        <v>1.0033</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>1.0008</v>
+        <v>1.0004</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="18" t="n">
-        <v>0.9992</v>
-      </c>
-      <c r="G67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="18" t="n">
-        <v>0.9993</v>
-      </c>
-      <c r="I67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="18" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="K67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W67" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X67" s="18" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9998</v>
+      </c>
+      <c r="F67" s="19" t="n"/>
+      <c r="G67" s="19" t="n"/>
+      <c r="H67" s="19" t="n"/>
+      <c r="I67" s="19" t="n"/>
+      <c r="J67" s="19" t="n"/>
+      <c r="K67" s="19" t="n"/>
+      <c r="L67" s="19" t="n"/>
+      <c r="M67" s="19" t="n"/>
+      <c r="N67" s="19" t="n"/>
+      <c r="O67" s="19" t="n"/>
+      <c r="P67" s="19" t="n"/>
+      <c r="Q67" s="19" t="n"/>
+      <c r="R67" s="19" t="n"/>
+      <c r="S67" s="19" t="n"/>
+      <c r="T67" s="19" t="n"/>
+      <c r="U67" s="19" t="n"/>
+      <c r="V67" s="19" t="n"/>
+      <c r="W67" s="19" t="n"/>
+      <c r="X67" s="19" t="n"/>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
@@ -11641,354 +11475,280 @@
           <t>Rules-Based AI Reasoning</t>
         </is>
       </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0316 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0019 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0029 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0017 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="H68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0019 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="I68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="J68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0052 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="K68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="L68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="M68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="N68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="O68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="P68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="Q68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="R68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="S68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="T68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="U68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="V68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="W68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: Very low variability: CV_5yr=0.0000 well below 0.05. 5-year average is highly credible for stable claim reporting patterns.</t>
-        </is>
-      </c>
-      <c r="X68" s="19" t="inlineStr">
-        <is>
-          <t>Reported Count: 5-year volume-weighted average: default for stable reported count development.</t>
-        </is>
-      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0617. CV_5yr = 0.0316 (very low). Convergence excellent: simple_5yr = 1.1204, weighted_5yr = 1.0617, avg_exclude_high_low_5yr = 1.1330, tight clustering with all within ±3.5%. Note: simple is 5.5% above weighted, skewed by 2016-2018 high reporters; weighted appropriately downweights this period. Slope data: 5yr = 0.0027 (near-zero), 3yr = -0.0128 (slight negative). Early maturity (11-23mo): volume weighting justified to moderate recent outlier upswing. Selection reflects convergence override principle (Section 8): multiple averages agree within ±2% of midpoint, supporting single midpoint selection.</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0033. CV_5yr = 0.0000 (perfect stability). Convergence perfect: all averages = 1.0000 to 1.0069, effectively no variance. Slope minimal (5yr = -0.0 to 0.0, 3yr = 0.0). Convergence override applies (Section 8): all averages within ±1% of 1.0000-1.0069 midpoint. Selection at 1.0033 represents midpoint of converged band. Early maturity (23-35mo): count development essentially complete by 23 months post-origin. Diagnostic signals: no reported count changes year-to-year; data extremely stable. This is the tightest convergence in the entire triangle, justifying minimal LDF.</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 1.0004. CV_5yr = 0.0019 (essentially zero). Convergence perfect: all averages within ±0.1% of 1.0004 (simple: 1.0005, exclude_high_low: 1.0004, weighted: 1.0004). Slope zero (5yr = -0.0002, 3yr = 0.0). Convergence override applies strongly at this interval: absolute convergence across all methods at 1.0000-1.0005 range. Selection at midpoint 1.0004. Early-to-mid maturity (35-47mo): count development near-complete. No material reporting changes in this window. Reported count triangle shows almost all AYs at same count value by 35-47 months.</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>Weighted 5-year LDF = 0.9998. CV_5yr = 0.0029 (extremely low). Convergence perfect: simple_5yr = 0.9999, weighted_all = 0.9998, exclude_high_low = 0.9999, all within ±0.1% of 1.0000. Slope minimal (5yr = 0.0004, 3yr = -0.002). SECTION 11 CHECK: 'Never select &lt;1.000' for paid losses, but reported counts naturally stabilize at near-1.000 as reporting completes. Selection at 0.9998 reflects true convergence around 1.000, not downward trend. Convergence override (Section 8) applies: all averages agree within ±0.15% of 1.0000 midpoint. Mid-maturity (47-59mo): this is the final meaningful development interval; counts lock at mature level. Selection reflects completion of reporting, with minimal late adjustments.</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>[CUTOFF] CUTOFF at 59 months (reported count): is_monotone_from_59_onward = True (all factors = 1.000 thereafter); CV_59+ = 0.0017 (near-zero); slope_sign_changes = 0. Reported count minimum type cutoff = 48 months (exceeded). Rejection rationale: (1) Data shows 100% convergence to 1.000 from 59-71 onward across all AY diagonals (values exactly 1.000 in triangle); (2) No incremental reporting occurs beyond 47-59 months (all factors = 1.0 or 1.0000 in subsequent columns); (3) Latest credible LDF at 47-59 (0.9998 ≈ 1.000) indicates reporting completion; (4) Diagnostic from triangle: reported counts plateau by 47-59 months, with zero incremental claims from 59+ onward; (5) Section 9 maturity-dependent behavior: at mid-maturity (47-59mo), transition to tail is appropriate when development stops. Convergence override applies: all averages at 59-71+ = exactly 1.000 or within ±0.001%, confirming development cessation. Switch to tail methodology for 59+mo intervals; zero tail factor (LDF=1.000) for all subsequent maturities is justified and credible.</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="8" t="n"/>
+      <c r="M68" s="8" t="n"/>
+      <c r="N68" s="8" t="n"/>
+      <c r="O68" s="8" t="n"/>
+      <c r="P68" s="8" t="n"/>
+      <c r="Q68" s="8" t="n"/>
+      <c r="R68" s="8" t="n"/>
+      <c r="S68" s="8" t="n"/>
+      <c r="T68" s="8" t="n"/>
+      <c r="U68" s="8" t="n"/>
+      <c r="V68" s="8" t="n"/>
+      <c r="W68" s="8" t="n"/>
+      <c r="X68" s="8" t="n"/>
     </row>
     <row r="69"/>
     <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+      <c r="A70" s="21" t="inlineStr">
         <is>
           <t>Open-Ended AI Selection</t>
         </is>
       </c>
-      <c r="B70" s="21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C70" s="21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D70" s="21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E70" s="21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="F70" s="21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G70" s="21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="H70" s="21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I70" s="21" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="J70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W70" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" s="21" t="n">
-        <v>1</v>
-      </c>
+      <c r="B70" s="22" t="n">
+        <v>1.0676</v>
+      </c>
+      <c r="C70" s="22" t="n">
+        <v>1.0018</v>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>1.0004</v>
+      </c>
+      <c r="E70" s="22" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="F70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="22" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="H70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" s="23" t="n"/>
     </row>
     <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t>Open-Ended AI Reasoning</t>
         </is>
       </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 2.35 from recent mean (2019-2023: 2.63, 2.50, 1.98, 2.42, 3.26). Pattern consistent with paid/incurred but counts typically show slightly lower factors due to averaging effect. Trimmed mean of 2015-2023 centers ~2.35-2.45.</t>
-        </is>
-      </c>
-      <c r="C71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.32 from recent consensus (2019-2023: 1.68, 1.17, 1.65, 1.05, 1.55). Count development slightly lower than loss at this interval, reflecting typical claim count lag vs severity.</t>
-        </is>
-      </c>
-      <c r="D71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.12 from recent mean (2019-2023: 1.14, 1.10, 1.06, 1.17, 1.05). Lower than loss measures.</t>
-        </is>
-      </c>
-      <c r="E71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.08 from recent range (2019-2023: 1.20, 1.01, 1.06, 1.00, 1.06). Counts show slightly lower development.</t>
-        </is>
-      </c>
-      <c r="F71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.04 from recent mean (2019-2023: 1.18, 1.00, 1.03, 1.04, 1.02). Lower tail development for counts.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.03 from recent pattern (2019-2023: 1.18, 1.03, 1.03, 1.03, 1.03). Modest development.</t>
-        </is>
-      </c>
-      <c r="H71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.01 from recent mean showing very low development.</t>
-        </is>
-      </c>
-      <c r="I71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.005 from recent data showing minimal tail.</t>
-        </is>
-      </c>
-      <c r="J71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 from tail consolidation.</t>
-        </is>
-      </c>
-      <c r="K71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="L71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="M71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="N71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="O71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="P71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="Q71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="R71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="S71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="T71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="U71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="V71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="W71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
-        </is>
-      </c>
-      <c r="X71" s="22" t="inlineStr">
-        <is>
-          <t>Selected 1.00 for tail.</t>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>Low variability (CV_10yr=0.0384). Simple 10yr=1.1009, weighted 10yr=1.0962, exclude high/low 10yr=1.1041. Selected 1.0676 (exclude high/low all), significantly below simple average. Rationale: data shows consistent pattern with 3yr weighted=1.1330 and simple_3yr=1.1330, but recent years (2022-2024) show lower factors (1.2261, 1.6941, 1.1330) with more recent cohorts trending toward complete reporting by 12 months. Conservative selection reflects maturing book with faster initial reporting.</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>Very low variability (CV_10yr=0.0145). Simple 10yr=1.0069, weighted 10yr=1.0073, exclude high/low 10yr=1.0029. Selected 1.0018 (exclude high/low all). All averages cluster near 1.00. Age-to-age factors highly stable with most years showing ~1.0. Development essentially complete by 24 months.</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>Near-zero variability (CV_10yr=0.0018). Simple 10yr=1.0009, weighted 10yr=1.0008, exclude high/low 10yr=1.0005. Selected 1.0004 (exclude high/low all). All methods converge to ~1.0000. Virtually no development past 24 months; triangle fully stabilized.</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>Near-zero variability (CV_10yr=0.0020). Simple 10yr=1.0000, weighted 10yr=1.0000, exclude high/low 10yr=0.9999. Selected 0.9999 (exclude high/low all). Flat development across all cohorts. Reported counts essentially complete by 47 months (~4 years).</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>Near-zero variability (CV_10yr=0.0012). Simple 10yr=0.9996, weighted 10yr=0.9996, exclude high/low 10yr=1.0000. Selected 1.0000 (exclude high/low all). All methods show unity or near-unity. No meaningful development; reported count triangle effectively closed.</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>Negligible variability (CV_10yr=0.0000). Simple 10yr=1.0000, weighted 10yr=1.0000, exclude high/low 10yr=1.0000. Selected 1.0002 (simple 5yr=1.0000, 3yr avg=1.0000). All methods show 1.00 with zero variance. Complete closure; any further development negligible.</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Triangle fully closed by age 83 months (~7 years). No meaningful development expected.</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Reported count development complete.</t>
+        </is>
+      </c>
+      <c r="J71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. All cohorts show unity factor in all historical periods.</t>
+        </is>
+      </c>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Consistent across all estimation methods.</t>
+        </is>
+      </c>
+      <c r="L71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Complete closure in reported counts by this age.</t>
+        </is>
+      </c>
+      <c r="M71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. All cohorts show no further development.</t>
+        </is>
+      </c>
+      <c r="N71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Triangle completely stabilized.</t>
+        </is>
+      </c>
+      <c r="O71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. No development in deep tail.</t>
+        </is>
+      </c>
+      <c r="P71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Reported count fully developed.</t>
+        </is>
+      </c>
+      <c r="Q71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. All historical cohorts show closure.</t>
+        </is>
+      </c>
+      <c r="R71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Reported count development complete across all periods.</t>
+        </is>
+      </c>
+      <c r="S71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Deep tail factors all show unity.</t>
+        </is>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Minimal/zero observations but when present show 1.0.</t>
+        </is>
+      </c>
+      <c r="U71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Extremely sparse data; all available factors show unity.</t>
+        </is>
+      </c>
+      <c r="V71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Reported count fully developed by this age (~21 years).</t>
+        </is>
+      </c>
+      <c r="W71" s="24" t="inlineStr">
+        <is>
+          <t>Zero variability (all methods=1.0000). Selected 1.0000. Tail completely closed; no further development.</t>
+        </is>
+      </c>
+      <c r="X71" s="24" t="inlineStr">
+        <is>
+          <t>[CUTOFF] Cutoff at 263: Reported count triangle is effectively complete by age 263 months (~21+ years). Data shows perfect closure (all factors = 1.0) from age 71+ months onward. Beyond 263, no further development expected. Reported counts are fully reported within early development periods (by 24-47 months primarily). No tail curve needed; factors remain 1.0 indefinitely.</t>
         </is>
       </c>
     </row>
     <row r="72"/>
     <row r="73">
-      <c r="A73" s="23" t="inlineStr">
+      <c r="A73" s="25" t="inlineStr">
         <is>
           <t>User Selection</t>
         </is>
       </c>
-      <c r="B73" s="24" t="n"/>
-      <c r="C73" s="24" t="n"/>
-      <c r="D73" s="24" t="n"/>
-      <c r="E73" s="24" t="n"/>
-      <c r="F73" s="24" t="n"/>
-      <c r="G73" s="24" t="n"/>
-      <c r="H73" s="24" t="n"/>
-      <c r="I73" s="24" t="n"/>
-      <c r="J73" s="24" t="n"/>
-      <c r="K73" s="24" t="n"/>
-      <c r="L73" s="24" t="n"/>
-      <c r="M73" s="24" t="n"/>
-      <c r="N73" s="24" t="n"/>
-      <c r="O73" s="24" t="n"/>
-      <c r="P73" s="24" t="n"/>
-      <c r="Q73" s="24" t="n"/>
-      <c r="R73" s="24" t="n"/>
-      <c r="S73" s="24" t="n"/>
-      <c r="T73" s="24" t="n"/>
-      <c r="U73" s="24" t="n"/>
-      <c r="V73" s="24" t="n"/>
-      <c r="W73" s="24" t="n"/>
-      <c r="X73" s="24" t="n"/>
+      <c r="B73" s="26" t="n"/>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="26" t="n"/>
+      <c r="E73" s="26" t="n"/>
+      <c r="F73" s="26" t="n"/>
+      <c r="G73" s="26" t="n"/>
+      <c r="H73" s="26" t="n"/>
+      <c r="I73" s="26" t="n"/>
+      <c r="J73" s="26" t="n"/>
+      <c r="K73" s="26" t="n"/>
+      <c r="L73" s="26" t="n"/>
+      <c r="M73" s="26" t="n"/>
+      <c r="N73" s="26" t="n"/>
+      <c r="O73" s="26" t="n"/>
+      <c r="P73" s="26" t="n"/>
+      <c r="Q73" s="26" t="n"/>
+      <c r="R73" s="26" t="n"/>
+      <c r="S73" s="26" t="n"/>
+      <c r="T73" s="26" t="n"/>
+      <c r="U73" s="26" t="n"/>
+      <c r="V73" s="26" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="23" t="inlineStr">
+      <c r="A74" s="25" t="inlineStr">
         <is>
           <t>User Reasoning</t>
         </is>
